--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202392</v>
+        <v>120205312</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566555</v>
+        <v>566618</v>
       </c>
       <c r="R2" t="n">
-        <v>7041027</v>
+        <v>7040939</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,9 +757,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120201451</v>
+        <v>120203078</v>
       </c>
       <c r="B3" t="n">
         <v>79607</v>
@@ -821,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566541</v>
+        <v>566621</v>
       </c>
       <c r="R3" t="n">
-        <v>7040997</v>
+        <v>7041057</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,19 +869,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,22 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120205179</v>
+        <v>120200832</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +910,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566503</v>
+        <v>566507</v>
       </c>
       <c r="R4" t="n">
-        <v>7041183</v>
+        <v>7041231</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,9 +976,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120205420</v>
+        <v>120204205</v>
       </c>
       <c r="B5" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,46 +1031,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566583</v>
+        <v>566711</v>
       </c>
       <c r="R5" t="n">
-        <v>7040942</v>
+        <v>7041082</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,19 +1088,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120200869</v>
+        <v>120204116</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,25 +1129,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566512</v>
+        <v>566691</v>
       </c>
       <c r="R6" t="n">
-        <v>7041220</v>
+        <v>7041096</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,19 +1190,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,22 +1207,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120205148</v>
+        <v>120204507</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566529</v>
+        <v>566602</v>
       </c>
       <c r="R7" t="n">
-        <v>7041203</v>
+        <v>7041134</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1330,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204862</v>
+        <v>120204797</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>96862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566579</v>
+        <v>566572</v>
       </c>
       <c r="R8" t="n">
-        <v>7041130</v>
+        <v>7041137</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1432,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203937</v>
+        <v>120203123</v>
       </c>
       <c r="B9" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,38 +1435,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566660</v>
+        <v>566628</v>
       </c>
       <c r="R9" t="n">
-        <v>7041078</v>
+        <v>7041063</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1534,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120201620</v>
+        <v>120205420</v>
       </c>
       <c r="B10" t="n">
-        <v>91005</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,38 +1541,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566582</v>
+        <v>566583</v>
       </c>
       <c r="R10" t="n">
-        <v>7040944</v>
+        <v>7040942</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1623,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,22 +1638,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120201767</v>
+        <v>120202492</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,41 +1662,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566610</v>
+        <v>566568</v>
       </c>
       <c r="R11" t="n">
-        <v>7040928</v>
+        <v>7041045</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,24 +1727,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,22 +1744,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120202642</v>
+        <v>120205460</v>
       </c>
       <c r="B12" t="n">
-        <v>74638</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,34 +1772,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566590</v>
+        <v>566500</v>
       </c>
       <c r="R12" t="n">
-        <v>7041023</v>
+        <v>7041094</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1839,6 +1837,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202571</v>
+        <v>120204492</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,42 +1880,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566582</v>
+        <v>566608</v>
       </c>
       <c r="R13" t="n">
-        <v>7041015</v>
+        <v>7041149</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1971,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120202697</v>
+        <v>120201490</v>
       </c>
       <c r="B14" t="n">
-        <v>90576</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,13 +2010,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566589</v>
+        <v>566563</v>
       </c>
       <c r="R14" t="n">
-        <v>7041075</v>
+        <v>7040951</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,9 +2043,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,22 +2070,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204507</v>
+        <v>120204567</v>
       </c>
       <c r="B15" t="n">
-        <v>79144</v>
+        <v>90527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2094,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566602</v>
+        <v>566612</v>
       </c>
       <c r="R15" t="n">
-        <v>7041134</v>
+        <v>7041175</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2175,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120205511</v>
+        <v>120205179</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,43 +2196,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566509</v>
+        <v>566503</v>
       </c>
       <c r="R16" t="n">
-        <v>7041097</v>
+        <v>7041183</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2256,11 +2260,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120201490</v>
+        <v>120200869</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,21 +2302,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2327,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566563</v>
+        <v>566512</v>
       </c>
       <c r="R17" t="n">
-        <v>7040951</v>
+        <v>7041220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,7 +2361,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2372,7 +2371,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,22 +2386,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204901</v>
+        <v>120200849</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,21 +2414,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2439,13 +2438,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566567</v>
+        <v>566521</v>
       </c>
       <c r="R18" t="n">
-        <v>7041107</v>
+        <v>7041283</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,9 +2471,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,22 +2503,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120205084</v>
+        <v>120202768</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,42 +2527,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566515</v>
+        <v>566600</v>
       </c>
       <c r="R19" t="n">
-        <v>7041125</v>
+        <v>7041007</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2607,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204104</v>
+        <v>120204945</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
+        <v>90846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,21 +2633,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2647,10 +2657,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566694</v>
+        <v>566565</v>
       </c>
       <c r="R20" t="n">
-        <v>7041098</v>
+        <v>7041107</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2709,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204980</v>
+        <v>120205398</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,21 +2735,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,13 +2759,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566561</v>
+        <v>566613</v>
       </c>
       <c r="R21" t="n">
-        <v>7041107</v>
+        <v>7040940</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2782,9 +2792,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2799,22 +2819,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120205064</v>
+        <v>120205323</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2823,25 +2843,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2851,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566502</v>
+        <v>566528</v>
       </c>
       <c r="R22" t="n">
-        <v>7041103</v>
+        <v>7041117</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2913,10 +2933,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120205024</v>
+        <v>120201983</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>57463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,41 +2945,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566549</v>
+        <v>566636</v>
       </c>
       <c r="R23" t="n">
-        <v>7041126</v>
+        <v>7040903</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2986,9 +3011,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,19 +3038,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120205221</v>
+        <v>120201767</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3049,24 +3084,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566496</v>
+        <v>566610</v>
       </c>
       <c r="R24" t="n">
-        <v>7041192</v>
+        <v>7040928</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3093,14 +3123,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3115,22 +3155,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120204013</v>
+        <v>120202239</v>
       </c>
       <c r="B25" t="n">
-        <v>78262</v>
+        <v>90724</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3143,21 +3183,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>1588</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3167,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566666</v>
+        <v>566526</v>
       </c>
       <c r="R25" t="n">
-        <v>7041066</v>
+        <v>7041005</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3229,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120203396</v>
+        <v>120205084</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,38 +3281,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566638</v>
+        <v>566515</v>
       </c>
       <c r="R26" t="n">
-        <v>7041075</v>
+        <v>7041125</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3331,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120204405</v>
+        <v>120204901</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,25 +3387,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3415,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566637</v>
+        <v>566567</v>
       </c>
       <c r="R27" t="n">
-        <v>7041131</v>
+        <v>7041107</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3433,10 +3477,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120204492</v>
+        <v>120205024</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,25 +3489,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3473,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566608</v>
+        <v>566549</v>
       </c>
       <c r="R28" t="n">
-        <v>7041149</v>
+        <v>7041126</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3535,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120204476</v>
+        <v>120201350</v>
       </c>
       <c r="B29" t="n">
-        <v>78262</v>
+        <v>79608</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3551,21 +3595,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3575,13 +3619,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566635</v>
+        <v>566534</v>
       </c>
       <c r="R29" t="n">
-        <v>7041139</v>
+        <v>7040990</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3608,9 +3652,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3625,22 +3679,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120205323</v>
+        <v>120205199</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3653,34 +3707,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566528</v>
+        <v>566499</v>
       </c>
       <c r="R30" t="n">
-        <v>7041117</v>
+        <v>7041189</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3713,6 +3772,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3739,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120205368</v>
+        <v>120205138</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3755,39 +3819,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566521</v>
+        <v>566529</v>
       </c>
       <c r="R31" t="n">
-        <v>7041138</v>
+        <v>7041203</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3820,11 +3879,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3851,10 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202492</v>
+        <v>120202733</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3863,42 +3917,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566568</v>
+        <v>566567</v>
       </c>
       <c r="R32" t="n">
-        <v>7041045</v>
+        <v>7041052</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3957,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120202755</v>
+        <v>120202674</v>
       </c>
       <c r="B33" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3969,25 +4019,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566572</v>
+        <v>566584</v>
       </c>
       <c r="R33" t="n">
-        <v>7041055</v>
+        <v>7041103</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4059,7 +4109,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120204153</v>
+        <v>120204862</v>
       </c>
       <c r="B34" t="n">
         <v>90527</v>
@@ -4099,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566671</v>
+        <v>566579</v>
       </c>
       <c r="R34" t="n">
-        <v>7041071</v>
+        <v>7041130</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4161,10 +4211,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120203571</v>
+        <v>120205278</v>
       </c>
       <c r="B35" t="n">
-        <v>89633</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,38 +4223,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566647</v>
+        <v>566528</v>
       </c>
       <c r="R35" t="n">
-        <v>7041053</v>
+        <v>7041117</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4263,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120202853</v>
+        <v>120202755</v>
       </c>
       <c r="B36" t="n">
-        <v>79607</v>
+        <v>91005</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4275,25 +4329,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4303,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566624</v>
+        <v>566572</v>
       </c>
       <c r="R36" t="n">
-        <v>7041060</v>
+        <v>7041055</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4365,10 +4419,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120203962</v>
+        <v>120202647</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4377,38 +4431,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566665</v>
+        <v>566587</v>
       </c>
       <c r="R37" t="n">
-        <v>7041086</v>
+        <v>7041021</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4467,10 +4525,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120204358</v>
+        <v>120202727</v>
       </c>
       <c r="B38" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4483,21 +4541,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4507,10 +4565,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566663</v>
+        <v>566577</v>
       </c>
       <c r="R38" t="n">
-        <v>7041118</v>
+        <v>7041064</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4569,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120204212</v>
+        <v>120205468</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,42 +4639,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566711</v>
+        <v>566498</v>
       </c>
       <c r="R39" t="n">
-        <v>7041082</v>
+        <v>7041093</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4675,10 +4729,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120202674</v>
+        <v>120204104</v>
       </c>
       <c r="B40" t="n">
-        <v>90562</v>
+        <v>78262</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4691,21 +4745,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4715,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566584</v>
+        <v>566694</v>
       </c>
       <c r="R40" t="n">
-        <v>7041103</v>
+        <v>7041098</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4777,10 +4831,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120202239</v>
+        <v>120204980</v>
       </c>
       <c r="B41" t="n">
-        <v>90724</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4793,21 +4847,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1588</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4817,10 +4871,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566526</v>
+        <v>566561</v>
       </c>
       <c r="R41" t="n">
-        <v>7041005</v>
+        <v>7041107</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4879,10 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120205138</v>
+        <v>120201661</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4895,21 +4949,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4919,13 +4973,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566529</v>
+        <v>566582</v>
       </c>
       <c r="R42" t="n">
-        <v>7041203</v>
+        <v>7040944</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4952,9 +5006,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4969,22 +5033,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120202867</v>
+        <v>120205511</v>
       </c>
       <c r="B43" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4993,38 +5057,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566626</v>
+        <v>566509</v>
       </c>
       <c r="R43" t="n">
-        <v>7041042</v>
+        <v>7041097</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5057,6 +5126,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5083,10 +5157,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120200832</v>
+        <v>120204816</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5099,42 +5173,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566507</v>
+        <v>566572</v>
       </c>
       <c r="R44" t="n">
-        <v>7041231</v>
+        <v>7041139</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5161,19 +5230,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5188,22 +5247,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120201661</v>
+        <v>120202622</v>
       </c>
       <c r="B45" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5212,25 +5271,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5240,13 +5299,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566582</v>
+        <v>566590</v>
       </c>
       <c r="R45" t="n">
-        <v>7040944</v>
+        <v>7041027</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5273,19 +5332,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5300,22 +5349,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120204567</v>
+        <v>120200809</v>
       </c>
       <c r="B46" t="n">
-        <v>90527</v>
+        <v>56514</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5324,41 +5373,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566612</v>
+        <v>566509</v>
       </c>
       <c r="R46" t="n">
-        <v>7041175</v>
+        <v>7041308</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5385,9 +5439,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5402,22 +5466,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120202824</v>
+        <v>120205148</v>
       </c>
       <c r="B47" t="n">
-        <v>90562</v>
+        <v>79636</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5426,25 +5490,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5454,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566616</v>
+        <v>566529</v>
       </c>
       <c r="R47" t="n">
-        <v>7041049</v>
+        <v>7041203</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5516,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120202768</v>
+        <v>120202297</v>
       </c>
       <c r="B48" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5532,21 +5596,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5556,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566600</v>
+        <v>566551</v>
       </c>
       <c r="R48" t="n">
-        <v>7041007</v>
+        <v>7040999</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5618,10 +5682,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120202786</v>
+        <v>120203937</v>
       </c>
       <c r="B49" t="n">
-        <v>91005</v>
+        <v>90846</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5630,25 +5694,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5658,10 +5722,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566623</v>
+        <v>566660</v>
       </c>
       <c r="R49" t="n">
-        <v>7041032</v>
+        <v>7041078</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5720,10 +5784,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120201231</v>
+        <v>120204958</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5736,21 +5800,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5760,13 +5824,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566502</v>
+        <v>566564</v>
       </c>
       <c r="R50" t="n">
-        <v>7041017</v>
+        <v>7041107</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5793,24 +5857,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5825,22 +5874,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120205154</v>
+        <v>120201620</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>91005</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5853,41 +5902,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566510</v>
+        <v>566582</v>
       </c>
       <c r="R51" t="n">
-        <v>7041190</v>
+        <v>7040944</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5914,9 +5959,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5931,22 +5986,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120204797</v>
+        <v>120204212</v>
       </c>
       <c r="B52" t="n">
-        <v>96862</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5955,38 +6010,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566572</v>
+        <v>566711</v>
       </c>
       <c r="R52" t="n">
-        <v>7041137</v>
+        <v>7041082</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6045,10 +6104,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120202811</v>
+        <v>120202571</v>
       </c>
       <c r="B53" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6061,34 +6120,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566616</v>
+        <v>566582</v>
       </c>
       <c r="R53" t="n">
-        <v>7041049</v>
+        <v>7041015</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6147,7 +6210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120202553</v>
+        <v>120202392</v>
       </c>
       <c r="B54" t="n">
         <v>97907</v>
@@ -6191,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566578</v>
+        <v>566555</v>
       </c>
       <c r="R54" t="n">
-        <v>7040998</v>
+        <v>7041027</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6253,10 +6316,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120204835</v>
+        <v>120203396</v>
       </c>
       <c r="B55" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6269,21 +6332,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6293,10 +6356,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566561</v>
+        <v>566638</v>
       </c>
       <c r="R55" t="n">
-        <v>7041134</v>
+        <v>7041075</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6355,7 +6418,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120200849</v>
+        <v>120201231</v>
       </c>
       <c r="B56" t="n">
         <v>57310</v>
@@ -6395,10 +6458,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566521</v>
+        <v>566502</v>
       </c>
       <c r="R56" t="n">
-        <v>7041283</v>
+        <v>7041017</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6430,7 +6493,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6440,12 +6503,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6472,10 +6535,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120202733</v>
+        <v>120205368</v>
       </c>
       <c r="B57" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6488,34 +6551,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566567</v>
+        <v>566521</v>
       </c>
       <c r="R57" t="n">
-        <v>7041052</v>
+        <v>7041138</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6548,6 +6616,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6574,10 +6647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120202647</v>
+        <v>120202867</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6586,42 +6659,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566587</v>
+        <v>566626</v>
       </c>
       <c r="R58" t="n">
-        <v>7041021</v>
+        <v>7041042</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6680,10 +6749,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120202622</v>
+        <v>120202553</v>
       </c>
       <c r="B59" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6692,38 +6761,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566590</v>
+        <v>566578</v>
       </c>
       <c r="R59" t="n">
-        <v>7041027</v>
+        <v>7040998</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6782,10 +6855,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120204807</v>
+        <v>120205154</v>
       </c>
       <c r="B60" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6794,38 +6867,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566575</v>
+        <v>566510</v>
       </c>
       <c r="R60" t="n">
-        <v>7041141</v>
+        <v>7041190</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6884,10 +6961,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120205278</v>
+        <v>120202824</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6896,42 +6973,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566528</v>
+        <v>566616</v>
       </c>
       <c r="R61" t="n">
-        <v>7041117</v>
+        <v>7041049</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6990,10 +7063,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120204945</v>
+        <v>120203571</v>
       </c>
       <c r="B62" t="n">
-        <v>90846</v>
+        <v>89633</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7006,21 +7079,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7030,10 +7103,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566565</v>
+        <v>566647</v>
       </c>
       <c r="R62" t="n">
-        <v>7041107</v>
+        <v>7041053</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7092,10 +7165,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120201350</v>
+        <v>120204267</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7104,25 +7177,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7132,13 +7205,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566534</v>
+        <v>566695</v>
       </c>
       <c r="R63" t="n">
-        <v>7040990</v>
+        <v>7041080</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7165,19 +7238,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7192,22 +7255,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120203123</v>
+        <v>120204013</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7216,42 +7279,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566628</v>
+        <v>566666</v>
       </c>
       <c r="R64" t="n">
-        <v>7041063</v>
+        <v>7041066</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7310,10 +7369,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120201983</v>
+        <v>120205064</v>
       </c>
       <c r="B65" t="n">
-        <v>57463</v>
+        <v>90527</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7322,46 +7381,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566636</v>
+        <v>566502</v>
       </c>
       <c r="R65" t="n">
-        <v>7040903</v>
+        <v>7041103</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7388,19 +7442,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7415,22 +7459,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120205199</v>
+        <v>120203962</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7443,39 +7487,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566499</v>
+        <v>566665</v>
       </c>
       <c r="R66" t="n">
-        <v>7041189</v>
+        <v>7041086</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7508,11 +7547,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7539,10 +7573,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120205192</v>
+        <v>120204405</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7551,43 +7585,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566499</v>
+        <v>566637</v>
       </c>
       <c r="R67" t="n">
-        <v>7041186</v>
+        <v>7041131</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7620,11 +7649,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7651,10 +7675,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120203078</v>
+        <v>120204503</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7667,21 +7691,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7691,10 +7715,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566621</v>
+        <v>566603</v>
       </c>
       <c r="R68" t="n">
-        <v>7041057</v>
+        <v>7041138</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7753,10 +7777,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120204267</v>
+        <v>120204939</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7765,38 +7789,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566695</v>
+        <v>566566</v>
       </c>
       <c r="R69" t="n">
-        <v>7041080</v>
+        <v>7041107</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7855,10 +7883,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120204503</v>
+        <v>120202697</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>90576</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7871,21 +7899,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7895,10 +7923,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566603</v>
+        <v>566589</v>
       </c>
       <c r="R70" t="n">
-        <v>7041138</v>
+        <v>7041075</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7957,10 +7985,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120205398</v>
+        <v>120202811</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>90905</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7969,25 +7997,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7997,13 +8025,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566613</v>
+        <v>566616</v>
       </c>
       <c r="R71" t="n">
-        <v>7040940</v>
+        <v>7041049</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8030,19 +8058,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8057,22 +8075,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120205468</v>
+        <v>120202289</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8085,21 +8103,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8109,10 +8127,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566498</v>
+        <v>566546</v>
       </c>
       <c r="R72" t="n">
-        <v>7041093</v>
+        <v>7041010</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8171,10 +8189,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120204939</v>
+        <v>120204056</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>92030</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8183,42 +8201,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566566</v>
+        <v>566678</v>
       </c>
       <c r="R73" t="n">
-        <v>7041107</v>
+        <v>7041077</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8277,10 +8291,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120203004</v>
+        <v>120204153</v>
       </c>
       <c r="B74" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8289,25 +8303,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8317,10 +8331,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566624</v>
+        <v>566671</v>
       </c>
       <c r="R74" t="n">
-        <v>7041079</v>
+        <v>7041071</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8379,10 +8393,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120202289</v>
+        <v>120205192</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8395,34 +8409,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566546</v>
+        <v>566499</v>
       </c>
       <c r="R75" t="n">
-        <v>7041010</v>
+        <v>7041186</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8455,6 +8474,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8481,10 +8505,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120204116</v>
+        <v>120205221</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8493,38 +8517,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566691</v>
+        <v>566496</v>
       </c>
       <c r="R76" t="n">
-        <v>7041096</v>
+        <v>7041192</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8557,6 +8586,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8583,10 +8617,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120205460</v>
+        <v>120204807</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8595,43 +8629,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566500</v>
+        <v>566575</v>
       </c>
       <c r="R77" t="n">
-        <v>7041094</v>
+        <v>7041141</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8664,11 +8693,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8695,10 +8719,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120202297</v>
+        <v>120202786</v>
       </c>
       <c r="B78" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8707,25 +8731,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8735,10 +8759,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566551</v>
+        <v>566623</v>
       </c>
       <c r="R78" t="n">
-        <v>7040999</v>
+        <v>7041032</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8797,10 +8821,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120204205</v>
+        <v>120202642</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8813,21 +8837,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8837,10 +8861,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566711</v>
+        <v>566590</v>
       </c>
       <c r="R79" t="n">
-        <v>7041082</v>
+        <v>7041023</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8899,10 +8923,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120200809</v>
+        <v>120203004</v>
       </c>
       <c r="B80" t="n">
-        <v>56514</v>
+        <v>90562</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8915,42 +8939,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566509</v>
+        <v>566624</v>
       </c>
       <c r="R80" t="n">
-        <v>7041308</v>
+        <v>7041079</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8977,19 +8996,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9004,22 +9013,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120202727</v>
+        <v>120204835</v>
       </c>
       <c r="B81" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9028,25 +9037,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9056,10 +9065,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566577</v>
+        <v>566561</v>
       </c>
       <c r="R81" t="n">
-        <v>7041064</v>
+        <v>7041134</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9118,10 +9127,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120205312</v>
+        <v>120204476</v>
       </c>
       <c r="B82" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9130,50 +9139,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566618</v>
+        <v>566635</v>
       </c>
       <c r="R82" t="n">
-        <v>7040939</v>
+        <v>7041139</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9200,19 +9200,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9227,22 +9217,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120204816</v>
+        <v>120202853</v>
       </c>
       <c r="B83" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9255,21 +9245,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9279,10 +9269,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566572</v>
+        <v>566624</v>
       </c>
       <c r="R83" t="n">
-        <v>7041139</v>
+        <v>7041060</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9341,10 +9331,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120204958</v>
+        <v>120201451</v>
       </c>
       <c r="B84" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9357,21 +9347,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9381,13 +9371,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566564</v>
+        <v>566541</v>
       </c>
       <c r="R84" t="n">
-        <v>7041107</v>
+        <v>7040997</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9414,9 +9404,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9431,22 +9431,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120204056</v>
+        <v>120204358</v>
       </c>
       <c r="B85" t="n">
-        <v>92030</v>
+        <v>90562</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9459,21 +9459,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566678</v>
+        <v>566663</v>
       </c>
       <c r="R85" t="n">
-        <v>7041077</v>
+        <v>7041118</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9542,6 +9542,118 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120218923</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Dalsberget, Dalsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>566456</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7041061</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120205460</v>
+        <v>120204492</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,39 +1772,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566500</v>
+        <v>566608</v>
       </c>
       <c r="R12" t="n">
-        <v>7041094</v>
+        <v>7041149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1837,11 +1832,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204492</v>
+        <v>120201490</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,21 +1874,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,13 +1898,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566608</v>
+        <v>566563</v>
       </c>
       <c r="R13" t="n">
-        <v>7041149</v>
+        <v>7040951</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,9 +1931,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,22 +1958,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120201490</v>
+        <v>120205460</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,37 +1986,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566563</v>
+        <v>566500</v>
       </c>
       <c r="R14" t="n">
-        <v>7040951</v>
+        <v>7041094</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,19 +2048,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,12 +2070,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204945</v>
+        <v>120205398</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566565</v>
+        <v>566613</v>
       </c>
       <c r="R20" t="n">
-        <v>7041107</v>
+        <v>7040940</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,9 +2690,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,22 +2717,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120205398</v>
+        <v>120205323</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,21 +2745,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2759,13 +2769,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566613</v>
+        <v>566528</v>
       </c>
       <c r="R21" t="n">
-        <v>7040940</v>
+        <v>7041117</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2792,19 +2802,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2819,22 +2819,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120205323</v>
+        <v>120204945</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566528</v>
+        <v>566565</v>
       </c>
       <c r="R22" t="n">
-        <v>7041117</v>
+        <v>7041107</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120205468</v>
+        <v>120201661</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566498</v>
+        <v>566582</v>
       </c>
       <c r="R39" t="n">
-        <v>7041093</v>
+        <v>7040944</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4700,9 +4700,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4717,22 +4727,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120204104</v>
+        <v>120205468</v>
       </c>
       <c r="B40" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4745,21 +4755,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566694</v>
+        <v>566498</v>
       </c>
       <c r="R40" t="n">
-        <v>7041098</v>
+        <v>7041093</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4831,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120204980</v>
+        <v>120204104</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>78262</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4847,21 +4857,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4871,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566561</v>
+        <v>566694</v>
       </c>
       <c r="R41" t="n">
-        <v>7041107</v>
+        <v>7041098</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4933,10 +4943,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120201661</v>
+        <v>120205511</v>
       </c>
       <c r="B42" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4949,37 +4959,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566582</v>
+        <v>566509</v>
       </c>
       <c r="R42" t="n">
-        <v>7040944</v>
+        <v>7041097</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5006,19 +5021,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:21</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5033,22 +5043,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120205511</v>
+        <v>120204980</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,39 +5071,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566509</v>
+        <v>566561</v>
       </c>
       <c r="R43" t="n">
-        <v>7041097</v>
+        <v>7041107</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5126,11 +5131,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5998,10 +5998,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120204212</v>
+        <v>120203396</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,42 +6010,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566711</v>
+        <v>566638</v>
       </c>
       <c r="R52" t="n">
-        <v>7041082</v>
+        <v>7041075</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6316,10 +6312,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120203396</v>
+        <v>120204212</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6328,38 +6324,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566638</v>
+        <v>566711</v>
       </c>
       <c r="R55" t="n">
-        <v>7041075</v>
+        <v>7041082</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -9331,10 +9331,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120201451</v>
+        <v>120204358</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9347,21 +9347,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9371,13 +9371,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566541</v>
+        <v>566663</v>
       </c>
       <c r="R84" t="n">
-        <v>7040997</v>
+        <v>7041118</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9404,19 +9404,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9431,22 +9421,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120204358</v>
+        <v>120201451</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9459,21 +9449,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9483,13 +9473,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566663</v>
+        <v>566541</v>
       </c>
       <c r="R85" t="n">
-        <v>7041118</v>
+        <v>7040997</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9516,9 +9506,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9533,12 +9533,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204492</v>
+        <v>120205460</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,34 +1772,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566608</v>
+        <v>566500</v>
       </c>
       <c r="R12" t="n">
-        <v>7041149</v>
+        <v>7041094</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1832,6 +1837,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120201490</v>
+        <v>120204492</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,21 +1884,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,13 +1908,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566563</v>
+        <v>566608</v>
       </c>
       <c r="R13" t="n">
-        <v>7040951</v>
+        <v>7041149</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1931,19 +1941,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,22 +1958,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120205460</v>
+        <v>120201490</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,42 +1986,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566500</v>
+        <v>566563</v>
       </c>
       <c r="R14" t="n">
-        <v>7041094</v>
+        <v>7040951</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,14 +2043,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,12 +2070,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120205398</v>
+        <v>120204945</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566613</v>
+        <v>566565</v>
       </c>
       <c r="R20" t="n">
-        <v>7040940</v>
+        <v>7041107</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,19 +2690,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,22 +2707,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120205323</v>
+        <v>120205398</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,21 +2735,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,13 +2759,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566528</v>
+        <v>566613</v>
       </c>
       <c r="R21" t="n">
-        <v>7041117</v>
+        <v>7040940</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2802,9 +2792,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2819,22 +2819,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204945</v>
+        <v>120205323</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566565</v>
+        <v>566528</v>
       </c>
       <c r="R22" t="n">
-        <v>7041107</v>
+        <v>7041117</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120201983</v>
+        <v>120205084</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2945,31 +2945,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2978,13 +2977,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566636</v>
+        <v>566515</v>
       </c>
       <c r="R23" t="n">
-        <v>7040903</v>
+        <v>7041125</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3011,19 +3010,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,22 +3027,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120201767</v>
+        <v>120204901</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3066,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3090,13 +3079,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566610</v>
+        <v>566567</v>
       </c>
       <c r="R24" t="n">
-        <v>7040928</v>
+        <v>7041107</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3123,24 +3112,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,22 +3129,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120202239</v>
+        <v>120205024</v>
       </c>
       <c r="B25" t="n">
-        <v>90724</v>
+        <v>90527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3179,25 +3153,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3207,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566526</v>
+        <v>566549</v>
       </c>
       <c r="R25" t="n">
-        <v>7041005</v>
+        <v>7041126</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3269,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120205084</v>
+        <v>120201983</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3281,30 +3255,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3313,13 +3288,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566515</v>
+        <v>566636</v>
       </c>
       <c r="R26" t="n">
-        <v>7041125</v>
+        <v>7040903</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3346,9 +3321,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,22 +3348,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120204901</v>
+        <v>120201767</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,21 +3376,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3415,13 +3400,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566567</v>
+        <v>566610</v>
       </c>
       <c r="R27" t="n">
-        <v>7041107</v>
+        <v>7040928</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3448,9 +3433,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3465,22 +3465,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120205024</v>
+        <v>120202239</v>
       </c>
       <c r="B28" t="n">
-        <v>90527</v>
+        <v>90724</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3489,25 +3489,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566549</v>
+        <v>566526</v>
       </c>
       <c r="R28" t="n">
-        <v>7041126</v>
+        <v>7041005</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4109,10 +4109,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120204862</v>
+        <v>120202755</v>
       </c>
       <c r="B34" t="n">
-        <v>90527</v>
+        <v>91005</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4121,25 +4121,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566579</v>
+        <v>566572</v>
       </c>
       <c r="R34" t="n">
-        <v>7041130</v>
+        <v>7041055</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120205278</v>
+        <v>120202647</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566528</v>
+        <v>566587</v>
       </c>
       <c r="R35" t="n">
-        <v>7041117</v>
+        <v>7041021</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120202755</v>
+        <v>120204862</v>
       </c>
       <c r="B36" t="n">
-        <v>91005</v>
+        <v>90527</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4329,25 +4329,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566572</v>
+        <v>566579</v>
       </c>
       <c r="R36" t="n">
-        <v>7041055</v>
+        <v>7041130</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4419,7 +4419,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120202647</v>
+        <v>120205278</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566587</v>
+        <v>566528</v>
       </c>
       <c r="R37" t="n">
-        <v>7041021</v>
+        <v>7041117</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120203396</v>
+        <v>120204212</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,38 +6010,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566638</v>
+        <v>566711</v>
       </c>
       <c r="R52" t="n">
-        <v>7041075</v>
+        <v>7041082</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6312,10 +6316,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120204212</v>
+        <v>120203396</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6324,42 +6328,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566711</v>
+        <v>566638</v>
       </c>
       <c r="R55" t="n">
-        <v>7041082</v>
+        <v>7041075</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -9331,10 +9331,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120204358</v>
+        <v>120201451</v>
       </c>
       <c r="B84" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9347,21 +9347,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9371,13 +9371,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566663</v>
+        <v>566541</v>
       </c>
       <c r="R84" t="n">
-        <v>7041118</v>
+        <v>7040997</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9404,9 +9404,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9421,22 +9431,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120201451</v>
+        <v>120204358</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9449,21 +9459,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9473,13 +9483,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566541</v>
+        <v>566663</v>
       </c>
       <c r="R85" t="n">
-        <v>7040997</v>
+        <v>7041118</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9506,19 +9516,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9533,12 +9533,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120205312</v>
+        <v>120200832</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566618</v>
+        <v>566507</v>
       </c>
       <c r="R2" t="n">
-        <v>7040939</v>
+        <v>7041231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120203078</v>
+        <v>120205312</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +804,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566621</v>
+        <v>566618</v>
       </c>
       <c r="R3" t="n">
-        <v>7041057</v>
+        <v>7040939</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,9 +874,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120200832</v>
+        <v>120203078</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,42 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566507</v>
+        <v>566621</v>
       </c>
       <c r="R4" t="n">
-        <v>7041231</v>
+        <v>7041057</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +986,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,12 +1003,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120201661</v>
+        <v>120205468</v>
       </c>
       <c r="B39" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566582</v>
+        <v>566498</v>
       </c>
       <c r="R39" t="n">
-        <v>7040944</v>
+        <v>7041093</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4700,19 +4700,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4727,22 +4717,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120205468</v>
+        <v>120204104</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,21 +4745,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4779,10 +4769,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566498</v>
+        <v>566694</v>
       </c>
       <c r="R40" t="n">
-        <v>7041093</v>
+        <v>7041098</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4841,10 +4831,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120204104</v>
+        <v>120204980</v>
       </c>
       <c r="B41" t="n">
-        <v>78262</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,21 +4847,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4881,10 +4871,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566694</v>
+        <v>566561</v>
       </c>
       <c r="R41" t="n">
-        <v>7041098</v>
+        <v>7041107</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4943,10 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120205511</v>
+        <v>120201661</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,42 +4949,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566509</v>
+        <v>566582</v>
       </c>
       <c r="R42" t="n">
-        <v>7041097</v>
+        <v>7040944</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5021,14 +5006,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5043,22 +5033,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120204980</v>
+        <v>120205511</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5071,34 +5061,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566561</v>
+        <v>566509</v>
       </c>
       <c r="R43" t="n">
-        <v>7041107</v>
+        <v>7041097</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5131,6 +5126,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5157,7 +5157,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120204816</v>
+        <v>120202297</v>
       </c>
       <c r="B44" t="n">
         <v>90562</v>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566572</v>
+        <v>566551</v>
       </c>
       <c r="R44" t="n">
-        <v>7041139</v>
+        <v>7040999</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5259,10 +5259,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120202622</v>
+        <v>120200809</v>
       </c>
       <c r="B45" t="n">
-        <v>90527</v>
+        <v>56514</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5271,41 +5271,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566590</v>
+        <v>566509</v>
       </c>
       <c r="R45" t="n">
-        <v>7041027</v>
+        <v>7041308</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5332,9 +5337,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5349,22 +5364,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120200809</v>
+        <v>120205148</v>
       </c>
       <c r="B46" t="n">
-        <v>56514</v>
+        <v>79636</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5373,46 +5388,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566509</v>
+        <v>566529</v>
       </c>
       <c r="R46" t="n">
-        <v>7041308</v>
+        <v>7041203</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5439,19 +5449,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,22 +5466,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120205148</v>
+        <v>120204816</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,25 +5490,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566529</v>
+        <v>566572</v>
       </c>
       <c r="R47" t="n">
-        <v>7041203</v>
+        <v>7041139</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120202297</v>
+        <v>120202622</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566551</v>
+        <v>566590</v>
       </c>
       <c r="R48" t="n">
-        <v>7040999</v>
+        <v>7041027</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120205154</v>
+        <v>120203571</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>89633</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6867,42 +6867,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566510</v>
+        <v>566647</v>
       </c>
       <c r="R60" t="n">
-        <v>7041190</v>
+        <v>7041053</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7063,10 +7059,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120203571</v>
+        <v>120205154</v>
       </c>
       <c r="B62" t="n">
-        <v>89633</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7075,38 +7071,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566647</v>
+        <v>566510</v>
       </c>
       <c r="R62" t="n">
-        <v>7041053</v>
+        <v>7041190</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120204503</v>
+        <v>120202697</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>90576</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7691,21 +7691,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566603</v>
+        <v>566589</v>
       </c>
       <c r="R68" t="n">
-        <v>7041138</v>
+        <v>7041075</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120204939</v>
+        <v>120202811</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7793,38 +7793,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566566</v>
+        <v>566616</v>
       </c>
       <c r="R69" t="n">
-        <v>7041107</v>
+        <v>7041049</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7883,10 +7879,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120202697</v>
+        <v>120204503</v>
       </c>
       <c r="B70" t="n">
-        <v>90576</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7899,21 +7895,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,10 +7919,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566589</v>
+        <v>566603</v>
       </c>
       <c r="R70" t="n">
-        <v>7041075</v>
+        <v>7041138</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7985,10 +7981,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120202811</v>
+        <v>120204939</v>
       </c>
       <c r="B71" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8001,34 +7997,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566616</v>
+        <v>566566</v>
       </c>
       <c r="R71" t="n">
-        <v>7041049</v>
+        <v>7041107</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120200832</v>
+        <v>120205312</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566507</v>
+        <v>566618</v>
       </c>
       <c r="R2" t="n">
-        <v>7041231</v>
+        <v>7040939</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120205312</v>
+        <v>120203078</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,50 +808,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566618</v>
+        <v>566621</v>
       </c>
       <c r="R3" t="n">
-        <v>7040939</v>
+        <v>7041057</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,19 +869,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120203078</v>
+        <v>120200832</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,37 +914,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566621</v>
+        <v>566507</v>
       </c>
       <c r="R4" t="n">
-        <v>7041057</v>
+        <v>7041231</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,9 +976,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204205</v>
+        <v>120205420</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,37 +1031,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566711</v>
+        <v>566583</v>
       </c>
       <c r="R5" t="n">
-        <v>7041082</v>
+        <v>7040942</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,9 +1097,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1124,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120204116</v>
+        <v>120204507</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566691</v>
+        <v>566602</v>
       </c>
       <c r="R6" t="n">
-        <v>7041096</v>
+        <v>7041134</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1219,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204507</v>
+        <v>120204797</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>96862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1250,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566602</v>
+        <v>566572</v>
       </c>
       <c r="R7" t="n">
-        <v>7041134</v>
+        <v>7041137</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1321,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204797</v>
+        <v>120203123</v>
       </c>
       <c r="B8" t="n">
-        <v>96862</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,38 +1352,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566572</v>
+        <v>566628</v>
       </c>
       <c r="R8" t="n">
-        <v>7041137</v>
+        <v>7041063</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1423,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203123</v>
+        <v>120204205</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,42 +1458,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566628</v>
+        <v>566711</v>
       </c>
       <c r="R9" t="n">
-        <v>7041063</v>
+        <v>7041082</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1529,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120205420</v>
+        <v>120204116</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,50 +1560,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566583</v>
+        <v>566691</v>
       </c>
       <c r="R10" t="n">
-        <v>7040942</v>
+        <v>7041096</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,19 +1621,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,12 +1638,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120205460</v>
+        <v>120204492</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,39 +1772,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566500</v>
+        <v>566608</v>
       </c>
       <c r="R12" t="n">
-        <v>7041094</v>
+        <v>7041149</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1837,11 +1832,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204492</v>
+        <v>120201490</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,21 +1874,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,13 +1898,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566608</v>
+        <v>566563</v>
       </c>
       <c r="R13" t="n">
-        <v>7041149</v>
+        <v>7040951</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,9 +1931,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,22 +1958,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120201490</v>
+        <v>120205460</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,37 +1986,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566563</v>
+        <v>566500</v>
       </c>
       <c r="R14" t="n">
-        <v>7040951</v>
+        <v>7041094</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,19 +2048,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,12 +2070,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120201350</v>
+        <v>120205199</v>
       </c>
       <c r="B29" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,37 +3595,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566534</v>
+        <v>566499</v>
       </c>
       <c r="R29" t="n">
-        <v>7040990</v>
+        <v>7041189</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3652,19 +3657,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:10</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3679,22 +3679,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120205199</v>
+        <v>120205138</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,39 +3707,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566499</v>
+        <v>566529</v>
       </c>
       <c r="R30" t="n">
-        <v>7041189</v>
+        <v>7041203</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3772,11 +3767,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120205138</v>
+        <v>120201350</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3819,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,13 +3833,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566529</v>
+        <v>566534</v>
       </c>
       <c r="R31" t="n">
-        <v>7041203</v>
+        <v>7040990</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3876,9 +3866,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,12 +3893,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120202297</v>
+        <v>120204816</v>
       </c>
       <c r="B44" t="n">
         <v>90562</v>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566551</v>
+        <v>566572</v>
       </c>
       <c r="R44" t="n">
-        <v>7040999</v>
+        <v>7041139</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5259,10 +5259,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120200809</v>
+        <v>120202622</v>
       </c>
       <c r="B45" t="n">
-        <v>56514</v>
+        <v>90527</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5271,46 +5271,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566509</v>
+        <v>566590</v>
       </c>
       <c r="R45" t="n">
-        <v>7041308</v>
+        <v>7041027</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5337,19 +5332,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5364,22 +5349,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120205148</v>
+        <v>120200809</v>
       </c>
       <c r="B46" t="n">
-        <v>79636</v>
+        <v>56514</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5388,41 +5373,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566529</v>
+        <v>566509</v>
       </c>
       <c r="R46" t="n">
-        <v>7041203</v>
+        <v>7041308</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5449,9 +5439,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,22 +5466,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120204816</v>
+        <v>120205148</v>
       </c>
       <c r="B47" t="n">
-        <v>90562</v>
+        <v>79636</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,25 +5490,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566572</v>
+        <v>566529</v>
       </c>
       <c r="R47" t="n">
-        <v>7041139</v>
+        <v>7041203</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120202622</v>
+        <v>120202297</v>
       </c>
       <c r="B48" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566590</v>
+        <v>566551</v>
       </c>
       <c r="R48" t="n">
-        <v>7041027</v>
+        <v>7040999</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120204212</v>
+        <v>120203396</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,42 +6010,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566711</v>
+        <v>566638</v>
       </c>
       <c r="R52" t="n">
-        <v>7041082</v>
+        <v>7041075</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6316,10 +6312,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120203396</v>
+        <v>120204212</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6328,38 +6324,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566638</v>
+        <v>566711</v>
       </c>
       <c r="R55" t="n">
-        <v>7041075</v>
+        <v>7041082</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120203571</v>
+        <v>120205154</v>
       </c>
       <c r="B60" t="n">
-        <v>89633</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6867,38 +6867,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566647</v>
+        <v>566510</v>
       </c>
       <c r="R60" t="n">
-        <v>7041053</v>
+        <v>7041190</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7059,10 +7063,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120205154</v>
+        <v>120203571</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>89633</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7071,42 +7075,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566510</v>
+        <v>566647</v>
       </c>
       <c r="R62" t="n">
-        <v>7041190</v>
+        <v>7041053</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120202697</v>
+        <v>120204503</v>
       </c>
       <c r="B68" t="n">
-        <v>90576</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7691,21 +7691,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566589</v>
+        <v>566603</v>
       </c>
       <c r="R68" t="n">
-        <v>7041075</v>
+        <v>7041138</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120202811</v>
+        <v>120204939</v>
       </c>
       <c r="B69" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7793,34 +7793,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566616</v>
+        <v>566566</v>
       </c>
       <c r="R69" t="n">
-        <v>7041049</v>
+        <v>7041107</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7879,10 +7883,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120204503</v>
+        <v>120202697</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>90576</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7895,21 +7899,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7919,10 +7923,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566603</v>
+        <v>566589</v>
       </c>
       <c r="R70" t="n">
-        <v>7041138</v>
+        <v>7041075</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7981,10 +7985,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120204939</v>
+        <v>120202811</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7997,38 +8001,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566566</v>
+        <v>566616</v>
       </c>
       <c r="R71" t="n">
-        <v>7041107</v>
+        <v>7041049</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9331,10 +9331,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120201451</v>
+        <v>120204358</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9347,21 +9347,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9371,13 +9371,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566541</v>
+        <v>566663</v>
       </c>
       <c r="R84" t="n">
-        <v>7040997</v>
+        <v>7041118</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9404,19 +9404,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9431,22 +9421,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120204358</v>
+        <v>120201451</v>
       </c>
       <c r="B85" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9459,21 +9449,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9483,13 +9473,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566663</v>
+        <v>566541</v>
       </c>
       <c r="R85" t="n">
-        <v>7041118</v>
+        <v>7040997</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9516,9 +9506,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9533,12 +9533,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120205312</v>
+        <v>120200832</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566618</v>
+        <v>566507</v>
       </c>
       <c r="R2" t="n">
-        <v>7040939</v>
+        <v>7041231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120203078</v>
+        <v>120205312</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +804,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566621</v>
+        <v>566618</v>
       </c>
       <c r="R3" t="n">
-        <v>7041057</v>
+        <v>7040939</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,9 +874,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120200832</v>
+        <v>120203078</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,42 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566507</v>
+        <v>566621</v>
       </c>
       <c r="R4" t="n">
-        <v>7041231</v>
+        <v>7041057</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +986,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120205420</v>
+        <v>120204205</v>
       </c>
       <c r="B5" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,46 +1031,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566583</v>
+        <v>566711</v>
       </c>
       <c r="R5" t="n">
-        <v>7040942</v>
+        <v>7041082</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,19 +1088,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120204507</v>
+        <v>120204116</v>
       </c>
       <c r="B6" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,25 +1129,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566602</v>
+        <v>566691</v>
       </c>
       <c r="R6" t="n">
-        <v>7041134</v>
+        <v>7041096</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204797</v>
+        <v>120204507</v>
       </c>
       <c r="B7" t="n">
-        <v>96862</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566572</v>
+        <v>566602</v>
       </c>
       <c r="R7" t="n">
-        <v>7041137</v>
+        <v>7041134</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1340,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120203123</v>
+        <v>120204797</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>96862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,42 +1333,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566628</v>
+        <v>566572</v>
       </c>
       <c r="R8" t="n">
-        <v>7041063</v>
+        <v>7041137</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1446,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204205</v>
+        <v>120203123</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,38 +1435,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566711</v>
+        <v>566628</v>
       </c>
       <c r="R9" t="n">
-        <v>7041082</v>
+        <v>7041063</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1548,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204116</v>
+        <v>120205420</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,41 +1541,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566691</v>
+        <v>566583</v>
       </c>
       <c r="R10" t="n">
-        <v>7041096</v>
+        <v>7040942</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,9 +1611,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,12 +1638,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204567</v>
+        <v>120202768</v>
       </c>
       <c r="B15" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,25 +2094,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566612</v>
+        <v>566600</v>
       </c>
       <c r="R15" t="n">
-        <v>7041175</v>
+        <v>7041007</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2184,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120205179</v>
+        <v>120204567</v>
       </c>
       <c r="B16" t="n">
         <v>90527</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566503</v>
+        <v>566612</v>
       </c>
       <c r="R16" t="n">
-        <v>7041183</v>
+        <v>7041175</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120200869</v>
+        <v>120205179</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,25 +2298,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566512</v>
+        <v>566503</v>
       </c>
       <c r="R17" t="n">
-        <v>7041220</v>
+        <v>7041183</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,19 +2359,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,22 +2376,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120200849</v>
+        <v>120200869</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,21 +2404,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2438,10 +2428,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566521</v>
+        <v>566512</v>
       </c>
       <c r="R18" t="n">
-        <v>7041283</v>
+        <v>7041220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,7 +2463,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2483,12 +2473,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,22 +2488,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120202768</v>
+        <v>120200849</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2531,21 +2516,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2555,13 +2540,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566600</v>
+        <v>566521</v>
       </c>
       <c r="R19" t="n">
-        <v>7041007</v>
+        <v>7041283</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,9 +2573,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,12 +2605,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120205468</v>
+        <v>120201661</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566498</v>
+        <v>566582</v>
       </c>
       <c r="R39" t="n">
-        <v>7041093</v>
+        <v>7040944</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4700,9 +4700,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4717,22 +4727,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120204104</v>
+        <v>120205468</v>
       </c>
       <c r="B40" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4745,21 +4755,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566694</v>
+        <v>566498</v>
       </c>
       <c r="R40" t="n">
-        <v>7041098</v>
+        <v>7041093</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4831,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120204980</v>
+        <v>120204104</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>78262</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4847,21 +4857,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4871,10 +4881,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566561</v>
+        <v>566694</v>
       </c>
       <c r="R41" t="n">
-        <v>7041107</v>
+        <v>7041098</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4933,10 +4943,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120201661</v>
+        <v>120205511</v>
       </c>
       <c r="B42" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4949,37 +4959,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566582</v>
+        <v>566509</v>
       </c>
       <c r="R42" t="n">
-        <v>7040944</v>
+        <v>7041097</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5006,19 +5021,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:21</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5033,22 +5043,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120205511</v>
+        <v>120204980</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,39 +5071,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566509</v>
+        <v>566561</v>
       </c>
       <c r="R43" t="n">
-        <v>7041097</v>
+        <v>7041107</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5126,11 +5131,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5998,10 +5998,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120203396</v>
+        <v>120204212</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,38 +6010,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566638</v>
+        <v>566711</v>
       </c>
       <c r="R52" t="n">
-        <v>7041075</v>
+        <v>7041082</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6312,10 +6316,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120204212</v>
+        <v>120203396</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6324,42 +6328,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566711</v>
+        <v>566638</v>
       </c>
       <c r="R55" t="n">
-        <v>7041082</v>
+        <v>7041075</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120204503</v>
+        <v>120202697</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>90576</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7691,21 +7691,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566603</v>
+        <v>566589</v>
       </c>
       <c r="R68" t="n">
-        <v>7041138</v>
+        <v>7041075</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120204939</v>
+        <v>120202811</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7793,38 +7793,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566566</v>
+        <v>566616</v>
       </c>
       <c r="R69" t="n">
-        <v>7041107</v>
+        <v>7041049</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7883,10 +7879,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120202697</v>
+        <v>120204503</v>
       </c>
       <c r="B70" t="n">
-        <v>90576</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7899,21 +7895,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,10 +7919,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566589</v>
+        <v>566603</v>
       </c>
       <c r="R70" t="n">
-        <v>7041075</v>
+        <v>7041138</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7985,10 +7981,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120202811</v>
+        <v>120204939</v>
       </c>
       <c r="B71" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8001,34 +7997,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566616</v>
+        <v>566566</v>
       </c>
       <c r="R71" t="n">
-        <v>7041049</v>
+        <v>7041107</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -2617,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204945</v>
+        <v>120205398</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566565</v>
+        <v>566613</v>
       </c>
       <c r="R20" t="n">
-        <v>7041107</v>
+        <v>7040940</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,9 +2690,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,22 +2717,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120205398</v>
+        <v>120205323</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,21 +2745,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2759,13 +2769,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566613</v>
+        <v>566528</v>
       </c>
       <c r="R21" t="n">
-        <v>7040940</v>
+        <v>7041117</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2792,19 +2802,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2819,22 +2819,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120205323</v>
+        <v>120204945</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566528</v>
+        <v>566565</v>
       </c>
       <c r="R22" t="n">
-        <v>7041117</v>
+        <v>7041107</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120204212</v>
+        <v>120203396</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,42 +6010,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566711</v>
+        <v>566638</v>
       </c>
       <c r="R52" t="n">
-        <v>7041082</v>
+        <v>7041075</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6316,10 +6312,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120203396</v>
+        <v>120204212</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6328,38 +6324,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566638</v>
+        <v>566711</v>
       </c>
       <c r="R55" t="n">
-        <v>7041075</v>
+        <v>7041082</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120200832</v>
+        <v>120202492</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566507</v>
+        <v>566568</v>
       </c>
       <c r="R2" t="n">
-        <v>7041231</v>
+        <v>7041045</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +752,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120205312</v>
+        <v>120203004</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,50 +793,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566618</v>
+        <v>566624</v>
       </c>
       <c r="R3" t="n">
-        <v>7040939</v>
+        <v>7041079</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,19 +854,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +871,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120203078</v>
+        <v>120205323</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566621</v>
+        <v>566528</v>
       </c>
       <c r="R4" t="n">
-        <v>7041057</v>
+        <v>7041117</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1015,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204205</v>
+        <v>120204980</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566711</v>
+        <v>566561</v>
       </c>
       <c r="R5" t="n">
-        <v>7041082</v>
+        <v>7041107</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1117,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120204116</v>
+        <v>120205064</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566691</v>
+        <v>566502</v>
       </c>
       <c r="R6" t="n">
-        <v>7041096</v>
+        <v>7041103</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1219,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204507</v>
+        <v>120204405</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566602</v>
+        <v>566637</v>
       </c>
       <c r="R7" t="n">
-        <v>7041134</v>
+        <v>7041131</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1321,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204797</v>
+        <v>120202289</v>
       </c>
       <c r="B8" t="n">
-        <v>96862</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1303,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566572</v>
+        <v>566546</v>
       </c>
       <c r="R8" t="n">
-        <v>7041137</v>
+        <v>7041010</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1423,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203123</v>
+        <v>120200869</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,45 +1405,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566628</v>
+        <v>566512</v>
       </c>
       <c r="R9" t="n">
-        <v>7041063</v>
+        <v>7041220</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,9 +1466,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,22 +1493,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120205420</v>
+        <v>120204945</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,29 +1538,20 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566583</v>
+        <v>566565</v>
       </c>
       <c r="R10" t="n">
-        <v>7040942</v>
+        <v>7041107</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,19 +1578,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,22 +1595,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202492</v>
+        <v>120201490</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,45 +1619,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566568</v>
+        <v>566563</v>
       </c>
       <c r="R11" t="n">
-        <v>7041045</v>
+        <v>7040951</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,9 +1680,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,22 +1707,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204492</v>
+        <v>120205199</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,34 +1735,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566608</v>
+        <v>566499</v>
       </c>
       <c r="R12" t="n">
-        <v>7041149</v>
+        <v>7041189</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1832,6 +1800,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120201490</v>
+        <v>120201231</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566563</v>
+        <v>566502</v>
       </c>
       <c r="R13" t="n">
-        <v>7040951</v>
+        <v>7041017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,7 +1906,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1943,7 +1916,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120205460</v>
+        <v>120204212</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,31 +1960,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2015,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566500</v>
+        <v>566711</v>
       </c>
       <c r="R14" t="n">
-        <v>7041094</v>
+        <v>7041082</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2051,11 +2028,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120202768</v>
+        <v>120202824</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2122,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566600</v>
+        <v>566616</v>
       </c>
       <c r="R15" t="n">
-        <v>7041007</v>
+        <v>7041049</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2184,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204567</v>
+        <v>120203937</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,25 +2168,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2224,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566612</v>
+        <v>566660</v>
       </c>
       <c r="R16" t="n">
-        <v>7041175</v>
+        <v>7041078</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2286,10 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120205179</v>
+        <v>120202571</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,38 +2270,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566503</v>
+        <v>566582</v>
       </c>
       <c r="R17" t="n">
-        <v>7041183</v>
+        <v>7041015</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2388,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120200869</v>
+        <v>120202239</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>90742</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,21 +2380,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2428,13 +2404,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566512</v>
+        <v>566526</v>
       </c>
       <c r="R18" t="n">
-        <v>7041220</v>
+        <v>7041005</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2461,19 +2437,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,22 +2454,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120200849</v>
+        <v>120205024</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2512,25 +2478,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2540,13 +2506,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566521</v>
+        <v>566549</v>
       </c>
       <c r="R19" t="n">
-        <v>7041283</v>
+        <v>7041126</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2573,24 +2539,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,22 +2556,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120205398</v>
+        <v>120204013</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,21 +2584,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2657,13 +2608,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566613</v>
+        <v>566666</v>
       </c>
       <c r="R20" t="n">
-        <v>7040940</v>
+        <v>7041066</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,19 +2641,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,22 +2658,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120205323</v>
+        <v>120204267</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,25 +2682,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566528</v>
+        <v>566695</v>
       </c>
       <c r="R21" t="n">
-        <v>7041117</v>
+        <v>7041080</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2831,10 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204945</v>
+        <v>120204476</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2788,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2871,10 +2812,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566565</v>
+        <v>566635</v>
       </c>
       <c r="R22" t="n">
-        <v>7041107</v>
+        <v>7041139</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2933,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120205084</v>
+        <v>120204104</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2945,42 +2886,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566515</v>
+        <v>566694</v>
       </c>
       <c r="R23" t="n">
-        <v>7041125</v>
+        <v>7041098</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3039,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120204901</v>
+        <v>120202697</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,21 +2992,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3016,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566567</v>
+        <v>566589</v>
       </c>
       <c r="R24" t="n">
-        <v>7041107</v>
+        <v>7041075</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3141,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120205024</v>
+        <v>120202811</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>90923</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,25 +3090,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566549</v>
+        <v>566616</v>
       </c>
       <c r="R25" t="n">
-        <v>7041126</v>
+        <v>7041049</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3243,10 +3180,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120201983</v>
+        <v>120204153</v>
       </c>
       <c r="B26" t="n">
-        <v>57463</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3255,46 +3192,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566636</v>
+        <v>566671</v>
       </c>
       <c r="R26" t="n">
-        <v>7040903</v>
+        <v>7041071</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3321,19 +3253,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,22 +3270,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120201767</v>
+        <v>120204116</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,25 +3294,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,13 +3322,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566610</v>
+        <v>566691</v>
       </c>
       <c r="R27" t="n">
-        <v>7040928</v>
+        <v>7041096</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3433,24 +3355,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3465,22 +3372,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120202239</v>
+        <v>120201767</v>
       </c>
       <c r="B28" t="n">
-        <v>90724</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3493,21 +3400,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3424,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566526</v>
+        <v>566610</v>
       </c>
       <c r="R28" t="n">
-        <v>7041005</v>
+        <v>7040928</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3550,9 +3457,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,22 +3489,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120205199</v>
+        <v>120205221</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3624,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566499</v>
+        <v>566496</v>
       </c>
       <c r="R29" t="n">
-        <v>7041189</v>
+        <v>7041192</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3691,10 +3613,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120205138</v>
+        <v>120204503</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>78279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,21 +3629,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,10 +3653,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566529</v>
+        <v>566603</v>
       </c>
       <c r="R30" t="n">
-        <v>7041203</v>
+        <v>7041138</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3793,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120201350</v>
+        <v>120204205</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3809,21 +3731,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3833,13 +3755,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566534</v>
+        <v>566711</v>
       </c>
       <c r="R31" t="n">
-        <v>7040990</v>
+        <v>7041082</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3866,19 +3788,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,22 +3805,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202733</v>
+        <v>120205398</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3921,21 +3833,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3945,13 +3857,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566567</v>
+        <v>566613</v>
       </c>
       <c r="R32" t="n">
-        <v>7041052</v>
+        <v>7040940</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3978,9 +3890,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,22 +3917,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120202674</v>
+        <v>120202768</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>90864</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4023,21 +3945,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +3969,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566584</v>
+        <v>566600</v>
       </c>
       <c r="R33" t="n">
-        <v>7041103</v>
+        <v>7041007</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4109,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120202755</v>
+        <v>120202727</v>
       </c>
       <c r="B34" t="n">
-        <v>91005</v>
+        <v>90864</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4121,25 +4043,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4149,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566572</v>
+        <v>566577</v>
       </c>
       <c r="R34" t="n">
-        <v>7041055</v>
+        <v>7041064</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4211,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120202647</v>
+        <v>120202553</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4246,7 +4168,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4255,10 +4177,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566587</v>
+        <v>566578</v>
       </c>
       <c r="R35" t="n">
-        <v>7041021</v>
+        <v>7040998</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4317,10 +4239,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120204862</v>
+        <v>120205179</v>
       </c>
       <c r="B36" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4357,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566579</v>
+        <v>566503</v>
       </c>
       <c r="R36" t="n">
-        <v>7041130</v>
+        <v>7041183</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4419,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120205278</v>
+        <v>120205084</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4454,7 +4376,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4463,10 +4385,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566528</v>
+        <v>566515</v>
       </c>
       <c r="R37" t="n">
-        <v>7041117</v>
+        <v>7041125</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4525,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120202727</v>
+        <v>120202642</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>74654</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4541,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4565,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566577</v>
+        <v>566590</v>
       </c>
       <c r="R38" t="n">
-        <v>7041064</v>
+        <v>7041023</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4627,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120201661</v>
+        <v>120202853</v>
       </c>
       <c r="B39" t="n">
-        <v>90846</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4643,21 +4565,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,13 +4589,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566582</v>
+        <v>566624</v>
       </c>
       <c r="R39" t="n">
-        <v>7040944</v>
+        <v>7041060</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4700,19 +4622,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4727,22 +4639,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120205468</v>
+        <v>120204939</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4751,38 +4663,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566498</v>
+        <v>566566</v>
       </c>
       <c r="R40" t="n">
-        <v>7041093</v>
+        <v>7041107</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4841,10 +4757,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120204104</v>
+        <v>120205511</v>
       </c>
       <c r="B41" t="n">
-        <v>78262</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,34 +4773,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566694</v>
+        <v>566509</v>
       </c>
       <c r="R41" t="n">
-        <v>7041098</v>
+        <v>7041097</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4917,6 +4838,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4943,10 +4869,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120205511</v>
+        <v>120204797</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>96885</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4955,43 +4881,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566509</v>
+        <v>566572</v>
       </c>
       <c r="R42" t="n">
-        <v>7041097</v>
+        <v>7041137</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5024,11 +4945,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5055,7 +4971,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120204980</v>
+        <v>120202674</v>
       </c>
       <c r="B43" t="n">
         <v>90580</v>
@@ -5071,21 +4987,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5095,10 +5011,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566561</v>
+        <v>566584</v>
       </c>
       <c r="R43" t="n">
-        <v>7041107</v>
+        <v>7041103</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5157,10 +5073,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120204816</v>
+        <v>120202755</v>
       </c>
       <c r="B44" t="n">
-        <v>90562</v>
+        <v>91023</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5169,25 +5085,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5200,7 +5116,7 @@
         <v>566572</v>
       </c>
       <c r="R44" t="n">
-        <v>7041139</v>
+        <v>7041055</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5259,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120202622</v>
+        <v>120203571</v>
       </c>
       <c r="B45" t="n">
-        <v>90527</v>
+        <v>89650</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5271,25 +5187,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5299,10 +5215,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566590</v>
+        <v>566647</v>
       </c>
       <c r="R45" t="n">
-        <v>7041027</v>
+        <v>7041053</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5361,10 +5277,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120200809</v>
+        <v>120204056</v>
       </c>
       <c r="B46" t="n">
-        <v>56514</v>
+        <v>92048</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5377,42 +5293,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566509</v>
+        <v>566678</v>
       </c>
       <c r="R46" t="n">
-        <v>7041308</v>
+        <v>7041077</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5439,19 +5350,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,22 +5367,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120205148</v>
+        <v>120205460</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,38 +5391,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566529</v>
+        <v>566500</v>
       </c>
       <c r="R47" t="n">
-        <v>7041203</v>
+        <v>7041094</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5554,6 +5460,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5580,10 +5491,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120202297</v>
+        <v>120205278</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5592,38 +5503,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566551</v>
+        <v>566528</v>
       </c>
       <c r="R48" t="n">
-        <v>7040999</v>
+        <v>7041117</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5682,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120203937</v>
+        <v>120204492</v>
       </c>
       <c r="B49" t="n">
-        <v>90846</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5698,21 +5613,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5722,10 +5637,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566660</v>
+        <v>566608</v>
       </c>
       <c r="R49" t="n">
-        <v>7041078</v>
+        <v>7041149</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5784,10 +5699,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120204958</v>
+        <v>120204507</v>
       </c>
       <c r="B50" t="n">
-        <v>90562</v>
+        <v>79160</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5800,21 +5715,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5824,10 +5739,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566564</v>
+        <v>566602</v>
       </c>
       <c r="R50" t="n">
-        <v>7041107</v>
+        <v>7041134</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5886,10 +5801,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120201620</v>
+        <v>120204958</v>
       </c>
       <c r="B51" t="n">
-        <v>91005</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5898,25 +5813,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5926,13 +5841,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566582</v>
+        <v>566564</v>
       </c>
       <c r="R51" t="n">
-        <v>7040944</v>
+        <v>7041107</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5959,19 +5874,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5986,22 +5891,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120203396</v>
+        <v>120201451</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6010,25 +5915,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6038,13 +5943,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566638</v>
+        <v>566541</v>
       </c>
       <c r="R52" t="n">
-        <v>7041075</v>
+        <v>7040997</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6071,9 +5976,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6088,22 +6003,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120202571</v>
+        <v>120202733</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6112,42 +6027,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566582</v>
+        <v>566567</v>
       </c>
       <c r="R53" t="n">
-        <v>7041015</v>
+        <v>7041052</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6206,10 +6117,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120202392</v>
+        <v>120202647</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6241,7 +6152,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6250,10 +6161,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566555</v>
+        <v>566587</v>
       </c>
       <c r="R54" t="n">
-        <v>7041027</v>
+        <v>7041021</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6312,10 +6223,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120204212</v>
+        <v>120204358</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6324,42 +6235,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566711</v>
+        <v>566663</v>
       </c>
       <c r="R55" t="n">
-        <v>7041082</v>
+        <v>7041118</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6418,10 +6325,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120201231</v>
+        <v>120204567</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6430,25 +6337,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6458,13 +6365,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566502</v>
+        <v>566612</v>
       </c>
       <c r="R56" t="n">
-        <v>7041017</v>
+        <v>7041175</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6491,24 +6398,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6523,22 +6415,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120205368</v>
+        <v>120202622</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6547,43 +6439,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566521</v>
+        <v>566590</v>
       </c>
       <c r="R57" t="n">
-        <v>7041138</v>
+        <v>7041027</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6616,11 +6503,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6647,10 +6529,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120202867</v>
+        <v>120205138</v>
       </c>
       <c r="B58" t="n">
-        <v>90527</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6659,25 +6541,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6687,10 +6569,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566626</v>
+        <v>566529</v>
       </c>
       <c r="R58" t="n">
-        <v>7041042</v>
+        <v>7041203</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6749,10 +6631,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120202553</v>
+        <v>120205468</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6761,42 +6643,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566578</v>
+        <v>566498</v>
       </c>
       <c r="R59" t="n">
-        <v>7040998</v>
+        <v>7041093</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6855,10 +6733,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120205154</v>
+        <v>120200832</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6867,30 +6745,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6899,13 +6778,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566510</v>
+        <v>566507</v>
       </c>
       <c r="R60" t="n">
-        <v>7041190</v>
+        <v>7041231</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6932,9 +6811,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6949,22 +6838,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120202824</v>
+        <v>120200849</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6977,21 +6866,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7001,13 +6890,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566616</v>
+        <v>566521</v>
       </c>
       <c r="R61" t="n">
-        <v>7041049</v>
+        <v>7041283</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7034,9 +6923,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7051,22 +6955,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120203571</v>
+        <v>120201983</v>
       </c>
       <c r="B62" t="n">
-        <v>89633</v>
+        <v>57473</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7079,37 +6983,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566647</v>
+        <v>566636</v>
       </c>
       <c r="R62" t="n">
-        <v>7041053</v>
+        <v>7040903</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7136,9 +7045,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7153,22 +7072,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120204267</v>
+        <v>120204807</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>90545</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7181,21 +7100,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7205,10 +7124,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566695</v>
+        <v>566575</v>
       </c>
       <c r="R63" t="n">
-        <v>7041080</v>
+        <v>7041141</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7267,10 +7186,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120204013</v>
+        <v>120202867</v>
       </c>
       <c r="B64" t="n">
-        <v>78262</v>
+        <v>90545</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7279,25 +7198,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7307,10 +7226,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566666</v>
+        <v>566626</v>
       </c>
       <c r="R64" t="n">
-        <v>7041066</v>
+        <v>7041042</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7369,10 +7288,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120205064</v>
+        <v>120203396</v>
       </c>
       <c r="B65" t="n">
-        <v>90527</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7385,21 +7304,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7409,10 +7328,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566502</v>
+        <v>566638</v>
       </c>
       <c r="R65" t="n">
-        <v>7041103</v>
+        <v>7041075</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7471,10 +7390,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120203962</v>
+        <v>120200809</v>
       </c>
       <c r="B66" t="n">
-        <v>79144</v>
+        <v>56524</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7487,37 +7406,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566665</v>
+        <v>566509</v>
       </c>
       <c r="R66" t="n">
-        <v>7041086</v>
+        <v>7041308</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7544,9 +7468,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7561,22 +7495,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120204405</v>
+        <v>120205154</v>
       </c>
       <c r="B67" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7585,38 +7519,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566637</v>
+        <v>566510</v>
       </c>
       <c r="R67" t="n">
-        <v>7041131</v>
+        <v>7041190</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7675,10 +7613,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120202697</v>
+        <v>120202786</v>
       </c>
       <c r="B68" t="n">
-        <v>90576</v>
+        <v>91023</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7687,25 +7625,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7715,10 +7653,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566589</v>
+        <v>566623</v>
       </c>
       <c r="R68" t="n">
-        <v>7041075</v>
+        <v>7041032</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7777,10 +7715,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120202811</v>
+        <v>120205420</v>
       </c>
       <c r="B69" t="n">
-        <v>90905</v>
+        <v>90864</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7789,41 +7727,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566616</v>
+        <v>566583</v>
       </c>
       <c r="R69" t="n">
-        <v>7041049</v>
+        <v>7040942</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7850,9 +7797,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7867,22 +7824,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120204503</v>
+        <v>120203962</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>79160</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7895,21 +7852,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7919,10 +7876,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566603</v>
+        <v>566665</v>
       </c>
       <c r="R70" t="n">
-        <v>7041138</v>
+        <v>7041086</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7981,10 +7938,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120204939</v>
+        <v>120203123</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8016,7 +7973,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8025,10 +7982,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566566</v>
+        <v>566628</v>
       </c>
       <c r="R71" t="n">
-        <v>7041107</v>
+        <v>7041063</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8087,10 +8044,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120202289</v>
+        <v>120205312</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8099,41 +8056,50 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566546</v>
+        <v>566618</v>
       </c>
       <c r="R72" t="n">
-        <v>7041010</v>
+        <v>7040939</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8160,9 +8126,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8177,22 +8153,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120204056</v>
+        <v>120202297</v>
       </c>
       <c r="B73" t="n">
-        <v>92030</v>
+        <v>90580</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8205,21 +8181,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8229,10 +8205,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566678</v>
+        <v>566551</v>
       </c>
       <c r="R73" t="n">
-        <v>7041077</v>
+        <v>7040999</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8291,10 +8267,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120204153</v>
+        <v>120205192</v>
       </c>
       <c r="B74" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8303,38 +8279,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566671</v>
+        <v>566499</v>
       </c>
       <c r="R74" t="n">
-        <v>7041071</v>
+        <v>7041186</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8367,6 +8348,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8393,10 +8379,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120205192</v>
+        <v>120201661</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>90864</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8409,42 +8395,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566499</v>
+        <v>566582</v>
       </c>
       <c r="R75" t="n">
-        <v>7041186</v>
+        <v>7040944</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8471,14 +8452,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8493,22 +8479,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120205221</v>
+        <v>120201350</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8521,42 +8507,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566496</v>
+        <v>566534</v>
       </c>
       <c r="R76" t="n">
-        <v>7041192</v>
+        <v>7040990</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8583,14 +8564,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8605,22 +8591,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120204807</v>
+        <v>120204862</v>
       </c>
       <c r="B77" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8657,10 +8643,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566575</v>
+        <v>566579</v>
       </c>
       <c r="R77" t="n">
-        <v>7041141</v>
+        <v>7041130</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8719,10 +8705,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120202786</v>
+        <v>120205148</v>
       </c>
       <c r="B78" t="n">
-        <v>91005</v>
+        <v>79652</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8731,25 +8717,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8759,10 +8745,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566623</v>
+        <v>566529</v>
       </c>
       <c r="R78" t="n">
-        <v>7041032</v>
+        <v>7041203</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8821,10 +8807,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120202642</v>
+        <v>120203078</v>
       </c>
       <c r="B79" t="n">
-        <v>74638</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8837,21 +8823,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8861,10 +8847,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566590</v>
+        <v>566621</v>
       </c>
       <c r="R79" t="n">
-        <v>7041023</v>
+        <v>7041057</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8923,10 +8909,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120203004</v>
+        <v>120204816</v>
       </c>
       <c r="B80" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8963,10 +8949,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566624</v>
+        <v>566572</v>
       </c>
       <c r="R80" t="n">
-        <v>7041079</v>
+        <v>7041139</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9025,10 +9011,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120204835</v>
+        <v>120201620</v>
       </c>
       <c r="B81" t="n">
-        <v>90527</v>
+        <v>91023</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9037,25 +9023,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9065,13 +9051,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566561</v>
+        <v>566582</v>
       </c>
       <c r="R81" t="n">
-        <v>7041134</v>
+        <v>7040944</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9098,9 +9084,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9115,22 +9111,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120204476</v>
+        <v>120204835</v>
       </c>
       <c r="B82" t="n">
-        <v>78262</v>
+        <v>90545</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9139,25 +9135,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9167,10 +9163,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566635</v>
+        <v>566561</v>
       </c>
       <c r="R82" t="n">
-        <v>7041139</v>
+        <v>7041134</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9229,10 +9225,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120202853</v>
+        <v>120204901</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>90598</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9245,21 +9241,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9269,10 +9265,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566624</v>
+        <v>566567</v>
       </c>
       <c r="R83" t="n">
-        <v>7041060</v>
+        <v>7041107</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9331,10 +9327,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120204358</v>
+        <v>120202392</v>
       </c>
       <c r="B84" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9343,38 +9339,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566663</v>
+        <v>566555</v>
       </c>
       <c r="R84" t="n">
-        <v>7041118</v>
+        <v>7041027</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9433,10 +9433,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120201451</v>
+        <v>120205368</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9449,37 +9449,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566541</v>
+        <v>566521</v>
       </c>
       <c r="R85" t="n">
-        <v>7040997</v>
+        <v>7041138</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9506,19 +9511,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:13</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9533,12 +9533,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9548,7 +9548,7 @@
         <v>120218923</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204945</v>
+        <v>120201490</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566565</v>
+        <v>566563</v>
       </c>
       <c r="R10" t="n">
-        <v>7041107</v>
+        <v>7040951</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1578,9 +1578,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,22 +1605,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120201490</v>
+        <v>120204945</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1633,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,13 +1657,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566563</v>
+        <v>566565</v>
       </c>
       <c r="R11" t="n">
-        <v>7040951</v>
+        <v>7041107</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,19 +1690,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,12 +1707,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120205024</v>
+        <v>120204267</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,21 +2482,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566549</v>
+        <v>566695</v>
       </c>
       <c r="R19" t="n">
-        <v>7041126</v>
+        <v>7041080</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204013</v>
+        <v>120205024</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,25 +2580,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566666</v>
+        <v>566549</v>
       </c>
       <c r="R20" t="n">
-        <v>7041066</v>
+        <v>7041126</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204267</v>
+        <v>120204013</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2682,25 +2682,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566695</v>
+        <v>566666</v>
       </c>
       <c r="R21" t="n">
-        <v>7041080</v>
+        <v>7041066</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120204104</v>
+        <v>120202697</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>90594</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566694</v>
+        <v>566589</v>
       </c>
       <c r="R23" t="n">
-        <v>7041098</v>
+        <v>7041075</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2976,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120202697</v>
+        <v>120202811</v>
       </c>
       <c r="B24" t="n">
-        <v>90594</v>
+        <v>90923</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2988,25 +2988,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566589</v>
+        <v>566616</v>
       </c>
       <c r="R24" t="n">
-        <v>7041075</v>
+        <v>7041049</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120202811</v>
+        <v>120204153</v>
       </c>
       <c r="B25" t="n">
-        <v>90923</v>
+        <v>90545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,25 +3090,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566616</v>
+        <v>566671</v>
       </c>
       <c r="R25" t="n">
-        <v>7041049</v>
+        <v>7041071</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120204153</v>
+        <v>120204104</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3192,25 +3192,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566671</v>
+        <v>566694</v>
       </c>
       <c r="R26" t="n">
-        <v>7041071</v>
+        <v>7041098</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120204116</v>
+        <v>120201767</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3294,25 +3294,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566691</v>
+        <v>566610</v>
       </c>
       <c r="R27" t="n">
-        <v>7041096</v>
+        <v>7040928</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3355,9 +3355,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,19 +3387,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120201767</v>
+        <v>120205221</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3418,19 +3433,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566610</v>
+        <v>566496</v>
       </c>
       <c r="R28" t="n">
-        <v>7040928</v>
+        <v>7041192</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3457,24 +3477,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3489,22 +3499,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120205221</v>
+        <v>120204116</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,43 +3523,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566496</v>
+        <v>566691</v>
       </c>
       <c r="R29" t="n">
-        <v>7041192</v>
+        <v>7041096</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3582,11 +3587,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120204205</v>
+        <v>120202553</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,38 +3727,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566711</v>
+        <v>566578</v>
       </c>
       <c r="R31" t="n">
-        <v>7041082</v>
+        <v>7040998</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3817,10 +3821,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120205398</v>
+        <v>120202768</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3833,21 +3837,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3857,13 +3861,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566613</v>
+        <v>566600</v>
       </c>
       <c r="R32" t="n">
-        <v>7040940</v>
+        <v>7041007</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3890,19 +3894,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,19 +3911,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120202768</v>
+        <v>120202727</v>
       </c>
       <c r="B33" t="n">
         <v>90864</v>
@@ -3969,10 +3963,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566600</v>
+        <v>566577</v>
       </c>
       <c r="R33" t="n">
-        <v>7041007</v>
+        <v>7041064</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4031,10 +4025,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120202727</v>
+        <v>120204205</v>
       </c>
       <c r="B34" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,21 +4041,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4065,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566577</v>
+        <v>566711</v>
       </c>
       <c r="R34" t="n">
-        <v>7041064</v>
+        <v>7041082</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4133,10 +4127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120202553</v>
+        <v>120205398</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4145,45 +4139,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566578</v>
+        <v>566613</v>
       </c>
       <c r="R35" t="n">
-        <v>7040998</v>
+        <v>7040940</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4210,9 +4200,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4227,12 +4227,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120202853</v>
+        <v>120204939</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4561,38 +4561,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566624</v>
+        <v>566566</v>
       </c>
       <c r="R39" t="n">
-        <v>7041060</v>
+        <v>7041107</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4651,10 +4655,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120204939</v>
+        <v>120202853</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4663,42 +4667,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566566</v>
+        <v>566624</v>
       </c>
       <c r="R40" t="n">
-        <v>7041107</v>
+        <v>7041060</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -8165,10 +8165,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120202297</v>
+        <v>120205192</v>
       </c>
       <c r="B73" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8181,34 +8181,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566551</v>
+        <v>566499</v>
       </c>
       <c r="R73" t="n">
-        <v>7040999</v>
+        <v>7041186</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8241,6 +8246,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8267,10 +8277,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120205192</v>
+        <v>120202297</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8283,39 +8293,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566499</v>
+        <v>566551</v>
       </c>
       <c r="R74" t="n">
-        <v>7041186</v>
+        <v>7040999</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8348,11 +8353,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8379,10 +8379,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120201661</v>
+        <v>120204862</v>
       </c>
       <c r="B75" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8391,25 +8391,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8419,13 +8419,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566582</v>
+        <v>566579</v>
       </c>
       <c r="R75" t="n">
-        <v>7040944</v>
+        <v>7041130</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8452,19 +8452,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8479,22 +8469,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120201350</v>
+        <v>120205148</v>
       </c>
       <c r="B76" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8503,25 +8493,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8531,13 +8521,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566534</v>
+        <v>566529</v>
       </c>
       <c r="R76" t="n">
-        <v>7040990</v>
+        <v>7041203</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8564,19 +8554,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8591,22 +8571,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120204862</v>
+        <v>120203078</v>
       </c>
       <c r="B77" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8615,25 +8595,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8643,10 +8623,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566579</v>
+        <v>566621</v>
       </c>
       <c r="R77" t="n">
-        <v>7041130</v>
+        <v>7041057</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8705,10 +8685,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120205148</v>
+        <v>120201661</v>
       </c>
       <c r="B78" t="n">
-        <v>79652</v>
+        <v>90864</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8717,25 +8697,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8745,13 +8725,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566529</v>
+        <v>566582</v>
       </c>
       <c r="R78" t="n">
-        <v>7041203</v>
+        <v>7040944</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8778,9 +8758,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8795,22 +8785,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120203078</v>
+        <v>120201350</v>
       </c>
       <c r="B79" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8823,21 +8813,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8847,13 +8837,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566621</v>
+        <v>566534</v>
       </c>
       <c r="R79" t="n">
-        <v>7041057</v>
+        <v>7040990</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8880,9 +8870,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8897,22 +8897,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120204816</v>
+        <v>120202392</v>
       </c>
       <c r="B80" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8921,38 +8921,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566572</v>
+        <v>566555</v>
       </c>
       <c r="R80" t="n">
-        <v>7041139</v>
+        <v>7041027</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9011,10 +9015,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120201620</v>
+        <v>120204816</v>
       </c>
       <c r="B81" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9023,25 +9027,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9051,13 +9055,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566582</v>
+        <v>566572</v>
       </c>
       <c r="R81" t="n">
-        <v>7040944</v>
+        <v>7041139</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9084,19 +9088,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9111,22 +9105,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120204835</v>
+        <v>120201620</v>
       </c>
       <c r="B82" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9135,25 +9129,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9163,13 +9157,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566561</v>
+        <v>566582</v>
       </c>
       <c r="R82" t="n">
-        <v>7041134</v>
+        <v>7040944</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9196,9 +9190,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9213,22 +9217,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120204901</v>
+        <v>120204835</v>
       </c>
       <c r="B83" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9237,25 +9241,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9265,10 +9269,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566567</v>
+        <v>566561</v>
       </c>
       <c r="R83" t="n">
-        <v>7041107</v>
+        <v>7041134</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9327,10 +9331,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120202392</v>
+        <v>120204901</v>
       </c>
       <c r="B84" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9339,42 +9343,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566555</v>
+        <v>566567</v>
       </c>
       <c r="R84" t="n">
-        <v>7041027</v>
+        <v>7041107</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202492</v>
+        <v>120204104</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566568</v>
+        <v>566694</v>
       </c>
       <c r="R2" t="n">
-        <v>7041045</v>
+        <v>7041098</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120203004</v>
+        <v>120202786</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566624</v>
+        <v>566623</v>
       </c>
       <c r="R3" t="n">
-        <v>7041079</v>
+        <v>7041032</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120205323</v>
+        <v>120204507</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566528</v>
+        <v>566602</v>
       </c>
       <c r="R4" t="n">
-        <v>7041117</v>
+        <v>7041134</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204980</v>
+        <v>120201983</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,37 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566561</v>
+        <v>566636</v>
       </c>
       <c r="R5" t="n">
-        <v>7041107</v>
+        <v>7040903</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,9 +1059,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,19 +1086,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120205064</v>
+        <v>120204835</v>
       </c>
       <c r="B6" t="n">
         <v>90545</v>
@@ -1127,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566502</v>
+        <v>566561</v>
       </c>
       <c r="R6" t="n">
-        <v>7041103</v>
+        <v>7041134</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204405</v>
+        <v>120205024</v>
       </c>
       <c r="B7" t="n">
         <v>90545</v>
@@ -1229,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566637</v>
+        <v>566549</v>
       </c>
       <c r="R7" t="n">
-        <v>7041131</v>
+        <v>7041126</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120202289</v>
+        <v>120205398</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1331,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566546</v>
+        <v>566613</v>
       </c>
       <c r="R8" t="n">
-        <v>7041010</v>
+        <v>7040940</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,9 +1375,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,19 +1402,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120200869</v>
+        <v>120203078</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1433,13 +1454,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566512</v>
+        <v>566621</v>
       </c>
       <c r="R9" t="n">
-        <v>7041220</v>
+        <v>7041057</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1466,19 +1487,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,22 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120201490</v>
+        <v>120200849</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566563</v>
+        <v>566521</v>
       </c>
       <c r="R10" t="n">
-        <v>7040951</v>
+        <v>7041283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1590,7 +1601,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120204945</v>
+        <v>120202492</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,38 +1645,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566565</v>
+        <v>566568</v>
       </c>
       <c r="R11" t="n">
-        <v>7041107</v>
+        <v>7041045</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1719,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120205199</v>
+        <v>120204476</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,39 +1755,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566499</v>
+        <v>566635</v>
       </c>
       <c r="R12" t="n">
-        <v>7041189</v>
+        <v>7041139</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1800,11 +1815,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120201231</v>
+        <v>120204503</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,13 +1881,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566502</v>
+        <v>566603</v>
       </c>
       <c r="R13" t="n">
-        <v>7041017</v>
+        <v>7041138</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,24 +1914,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,22 +1931,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204212</v>
+        <v>120202768</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,42 +1955,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566711</v>
+        <v>566600</v>
       </c>
       <c r="R14" t="n">
-        <v>7041082</v>
+        <v>7041007</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2054,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120202824</v>
+        <v>120204492</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566616</v>
+        <v>566608</v>
       </c>
       <c r="R15" t="n">
-        <v>7041049</v>
+        <v>7041149</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2156,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120203937</v>
+        <v>120205460</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,34 +2163,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566660</v>
+        <v>566500</v>
       </c>
       <c r="R16" t="n">
-        <v>7041078</v>
+        <v>7041094</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2232,6 +2228,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2258,7 +2259,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120202571</v>
+        <v>120205084</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2293,7 +2294,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2302,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566582</v>
+        <v>566515</v>
       </c>
       <c r="R17" t="n">
-        <v>7041015</v>
+        <v>7041125</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2364,10 +2365,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120202239</v>
+        <v>120204116</v>
       </c>
       <c r="B18" t="n">
-        <v>90742</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2376,25 +2377,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2404,10 +2405,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566526</v>
+        <v>566691</v>
       </c>
       <c r="R18" t="n">
-        <v>7041005</v>
+        <v>7041096</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2466,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120204267</v>
+        <v>120202297</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2478,25 +2479,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2506,10 +2507,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566695</v>
+        <v>566551</v>
       </c>
       <c r="R19" t="n">
-        <v>7041080</v>
+        <v>7040999</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2568,7 +2569,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120205024</v>
+        <v>120204807</v>
       </c>
       <c r="B20" t="n">
         <v>90545</v>
@@ -2608,10 +2609,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566549</v>
+        <v>566575</v>
       </c>
       <c r="R20" t="n">
-        <v>7041126</v>
+        <v>7041141</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2670,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204013</v>
+        <v>120204901</v>
       </c>
       <c r="B21" t="n">
-        <v>78278</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,21 +2687,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,10 +2711,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566666</v>
+        <v>566567</v>
       </c>
       <c r="R21" t="n">
-        <v>7041066</v>
+        <v>7041107</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2772,10 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204476</v>
+        <v>120202289</v>
       </c>
       <c r="B22" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,21 +2789,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2812,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566635</v>
+        <v>566546</v>
       </c>
       <c r="R22" t="n">
-        <v>7041139</v>
+        <v>7041010</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2874,10 +2875,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120202697</v>
+        <v>120201490</v>
       </c>
       <c r="B23" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,21 +2891,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2914,13 +2915,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566589</v>
+        <v>566563</v>
       </c>
       <c r="R23" t="n">
-        <v>7041075</v>
+        <v>7040951</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2947,9 +2948,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,22 +2975,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120202811</v>
+        <v>120205468</v>
       </c>
       <c r="B24" t="n">
-        <v>90923</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2988,25 +2999,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3016,10 +3027,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566616</v>
+        <v>566498</v>
       </c>
       <c r="R24" t="n">
-        <v>7041049</v>
+        <v>7041093</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3078,10 +3089,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120204153</v>
+        <v>120205312</v>
       </c>
       <c r="B25" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,41 +3101,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566671</v>
+        <v>566618</v>
       </c>
       <c r="R25" t="n">
-        <v>7041071</v>
+        <v>7040939</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3151,9 +3171,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,22 +3198,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120204104</v>
+        <v>120204212</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3192,38 +3222,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566694</v>
+        <v>566711</v>
       </c>
       <c r="R26" t="n">
-        <v>7041098</v>
+        <v>7041082</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3282,10 +3316,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120201767</v>
+        <v>120201661</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3298,21 +3332,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3322,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566610</v>
+        <v>566582</v>
       </c>
       <c r="R27" t="n">
-        <v>7040928</v>
+        <v>7040944</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3367,12 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120205221</v>
+        <v>120202755</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,43 +3440,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566496</v>
+        <v>566572</v>
       </c>
       <c r="R28" t="n">
-        <v>7041192</v>
+        <v>7041055</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3480,11 +3504,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3511,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120204116</v>
+        <v>120203571</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3523,25 +3542,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3551,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566691</v>
+        <v>566647</v>
       </c>
       <c r="R29" t="n">
-        <v>7041096</v>
+        <v>7041053</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3613,10 +3632,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120204503</v>
+        <v>120200869</v>
       </c>
       <c r="B30" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3629,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3653,13 +3672,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566603</v>
+        <v>566512</v>
       </c>
       <c r="R30" t="n">
-        <v>7041138</v>
+        <v>7041220</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3686,9 +3705,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,22 +3732,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120202553</v>
+        <v>120205138</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,42 +3756,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566578</v>
+        <v>566529</v>
       </c>
       <c r="R31" t="n">
-        <v>7040998</v>
+        <v>7041203</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3821,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202768</v>
+        <v>120202853</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3837,21 +3862,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3861,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566600</v>
+        <v>566624</v>
       </c>
       <c r="R32" t="n">
-        <v>7041007</v>
+        <v>7041060</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3923,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120202727</v>
+        <v>120203123</v>
       </c>
       <c r="B33" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3935,38 +3960,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566577</v>
+        <v>566628</v>
       </c>
       <c r="R33" t="n">
-        <v>7041064</v>
+        <v>7041063</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4025,10 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120204205</v>
+        <v>120204405</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4037,25 +4066,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4065,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566711</v>
+        <v>566637</v>
       </c>
       <c r="R34" t="n">
-        <v>7041082</v>
+        <v>7041131</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4127,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120205398</v>
+        <v>120202811</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>90923</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4139,25 +4168,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4167,13 +4196,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566613</v>
+        <v>566616</v>
       </c>
       <c r="R35" t="n">
-        <v>7040940</v>
+        <v>7041049</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4200,19 +4229,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4227,22 +4246,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120205179</v>
+        <v>120204267</v>
       </c>
       <c r="B36" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4255,21 +4274,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4298,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566503</v>
+        <v>566695</v>
       </c>
       <c r="R36" t="n">
-        <v>7041183</v>
+        <v>7041080</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4341,10 +4360,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120205084</v>
+        <v>120204013</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4353,42 +4372,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566515</v>
+        <v>566666</v>
       </c>
       <c r="R37" t="n">
-        <v>7041125</v>
+        <v>7041066</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4447,10 +4462,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120202642</v>
+        <v>120202392</v>
       </c>
       <c r="B38" t="n">
-        <v>74654</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,38 +4474,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566590</v>
+        <v>566555</v>
       </c>
       <c r="R38" t="n">
-        <v>7041023</v>
+        <v>7041027</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4549,10 +4568,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120204939</v>
+        <v>120204945</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4561,39 +4580,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566566</v>
+        <v>566565</v>
       </c>
       <c r="R39" t="n">
         <v>7041107</v>
@@ -4655,10 +4670,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120202853</v>
+        <v>120201350</v>
       </c>
       <c r="B40" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4671,21 +4686,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4695,13 +4710,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566624</v>
+        <v>566534</v>
       </c>
       <c r="R40" t="n">
-        <v>7041060</v>
+        <v>7040990</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4728,9 +4743,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4745,19 +4770,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120205511</v>
+        <v>120200832</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4802,13 +4827,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566509</v>
+        <v>566507</v>
       </c>
       <c r="R41" t="n">
-        <v>7041097</v>
+        <v>7041231</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4835,14 +4860,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4857,22 +4887,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120204797</v>
+        <v>120204862</v>
       </c>
       <c r="B42" t="n">
-        <v>96885</v>
+        <v>90545</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4885,21 +4915,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4909,10 +4939,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566572</v>
+        <v>566579</v>
       </c>
       <c r="R42" t="n">
-        <v>7041137</v>
+        <v>7041130</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4971,10 +5001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120202674</v>
+        <v>120203962</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>79160</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4987,21 +5017,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5011,10 +5041,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566584</v>
+        <v>566665</v>
       </c>
       <c r="R43" t="n">
-        <v>7041103</v>
+        <v>7041086</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5073,10 +5103,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120202755</v>
+        <v>120204816</v>
       </c>
       <c r="B44" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5085,25 +5115,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5116,7 +5146,7 @@
         <v>566572</v>
       </c>
       <c r="R44" t="n">
-        <v>7041055</v>
+        <v>7041139</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5175,10 +5205,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120203571</v>
+        <v>120205148</v>
       </c>
       <c r="B45" t="n">
-        <v>89650</v>
+        <v>79652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,25 +5217,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5215,10 +5245,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566647</v>
+        <v>566529</v>
       </c>
       <c r="R45" t="n">
-        <v>7041053</v>
+        <v>7041203</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5307,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120204056</v>
+        <v>120202647</v>
       </c>
       <c r="B46" t="n">
-        <v>92048</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5289,38 +5319,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566678</v>
+        <v>566587</v>
       </c>
       <c r="R46" t="n">
-        <v>7041077</v>
+        <v>7041021</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5379,10 +5413,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120205460</v>
+        <v>120202239</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5395,39 +5429,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566500</v>
+        <v>566526</v>
       </c>
       <c r="R47" t="n">
-        <v>7041094</v>
+        <v>7041005</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5460,11 +5489,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5491,7 +5515,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120205278</v>
+        <v>120202571</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5526,7 +5550,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5535,10 +5559,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566528</v>
+        <v>566582</v>
       </c>
       <c r="R48" t="n">
-        <v>7041117</v>
+        <v>7041015</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5597,10 +5621,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120204492</v>
+        <v>120205420</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5613,37 +5637,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566608</v>
+        <v>566583</v>
       </c>
       <c r="R49" t="n">
-        <v>7041149</v>
+        <v>7040942</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5670,9 +5703,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5687,22 +5730,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120204507</v>
+        <v>120202697</v>
       </c>
       <c r="B50" t="n">
-        <v>79160</v>
+        <v>90594</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5715,21 +5758,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5739,10 +5782,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566602</v>
+        <v>566589</v>
       </c>
       <c r="R50" t="n">
-        <v>7041134</v>
+        <v>7041075</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5801,7 +5844,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120204958</v>
+        <v>120202674</v>
       </c>
       <c r="B51" t="n">
         <v>90580</v>
@@ -5841,10 +5884,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566564</v>
+        <v>566584</v>
       </c>
       <c r="R51" t="n">
-        <v>7041107</v>
+        <v>7041103</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5903,10 +5946,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120201451</v>
+        <v>120202642</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>74654</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5919,21 +5962,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5943,13 +5986,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566541</v>
+        <v>566590</v>
       </c>
       <c r="R52" t="n">
-        <v>7040997</v>
+        <v>7041023</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5976,19 +6019,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6003,22 +6036,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120202733</v>
+        <v>120201451</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6031,21 +6064,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6055,13 +6088,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566567</v>
+        <v>566541</v>
       </c>
       <c r="R53" t="n">
-        <v>7041052</v>
+        <v>7040997</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6088,9 +6121,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6105,22 +6148,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120202647</v>
+        <v>120205368</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6129,30 +6172,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6161,10 +6205,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566587</v>
+        <v>566521</v>
       </c>
       <c r="R54" t="n">
-        <v>7041021</v>
+        <v>7041138</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6197,6 +6241,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6223,10 +6272,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120204358</v>
+        <v>120205154</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6235,38 +6284,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566663</v>
+        <v>566510</v>
       </c>
       <c r="R55" t="n">
-        <v>7041118</v>
+        <v>7041190</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6325,10 +6378,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120204567</v>
+        <v>120204939</v>
       </c>
       <c r="B56" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6337,38 +6390,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566612</v>
+        <v>566566</v>
       </c>
       <c r="R56" t="n">
-        <v>7041175</v>
+        <v>7041107</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6427,10 +6484,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120202622</v>
+        <v>120204358</v>
       </c>
       <c r="B57" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6439,25 +6496,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6467,10 +6524,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566590</v>
+        <v>566663</v>
       </c>
       <c r="R57" t="n">
-        <v>7041027</v>
+        <v>7041118</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6529,10 +6586,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120205138</v>
+        <v>120204056</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>92048</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6545,21 +6602,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6569,10 +6626,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566529</v>
+        <v>566678</v>
       </c>
       <c r="R58" t="n">
-        <v>7041203</v>
+        <v>7041077</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6631,10 +6688,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120205468</v>
+        <v>120203396</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6643,25 +6700,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6671,10 +6728,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566498</v>
+        <v>566638</v>
       </c>
       <c r="R59" t="n">
-        <v>7041093</v>
+        <v>7041075</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6733,10 +6790,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120200832</v>
+        <v>120201620</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6745,43 +6802,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566507</v>
+        <v>566582</v>
       </c>
       <c r="R60" t="n">
-        <v>7041231</v>
+        <v>7040944</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6813,7 +6865,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6823,7 +6875,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6838,22 +6890,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120200849</v>
+        <v>120205064</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6862,25 +6914,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6890,13 +6942,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566521</v>
+        <v>566502</v>
       </c>
       <c r="R61" t="n">
-        <v>7041283</v>
+        <v>7041103</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6923,24 +6975,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6955,22 +6992,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120201983</v>
+        <v>120203937</v>
       </c>
       <c r="B62" t="n">
-        <v>57473</v>
+        <v>90864</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6983,42 +7020,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566636</v>
+        <v>566660</v>
       </c>
       <c r="R62" t="n">
-        <v>7040903</v>
+        <v>7041078</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7045,19 +7077,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7072,22 +7094,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120204807</v>
+        <v>120205221</v>
       </c>
       <c r="B63" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7096,38 +7118,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566575</v>
+        <v>566496</v>
       </c>
       <c r="R63" t="n">
-        <v>7041141</v>
+        <v>7041192</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7160,6 +7187,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7186,10 +7218,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120202867</v>
+        <v>120205199</v>
       </c>
       <c r="B64" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7198,38 +7230,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566626</v>
+        <v>566499</v>
       </c>
       <c r="R64" t="n">
-        <v>7041042</v>
+        <v>7041189</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7262,6 +7299,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7288,10 +7330,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120203396</v>
+        <v>120202867</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7304,21 +7346,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7328,10 +7370,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566638</v>
+        <v>566626</v>
       </c>
       <c r="R65" t="n">
-        <v>7041075</v>
+        <v>7041042</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7390,10 +7432,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120200809</v>
+        <v>120202553</v>
       </c>
       <c r="B66" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7402,31 +7444,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7435,13 +7476,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566509</v>
+        <v>566578</v>
       </c>
       <c r="R66" t="n">
-        <v>7041308</v>
+        <v>7040998</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7468,19 +7509,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7495,22 +7526,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120205154</v>
+        <v>120202824</v>
       </c>
       <c r="B67" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7519,42 +7550,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566510</v>
+        <v>566616</v>
       </c>
       <c r="R67" t="n">
-        <v>7041190</v>
+        <v>7041049</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7613,10 +7640,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120202786</v>
+        <v>120204153</v>
       </c>
       <c r="B68" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7625,25 +7652,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7653,10 +7680,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566623</v>
+        <v>566671</v>
       </c>
       <c r="R68" t="n">
-        <v>7041032</v>
+        <v>7041071</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7715,10 +7742,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120205420</v>
+        <v>120204958</v>
       </c>
       <c r="B69" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7731,46 +7758,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566583</v>
+        <v>566564</v>
       </c>
       <c r="R69" t="n">
-        <v>7040942</v>
+        <v>7041107</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7797,19 +7815,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7824,22 +7832,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120203962</v>
+        <v>120202733</v>
       </c>
       <c r="B70" t="n">
-        <v>79160</v>
+        <v>90580</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7852,21 +7860,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7876,10 +7884,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566665</v>
+        <v>566567</v>
       </c>
       <c r="R70" t="n">
-        <v>7041086</v>
+        <v>7041052</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7938,10 +7946,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120203123</v>
+        <v>120201231</v>
       </c>
       <c r="B71" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7950,45 +7958,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566628</v>
+        <v>566502</v>
       </c>
       <c r="R71" t="n">
-        <v>7041063</v>
+        <v>7041017</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8015,9 +8019,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8032,22 +8051,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120205312</v>
+        <v>120200809</v>
       </c>
       <c r="B72" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8056,35 +8075,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8093,10 +8108,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566618</v>
+        <v>566509</v>
       </c>
       <c r="R72" t="n">
-        <v>7040939</v>
+        <v>7041308</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8128,7 +8143,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8138,7 +8153,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8153,22 +8168,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120205192</v>
+        <v>120205278</v>
       </c>
       <c r="B73" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8177,31 +8192,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8210,10 +8224,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566499</v>
+        <v>566528</v>
       </c>
       <c r="R73" t="n">
-        <v>7041186</v>
+        <v>7041117</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8246,11 +8260,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8277,10 +8286,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120202297</v>
+        <v>120201767</v>
       </c>
       <c r="B74" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8293,21 +8302,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8317,13 +8326,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566551</v>
+        <v>566610</v>
       </c>
       <c r="R74" t="n">
-        <v>7040999</v>
+        <v>7040928</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8350,9 +8359,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8367,22 +8391,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120204862</v>
+        <v>120205192</v>
       </c>
       <c r="B75" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8391,38 +8415,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566579</v>
+        <v>566499</v>
       </c>
       <c r="R75" t="n">
-        <v>7041130</v>
+        <v>7041186</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8455,6 +8484,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8481,10 +8515,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120205148</v>
+        <v>120202622</v>
       </c>
       <c r="B76" t="n">
-        <v>79652</v>
+        <v>90545</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8497,21 +8531,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8521,10 +8555,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566529</v>
+        <v>566590</v>
       </c>
       <c r="R76" t="n">
-        <v>7041203</v>
+        <v>7041027</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8583,10 +8617,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120203078</v>
+        <v>120204567</v>
       </c>
       <c r="B77" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8595,25 +8629,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8623,10 +8657,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566621</v>
+        <v>566612</v>
       </c>
       <c r="R77" t="n">
-        <v>7041057</v>
+        <v>7041175</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8685,10 +8719,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120201661</v>
+        <v>120205179</v>
       </c>
       <c r="B78" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8697,25 +8731,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8725,13 +8759,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566582</v>
+        <v>566503</v>
       </c>
       <c r="R78" t="n">
-        <v>7040944</v>
+        <v>7041183</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8758,19 +8792,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8785,22 +8809,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120201350</v>
+        <v>120204980</v>
       </c>
       <c r="B79" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8813,21 +8837,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8837,13 +8861,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566534</v>
+        <v>566561</v>
       </c>
       <c r="R79" t="n">
-        <v>7040990</v>
+        <v>7041107</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8870,19 +8894,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8897,22 +8911,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120202392</v>
+        <v>120204797</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8921,42 +8935,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566555</v>
+        <v>566572</v>
       </c>
       <c r="R80" t="n">
-        <v>7041027</v>
+        <v>7041137</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9015,7 +9025,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120204816</v>
+        <v>120203004</v>
       </c>
       <c r="B81" t="n">
         <v>90580</v>
@@ -9055,10 +9065,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566572</v>
+        <v>566624</v>
       </c>
       <c r="R81" t="n">
-        <v>7041139</v>
+        <v>7041079</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9117,10 +9127,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120201620</v>
+        <v>120205323</v>
       </c>
       <c r="B82" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9129,25 +9139,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9157,13 +9167,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566582</v>
+        <v>566528</v>
       </c>
       <c r="R82" t="n">
-        <v>7040944</v>
+        <v>7041117</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9190,19 +9200,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9217,22 +9217,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120204835</v>
+        <v>120202727</v>
       </c>
       <c r="B83" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9241,25 +9241,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9269,10 +9269,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566561</v>
+        <v>566577</v>
       </c>
       <c r="R83" t="n">
-        <v>7041134</v>
+        <v>7041064</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9331,10 +9331,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120204901</v>
+        <v>120204205</v>
       </c>
       <c r="B84" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9347,21 +9347,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566567</v>
+        <v>566711</v>
       </c>
       <c r="R84" t="n">
-        <v>7041107</v>
+        <v>7041082</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9433,7 +9433,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120205368</v>
+        <v>120205511</v>
       </c>
       <c r="B85" t="n">
         <v>57320</v>
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566521</v>
+        <v>566509</v>
       </c>
       <c r="R85" t="n">
-        <v>7041138</v>
+        <v>7041097</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120201983</v>
+        <v>120204835</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,46 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566636</v>
+        <v>566561</v>
       </c>
       <c r="R5" t="n">
-        <v>7040903</v>
+        <v>7041134</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,19 +1054,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120204835</v>
+        <v>120205024</v>
       </c>
       <c r="B6" t="n">
         <v>90545</v>
@@ -1138,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566561</v>
+        <v>566549</v>
       </c>
       <c r="R6" t="n">
-        <v>7041134</v>
+        <v>7041126</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120205024</v>
+        <v>120201983</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,41 +1197,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566549</v>
+        <v>566636</v>
       </c>
       <c r="R7" t="n">
-        <v>7041126</v>
+        <v>7040903</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1273,9 +1263,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120205398</v>
+        <v>120200849</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566613</v>
+        <v>566521</v>
       </c>
       <c r="R8" t="n">
-        <v>7040940</v>
+        <v>7041283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120203078</v>
+        <v>120205398</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566621</v>
+        <v>566613</v>
       </c>
       <c r="R9" t="n">
-        <v>7041057</v>
+        <v>7040940</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1487,9 +1492,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,22 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120200849</v>
+        <v>120203078</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566521</v>
+        <v>566621</v>
       </c>
       <c r="R10" t="n">
-        <v>7041283</v>
+        <v>7041057</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,24 +1604,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,12 +1621,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120205138</v>
+        <v>120204405</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,25 +3756,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566529</v>
+        <v>566637</v>
       </c>
       <c r="R31" t="n">
-        <v>7041203</v>
+        <v>7041131</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202853</v>
+        <v>120202811</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>90923</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566624</v>
+        <v>566616</v>
       </c>
       <c r="R32" t="n">
-        <v>7041060</v>
+        <v>7041049</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120204405</v>
+        <v>120204267</v>
       </c>
       <c r="B34" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,21 +4070,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566637</v>
+        <v>566695</v>
       </c>
       <c r="R34" t="n">
-        <v>7041131</v>
+        <v>7041080</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120202811</v>
+        <v>120205138</v>
       </c>
       <c r="B35" t="n">
-        <v>90923</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,25 +4168,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566616</v>
+        <v>566529</v>
       </c>
       <c r="R35" t="n">
-        <v>7041049</v>
+        <v>7041203</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120204267</v>
+        <v>120202853</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,25 +4270,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566695</v>
+        <v>566624</v>
       </c>
       <c r="R36" t="n">
-        <v>7041080</v>
+        <v>7041060</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120204945</v>
+        <v>120201350</v>
       </c>
       <c r="B39" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566565</v>
+        <v>566534</v>
       </c>
       <c r="R39" t="n">
-        <v>7041107</v>
+        <v>7040990</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4641,9 +4641,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4658,22 +4668,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120201350</v>
+        <v>120204945</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4686,21 +4696,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4710,13 +4720,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566534</v>
+        <v>566565</v>
       </c>
       <c r="R40" t="n">
-        <v>7040990</v>
+        <v>7041107</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4743,19 +4753,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4770,22 +4770,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120200832</v>
+        <v>120205148</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,46 +4794,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566507</v>
+        <v>566529</v>
       </c>
       <c r="R41" t="n">
-        <v>7041231</v>
+        <v>7041203</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4860,19 +4855,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4887,22 +4872,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120204862</v>
+        <v>120200832</v>
       </c>
       <c r="B42" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4911,41 +4896,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566579</v>
+        <v>566507</v>
       </c>
       <c r="R42" t="n">
-        <v>7041130</v>
+        <v>7041231</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4972,9 +4962,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4989,22 +4989,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120203962</v>
+        <v>120204816</v>
       </c>
       <c r="B43" t="n">
-        <v>79160</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566665</v>
+        <v>566572</v>
       </c>
       <c r="R43" t="n">
-        <v>7041086</v>
+        <v>7041139</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120204816</v>
+        <v>120204862</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5115,25 +5115,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566572</v>
+        <v>566579</v>
       </c>
       <c r="R44" t="n">
-        <v>7041139</v>
+        <v>7041130</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120205148</v>
+        <v>120203962</v>
       </c>
       <c r="B45" t="n">
-        <v>79652</v>
+        <v>79160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5217,25 +5217,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566529</v>
+        <v>566665</v>
       </c>
       <c r="R45" t="n">
-        <v>7041203</v>
+        <v>7041086</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -7218,10 +7218,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120205199</v>
+        <v>120202867</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7230,43 +7230,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566499</v>
+        <v>566626</v>
       </c>
       <c r="R64" t="n">
-        <v>7041189</v>
+        <v>7041042</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7299,11 +7294,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7330,10 +7320,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120202867</v>
+        <v>120205199</v>
       </c>
       <c r="B65" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7342,38 +7332,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566626</v>
+        <v>566499</v>
       </c>
       <c r="R65" t="n">
-        <v>7041042</v>
+        <v>7041189</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7406,6 +7401,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7946,10 +7946,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120201231</v>
+        <v>120200809</v>
       </c>
       <c r="B71" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7962,16 +7962,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7980,16 +7980,21 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566502</v>
+        <v>566509</v>
       </c>
       <c r="R71" t="n">
-        <v>7041017</v>
+        <v>7041308</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8021,7 +8026,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8031,12 +8036,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8063,10 +8063,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120200809</v>
+        <v>120201231</v>
       </c>
       <c r="B72" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8079,16 +8079,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8097,21 +8097,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566509</v>
+        <v>566502</v>
       </c>
       <c r="R72" t="n">
-        <v>7041308</v>
+        <v>7041017</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8143,7 +8138,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8153,7 +8148,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8923,10 +8923,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120204797</v>
+        <v>120203004</v>
       </c>
       <c r="B80" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8935,25 +8935,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8963,10 +8963,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566572</v>
+        <v>566624</v>
       </c>
       <c r="R80" t="n">
-        <v>7041137</v>
+        <v>7041079</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9025,7 +9025,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120203004</v>
+        <v>120205323</v>
       </c>
       <c r="B81" t="n">
         <v>90580</v>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566624</v>
+        <v>566528</v>
       </c>
       <c r="R81" t="n">
-        <v>7041079</v>
+        <v>7041117</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9127,10 +9127,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120205323</v>
+        <v>120202727</v>
       </c>
       <c r="B82" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9143,21 +9143,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566528</v>
+        <v>566577</v>
       </c>
       <c r="R82" t="n">
-        <v>7041117</v>
+        <v>7041064</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9229,10 +9229,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120202727</v>
+        <v>120204205</v>
       </c>
       <c r="B83" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9245,21 +9245,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9269,10 +9269,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566577</v>
+        <v>566711</v>
       </c>
       <c r="R83" t="n">
-        <v>7041064</v>
+        <v>7041082</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9331,10 +9331,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120204205</v>
+        <v>120205511</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9347,34 +9347,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566711</v>
+        <v>566509</v>
       </c>
       <c r="R84" t="n">
-        <v>7041082</v>
+        <v>7041097</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9407,6 +9412,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9433,10 +9443,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120205511</v>
+        <v>120204797</v>
       </c>
       <c r="B85" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9445,43 +9455,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566509</v>
+        <v>566572</v>
       </c>
       <c r="R85" t="n">
-        <v>7041097</v>
+        <v>7041137</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9514,11 +9519,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120204104</v>
+        <v>120204862</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566694</v>
+        <v>566579</v>
       </c>
       <c r="R2" t="n">
-        <v>7041098</v>
+        <v>7041130</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202786</v>
+        <v>120205468</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566623</v>
+        <v>566498</v>
       </c>
       <c r="R3" t="n">
-        <v>7041032</v>
+        <v>7041093</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204507</v>
+        <v>120204476</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566602</v>
+        <v>566635</v>
       </c>
       <c r="R4" t="n">
-        <v>7041134</v>
+        <v>7041139</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204835</v>
+        <v>120202674</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566561</v>
+        <v>566584</v>
       </c>
       <c r="R5" t="n">
-        <v>7041134</v>
+        <v>7041103</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120205024</v>
+        <v>120202239</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>90742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566549</v>
+        <v>566526</v>
       </c>
       <c r="R6" t="n">
-        <v>7041126</v>
+        <v>7041005</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120201983</v>
+        <v>120204816</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,42 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566636</v>
+        <v>566572</v>
       </c>
       <c r="R7" t="n">
-        <v>7040903</v>
+        <v>7041139</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,19 +1258,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120200849</v>
+        <v>120203004</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566521</v>
+        <v>566624</v>
       </c>
       <c r="R8" t="n">
-        <v>7041283</v>
+        <v>7041079</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,24 +1360,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120205398</v>
+        <v>120204807</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566613</v>
+        <v>566575</v>
       </c>
       <c r="R9" t="n">
-        <v>7040940</v>
+        <v>7041141</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,19 +1462,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,12 +1479,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1633,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120202492</v>
+        <v>120204153</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,42 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566568</v>
+        <v>566671</v>
       </c>
       <c r="R11" t="n">
-        <v>7041045</v>
+        <v>7041071</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1739,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204476</v>
+        <v>120205221</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,34 +1711,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566635</v>
+        <v>566496</v>
       </c>
       <c r="R12" t="n">
-        <v>7041139</v>
+        <v>7041192</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1815,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204503</v>
+        <v>120204056</v>
       </c>
       <c r="B13" t="n">
-        <v>78279</v>
+        <v>92048</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566603</v>
+        <v>566678</v>
       </c>
       <c r="R13" t="n">
-        <v>7041138</v>
+        <v>7041077</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1943,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120202768</v>
+        <v>120205084</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,38 +1921,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566600</v>
+        <v>566515</v>
       </c>
       <c r="R14" t="n">
-        <v>7041007</v>
+        <v>7041125</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2045,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204492</v>
+        <v>120205064</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,25 +2027,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2085,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566608</v>
+        <v>566502</v>
       </c>
       <c r="R15" t="n">
-        <v>7041149</v>
+        <v>7041103</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2147,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120205460</v>
+        <v>120201490</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,42 +2133,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566500</v>
+        <v>566563</v>
       </c>
       <c r="R16" t="n">
-        <v>7041094</v>
+        <v>7040951</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2225,14 +2190,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,22 +2217,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120205084</v>
+        <v>120201451</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,45 +2241,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566515</v>
+        <v>566541</v>
       </c>
       <c r="R17" t="n">
-        <v>7041125</v>
+        <v>7040997</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2336,9 +2302,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,22 +2329,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204116</v>
+        <v>120205460</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,38 +2353,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566691</v>
+        <v>566500</v>
       </c>
       <c r="R18" t="n">
-        <v>7041096</v>
+        <v>7041094</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2441,6 +2422,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2467,10 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120202297</v>
+        <v>120205179</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,25 +2465,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2507,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566551</v>
+        <v>566503</v>
       </c>
       <c r="R19" t="n">
-        <v>7040999</v>
+        <v>7041183</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2569,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204807</v>
+        <v>120205511</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2581,38 +2567,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566575</v>
+        <v>566509</v>
       </c>
       <c r="R20" t="n">
-        <v>7041141</v>
+        <v>7041097</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2645,6 +2636,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2671,10 +2667,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204901</v>
+        <v>120200809</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>56524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2687,37 +2683,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566567</v>
+        <v>566509</v>
       </c>
       <c r="R21" t="n">
-        <v>7041107</v>
+        <v>7041308</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2744,9 +2745,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2761,22 +2772,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120202289</v>
+        <v>120202392</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2785,38 +2796,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566546</v>
+        <v>566555</v>
       </c>
       <c r="R22" t="n">
-        <v>7041010</v>
+        <v>7041027</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2875,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120201490</v>
+        <v>120202867</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2887,25 +2902,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2915,13 +2930,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566563</v>
+        <v>566626</v>
       </c>
       <c r="R23" t="n">
-        <v>7040951</v>
+        <v>7041042</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2948,19 +2963,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2975,19 +2980,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120205468</v>
+        <v>120202853</v>
       </c>
       <c r="B24" t="n">
         <v>79623</v>
@@ -3027,10 +3032,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566498</v>
+        <v>566624</v>
       </c>
       <c r="R24" t="n">
-        <v>7041093</v>
+        <v>7041060</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3089,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120205312</v>
+        <v>120200832</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3101,35 +3106,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3138,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566618</v>
+        <v>566507</v>
       </c>
       <c r="R25" t="n">
-        <v>7040939</v>
+        <v>7041231</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3173,7 +3174,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3183,7 +3184,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3210,7 +3211,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120204212</v>
+        <v>120202553</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3245,7 +3246,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3254,10 +3255,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566711</v>
+        <v>566578</v>
       </c>
       <c r="R26" t="n">
-        <v>7041082</v>
+        <v>7040998</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3316,10 +3317,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120201661</v>
+        <v>120204212</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3328,41 +3329,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566582</v>
+        <v>566711</v>
       </c>
       <c r="R27" t="n">
-        <v>7040944</v>
+        <v>7041082</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3389,19 +3394,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3416,22 +3411,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120202755</v>
+        <v>120204958</v>
       </c>
       <c r="B28" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3440,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3468,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566572</v>
+        <v>566564</v>
       </c>
       <c r="R28" t="n">
-        <v>7041055</v>
+        <v>7041107</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3530,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120203571</v>
+        <v>120204013</v>
       </c>
       <c r="B29" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3546,21 +3541,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3570,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566647</v>
+        <v>566666</v>
       </c>
       <c r="R29" t="n">
-        <v>7041053</v>
+        <v>7041066</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3632,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120200869</v>
+        <v>120204567</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3644,25 +3639,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,13 +3667,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566512</v>
+        <v>566612</v>
       </c>
       <c r="R30" t="n">
-        <v>7041220</v>
+        <v>7041175</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3705,19 +3700,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3732,22 +3717,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120204405</v>
+        <v>120202768</v>
       </c>
       <c r="B31" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,25 +3741,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3769,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566637</v>
+        <v>566600</v>
       </c>
       <c r="R31" t="n">
-        <v>7041131</v>
+        <v>7041007</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3846,10 +3831,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202811</v>
+        <v>120203937</v>
       </c>
       <c r="B32" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,25 +3843,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3886,10 +3871,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566616</v>
+        <v>566660</v>
       </c>
       <c r="R32" t="n">
-        <v>7041049</v>
+        <v>7041078</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3948,10 +3933,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120203123</v>
+        <v>120201231</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,45 +3945,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566628</v>
+        <v>566502</v>
       </c>
       <c r="R33" t="n">
-        <v>7041063</v>
+        <v>7041017</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4025,9 +4006,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4042,22 +4038,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120204267</v>
+        <v>120202824</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4066,25 +4062,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4094,10 +4090,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566695</v>
+        <v>566616</v>
       </c>
       <c r="R34" t="n">
-        <v>7041080</v>
+        <v>7041049</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4156,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120205138</v>
+        <v>120202647</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,38 +4164,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566529</v>
+        <v>566587</v>
       </c>
       <c r="R35" t="n">
-        <v>7041203</v>
+        <v>7041021</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120202853</v>
+        <v>120202622</v>
       </c>
       <c r="B36" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,25 +4270,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566624</v>
+        <v>566590</v>
       </c>
       <c r="R36" t="n">
-        <v>7041060</v>
+        <v>7041027</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120204013</v>
+        <v>120201767</v>
       </c>
       <c r="B37" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4376,21 +4376,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566666</v>
+        <v>566610</v>
       </c>
       <c r="R37" t="n">
-        <v>7041066</v>
+        <v>7040928</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4433,9 +4433,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4450,22 +4465,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120202392</v>
+        <v>120202289</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,42 +4489,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566555</v>
+        <v>566546</v>
       </c>
       <c r="R38" t="n">
-        <v>7041027</v>
+        <v>7041010</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4568,10 +4579,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120201350</v>
+        <v>120205323</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4584,21 +4595,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4608,13 +4619,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566534</v>
+        <v>566528</v>
       </c>
       <c r="R39" t="n">
-        <v>7040990</v>
+        <v>7041117</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4641,19 +4652,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4668,22 +4669,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120204945</v>
+        <v>120205148</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>79652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4692,25 +4693,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4720,10 +4721,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566565</v>
+        <v>566529</v>
       </c>
       <c r="R40" t="n">
-        <v>7041107</v>
+        <v>7041203</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4782,10 +4783,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120205148</v>
+        <v>120205138</v>
       </c>
       <c r="B41" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,25 +4795,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4884,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120200832</v>
+        <v>120202727</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4900,42 +4901,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566507</v>
+        <v>566577</v>
       </c>
       <c r="R42" t="n">
-        <v>7041231</v>
+        <v>7041064</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4962,19 +4958,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4989,22 +4975,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120204816</v>
+        <v>120204901</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5017,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5041,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566572</v>
+        <v>566567</v>
       </c>
       <c r="R43" t="n">
-        <v>7041139</v>
+        <v>7041107</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5103,7 +5089,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120204862</v>
+        <v>120204405</v>
       </c>
       <c r="B44" t="n">
         <v>90545</v>
@@ -5143,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566579</v>
+        <v>566637</v>
       </c>
       <c r="R44" t="n">
-        <v>7041130</v>
+        <v>7041131</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5205,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120203962</v>
+        <v>120202733</v>
       </c>
       <c r="B45" t="n">
-        <v>79160</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5221,21 +5207,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5245,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566665</v>
+        <v>566567</v>
       </c>
       <c r="R45" t="n">
-        <v>7041086</v>
+        <v>7041052</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5307,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120202647</v>
+        <v>120204835</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5319,42 +5305,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566587</v>
+        <v>566561</v>
       </c>
       <c r="R46" t="n">
-        <v>7041021</v>
+        <v>7041134</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5413,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120202239</v>
+        <v>120204116</v>
       </c>
       <c r="B47" t="n">
-        <v>90742</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5425,25 +5407,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5453,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566526</v>
+        <v>566691</v>
       </c>
       <c r="R47" t="n">
-        <v>7041005</v>
+        <v>7041096</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5515,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120202571</v>
+        <v>120204492</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5527,42 +5509,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566582</v>
+        <v>566608</v>
       </c>
       <c r="R48" t="n">
-        <v>7041015</v>
+        <v>7041149</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5621,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120205420</v>
+        <v>120205199</v>
       </c>
       <c r="B49" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5637,31 +5615,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5670,13 +5644,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566583</v>
+        <v>566499</v>
       </c>
       <c r="R49" t="n">
-        <v>7040942</v>
+        <v>7041189</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5703,19 +5677,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:07</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5730,22 +5699,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120202697</v>
+        <v>120205312</v>
       </c>
       <c r="B50" t="n">
-        <v>90594</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5754,41 +5723,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566589</v>
+        <v>566618</v>
       </c>
       <c r="R50" t="n">
-        <v>7041075</v>
+        <v>7040939</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5815,9 +5793,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5832,22 +5820,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120202674</v>
+        <v>120204939</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5856,38 +5844,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566584</v>
+        <v>566566</v>
       </c>
       <c r="R51" t="n">
-        <v>7041103</v>
+        <v>7041107</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5946,10 +5938,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120202642</v>
+        <v>120202571</v>
       </c>
       <c r="B52" t="n">
-        <v>74654</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5958,38 +5950,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566590</v>
+        <v>566582</v>
       </c>
       <c r="R52" t="n">
-        <v>7041023</v>
+        <v>7041015</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6048,10 +6044,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120201451</v>
+        <v>120205154</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6060,41 +6056,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566541</v>
+        <v>566510</v>
       </c>
       <c r="R53" t="n">
-        <v>7040997</v>
+        <v>7041190</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6121,19 +6121,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6148,22 +6138,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120205368</v>
+        <v>120204104</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6176,39 +6166,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566521</v>
+        <v>566694</v>
       </c>
       <c r="R54" t="n">
-        <v>7041138</v>
+        <v>7041098</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6241,11 +6226,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6272,10 +6252,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120205154</v>
+        <v>120204205</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6284,42 +6264,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566510</v>
+        <v>566711</v>
       </c>
       <c r="R55" t="n">
-        <v>7041190</v>
+        <v>7041082</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6378,10 +6354,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120204939</v>
+        <v>120205024</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6390,42 +6366,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566566</v>
+        <v>566549</v>
       </c>
       <c r="R56" t="n">
-        <v>7041107</v>
+        <v>7041126</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6484,10 +6456,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120204358</v>
+        <v>120204797</v>
       </c>
       <c r="B57" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6496,25 +6468,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6524,10 +6496,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566663</v>
+        <v>566572</v>
       </c>
       <c r="R57" t="n">
-        <v>7041118</v>
+        <v>7041137</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6586,10 +6558,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120204056</v>
+        <v>120203123</v>
       </c>
       <c r="B58" t="n">
-        <v>92048</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6598,38 +6570,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566678</v>
+        <v>566628</v>
       </c>
       <c r="R58" t="n">
-        <v>7041077</v>
+        <v>7041063</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6688,10 +6664,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120203396</v>
+        <v>120201620</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6700,25 +6676,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6728,13 +6704,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566638</v>
+        <v>566582</v>
       </c>
       <c r="R59" t="n">
-        <v>7041075</v>
+        <v>7040944</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6761,9 +6737,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6778,22 +6764,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120201620</v>
+        <v>120204358</v>
       </c>
       <c r="B60" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6802,25 +6788,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6830,13 +6816,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566582</v>
+        <v>566663</v>
       </c>
       <c r="R60" t="n">
-        <v>7040944</v>
+        <v>7041118</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6863,19 +6849,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6890,22 +6866,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120205064</v>
+        <v>120205368</v>
       </c>
       <c r="B61" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6914,38 +6890,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566502</v>
+        <v>566521</v>
       </c>
       <c r="R61" t="n">
-        <v>7041103</v>
+        <v>7041138</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6978,6 +6959,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7004,10 +6990,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120203937</v>
+        <v>120200849</v>
       </c>
       <c r="B62" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7020,21 +7006,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7044,13 +7030,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566660</v>
+        <v>566521</v>
       </c>
       <c r="R62" t="n">
-        <v>7041078</v>
+        <v>7041283</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7077,9 +7063,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7094,22 +7095,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120205221</v>
+        <v>120203396</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7118,43 +7119,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566496</v>
+        <v>566638</v>
       </c>
       <c r="R63" t="n">
-        <v>7041192</v>
+        <v>7041075</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7187,11 +7183,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7218,10 +7209,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120202867</v>
+        <v>120204503</v>
       </c>
       <c r="B64" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7230,25 +7221,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7258,10 +7249,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566626</v>
+        <v>566603</v>
       </c>
       <c r="R64" t="n">
-        <v>7041042</v>
+        <v>7041138</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7320,10 +7311,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120205199</v>
+        <v>120205420</v>
       </c>
       <c r="B65" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7336,27 +7327,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7365,13 +7360,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566499</v>
+        <v>566583</v>
       </c>
       <c r="R65" t="n">
-        <v>7041189</v>
+        <v>7040942</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7398,14 +7393,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7420,22 +7420,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120202553</v>
+        <v>120202786</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7448,38 +7448,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566578</v>
+        <v>566623</v>
       </c>
       <c r="R66" t="n">
-        <v>7040998</v>
+        <v>7041032</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7538,10 +7534,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120202824</v>
+        <v>120203571</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
+        <v>89650</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7554,21 +7550,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7578,10 +7574,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566616</v>
+        <v>566647</v>
       </c>
       <c r="R67" t="n">
-        <v>7041049</v>
+        <v>7041053</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7640,10 +7636,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120204153</v>
+        <v>120205192</v>
       </c>
       <c r="B68" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7652,38 +7648,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566671</v>
+        <v>566499</v>
       </c>
       <c r="R68" t="n">
-        <v>7041071</v>
+        <v>7041186</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7716,6 +7717,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7742,10 +7748,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120204958</v>
+        <v>120202642</v>
       </c>
       <c r="B69" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7758,21 +7764,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7782,10 +7788,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566564</v>
+        <v>566590</v>
       </c>
       <c r="R69" t="n">
-        <v>7041107</v>
+        <v>7041023</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7844,10 +7850,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120202733</v>
+        <v>120204980</v>
       </c>
       <c r="B70" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7860,21 +7866,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7884,10 +7890,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566567</v>
+        <v>566561</v>
       </c>
       <c r="R70" t="n">
-        <v>7041052</v>
+        <v>7041107</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7946,10 +7952,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120200809</v>
+        <v>120202755</v>
       </c>
       <c r="B71" t="n">
-        <v>56524</v>
+        <v>91023</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7958,46 +7964,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566509</v>
+        <v>566572</v>
       </c>
       <c r="R71" t="n">
-        <v>7041308</v>
+        <v>7041055</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8024,19 +8025,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8051,22 +8042,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120201231</v>
+        <v>120203962</v>
       </c>
       <c r="B72" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8079,21 +8070,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8103,13 +8094,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566502</v>
+        <v>566665</v>
       </c>
       <c r="R72" t="n">
-        <v>7041017</v>
+        <v>7041086</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8136,24 +8127,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8168,22 +8144,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120205278</v>
+        <v>120204945</v>
       </c>
       <c r="B73" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8192,42 +8168,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566528</v>
+        <v>566565</v>
       </c>
       <c r="R73" t="n">
-        <v>7041117</v>
+        <v>7041107</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8286,10 +8258,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120201767</v>
+        <v>120201350</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8302,21 +8274,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8326,10 +8298,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566610</v>
+        <v>566534</v>
       </c>
       <c r="R74" t="n">
-        <v>7040928</v>
+        <v>7040990</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8361,7 +8333,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8371,12 +8343,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8403,10 +8370,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120205192</v>
+        <v>120202811</v>
       </c>
       <c r="B75" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8415,43 +8382,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566499</v>
+        <v>566616</v>
       </c>
       <c r="R75" t="n">
-        <v>7041186</v>
+        <v>7041049</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8484,11 +8446,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8515,10 +8472,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120202622</v>
+        <v>120204267</v>
       </c>
       <c r="B76" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8531,21 +8488,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8555,10 +8512,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566590</v>
+        <v>566695</v>
       </c>
       <c r="R76" t="n">
-        <v>7041027</v>
+        <v>7041080</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8617,10 +8574,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120204567</v>
+        <v>120202492</v>
       </c>
       <c r="B77" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8629,38 +8586,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566612</v>
+        <v>566568</v>
       </c>
       <c r="R77" t="n">
-        <v>7041175</v>
+        <v>7041045</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8719,10 +8680,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120205179</v>
+        <v>120204507</v>
       </c>
       <c r="B78" t="n">
-        <v>90545</v>
+        <v>79160</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8731,25 +8692,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8759,10 +8720,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566503</v>
+        <v>566602</v>
       </c>
       <c r="R78" t="n">
-        <v>7041183</v>
+        <v>7041134</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8821,10 +8782,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120204980</v>
+        <v>120200869</v>
       </c>
       <c r="B79" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8837,21 +8798,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8861,13 +8822,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566561</v>
+        <v>566512</v>
       </c>
       <c r="R79" t="n">
-        <v>7041107</v>
+        <v>7041220</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8894,9 +8855,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8911,22 +8882,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120203004</v>
+        <v>120201661</v>
       </c>
       <c r="B80" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8939,21 +8910,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8963,13 +8934,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566624</v>
+        <v>566582</v>
       </c>
       <c r="R80" t="n">
-        <v>7041079</v>
+        <v>7040944</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8996,9 +8967,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9013,22 +8994,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120205323</v>
+        <v>120205398</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9041,21 +9022,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9065,13 +9046,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566528</v>
+        <v>566613</v>
       </c>
       <c r="R81" t="n">
-        <v>7041117</v>
+        <v>7040940</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9098,9 +9079,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9115,22 +9106,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120202727</v>
+        <v>120201983</v>
       </c>
       <c r="B82" t="n">
-        <v>90864</v>
+        <v>57473</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9143,37 +9134,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566577</v>
+        <v>566636</v>
       </c>
       <c r="R82" t="n">
-        <v>7041064</v>
+        <v>7040903</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9200,9 +9196,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9217,22 +9223,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120204205</v>
+        <v>120205278</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9241,38 +9247,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566711</v>
+        <v>566528</v>
       </c>
       <c r="R83" t="n">
-        <v>7041082</v>
+        <v>7041117</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9331,10 +9341,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120205511</v>
+        <v>120202697</v>
       </c>
       <c r="B84" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9347,39 +9357,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566509</v>
+        <v>566589</v>
       </c>
       <c r="R84" t="n">
-        <v>7041097</v>
+        <v>7041075</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9412,11 +9417,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9443,10 +9443,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120204797</v>
+        <v>120202297</v>
       </c>
       <c r="B85" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9455,25 +9455,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566572</v>
+        <v>566551</v>
       </c>
       <c r="R85" t="n">
-        <v>7041137</v>
+        <v>7040999</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -3525,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120204013</v>
+        <v>120204567</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3537,25 +3537,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566666</v>
+        <v>566612</v>
       </c>
       <c r="R29" t="n">
-        <v>7041066</v>
+        <v>7041175</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3627,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120204567</v>
+        <v>120204013</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,25 +3639,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566612</v>
+        <v>566666</v>
       </c>
       <c r="R30" t="n">
-        <v>7041175</v>
+        <v>7041066</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3729,10 +3729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120202768</v>
+        <v>120201231</v>
       </c>
       <c r="B31" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566600</v>
+        <v>566502</v>
       </c>
       <c r="R31" t="n">
-        <v>7041007</v>
+        <v>7041017</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3802,9 +3802,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,19 +3834,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120203937</v>
+        <v>120202768</v>
       </c>
       <c r="B32" t="n">
         <v>90864</v>
@@ -3871,10 +3886,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566660</v>
+        <v>566600</v>
       </c>
       <c r="R32" t="n">
-        <v>7041078</v>
+        <v>7041007</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3933,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120201231</v>
+        <v>120203937</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3949,21 +3964,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3973,13 +3988,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566502</v>
+        <v>566660</v>
       </c>
       <c r="R33" t="n">
-        <v>7041017</v>
+        <v>7041078</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4006,24 +4021,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4038,22 +4038,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120202824</v>
+        <v>120202289</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566616</v>
+        <v>566546</v>
       </c>
       <c r="R34" t="n">
-        <v>7041049</v>
+        <v>7041010</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120202647</v>
+        <v>120202622</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,42 +4164,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566587</v>
+        <v>566590</v>
       </c>
       <c r="R35" t="n">
-        <v>7041021</v>
+        <v>7041027</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4258,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120202622</v>
+        <v>120205323</v>
       </c>
       <c r="B36" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,25 +4266,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4298,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566590</v>
+        <v>566528</v>
       </c>
       <c r="R36" t="n">
-        <v>7041027</v>
+        <v>7041117</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4360,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120201767</v>
+        <v>120202824</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4376,21 +4372,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4400,13 +4396,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566610</v>
+        <v>566616</v>
       </c>
       <c r="R37" t="n">
-        <v>7040928</v>
+        <v>7041049</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4433,24 +4429,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4465,22 +4446,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120202289</v>
+        <v>120205148</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4489,25 +4470,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4517,10 +4498,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566546</v>
+        <v>566529</v>
       </c>
       <c r="R38" t="n">
-        <v>7041010</v>
+        <v>7041203</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4579,10 +4560,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120205323</v>
+        <v>120205138</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4595,21 +4576,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4619,10 +4600,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566528</v>
+        <v>566529</v>
       </c>
       <c r="R39" t="n">
-        <v>7041117</v>
+        <v>7041203</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4681,10 +4662,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120205148</v>
+        <v>120201767</v>
       </c>
       <c r="B40" t="n">
-        <v>79652</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4693,25 +4674,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4721,13 +4702,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566529</v>
+        <v>566610</v>
       </c>
       <c r="R40" t="n">
-        <v>7041203</v>
+        <v>7040928</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4754,9 +4735,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4771,22 +4767,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120205138</v>
+        <v>120202647</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4795,38 +4791,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566529</v>
+        <v>566587</v>
       </c>
       <c r="R41" t="n">
-        <v>7041203</v>
+        <v>7041021</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -9235,10 +9235,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120205278</v>
+        <v>120202697</v>
       </c>
       <c r="B83" t="n">
-        <v>97930</v>
+        <v>90594</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9247,42 +9247,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566528</v>
+        <v>566589</v>
       </c>
       <c r="R83" t="n">
-        <v>7041117</v>
+        <v>7041075</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9341,10 +9337,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120202697</v>
+        <v>120202297</v>
       </c>
       <c r="B84" t="n">
-        <v>90594</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9357,21 +9353,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9381,10 +9377,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566589</v>
+        <v>566551</v>
       </c>
       <c r="R84" t="n">
-        <v>7041075</v>
+        <v>7040999</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9443,10 +9439,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120202297</v>
+        <v>120205278</v>
       </c>
       <c r="B85" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9455,38 +9451,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566551</v>
+        <v>566528</v>
       </c>
       <c r="R85" t="n">
-        <v>7040999</v>
+        <v>7041117</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120204862</v>
+        <v>120202755</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566579</v>
+        <v>566572</v>
       </c>
       <c r="R2" t="n">
-        <v>7041130</v>
+        <v>7041055</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120205468</v>
+        <v>120204901</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566498</v>
+        <v>566567</v>
       </c>
       <c r="R3" t="n">
-        <v>7041093</v>
+        <v>7041107</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204476</v>
+        <v>120204816</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566635</v>
+        <v>566572</v>
       </c>
       <c r="R4" t="n">
         <v>7041139</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202674</v>
+        <v>120204507</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566584</v>
+        <v>566602</v>
       </c>
       <c r="R5" t="n">
-        <v>7041103</v>
+        <v>7041134</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202239</v>
+        <v>120202727</v>
       </c>
       <c r="B6" t="n">
-        <v>90742</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566526</v>
+        <v>566577</v>
       </c>
       <c r="R6" t="n">
-        <v>7041005</v>
+        <v>7041064</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204816</v>
+        <v>120200849</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566572</v>
+        <v>566521</v>
       </c>
       <c r="R7" t="n">
-        <v>7041139</v>
+        <v>7041283</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,9 +1258,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120203004</v>
+        <v>120205148</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566624</v>
+        <v>566529</v>
       </c>
       <c r="R8" t="n">
-        <v>7041079</v>
+        <v>7041203</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120204807</v>
+        <v>120205154</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,38 +1416,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566575</v>
+        <v>566510</v>
       </c>
       <c r="R9" t="n">
-        <v>7041141</v>
+        <v>7041190</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120203078</v>
+        <v>120204358</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566621</v>
+        <v>566663</v>
       </c>
       <c r="R10" t="n">
-        <v>7041057</v>
+        <v>7041118</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120204153</v>
+        <v>120200809</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>56524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,41 +1624,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566671</v>
+        <v>566509</v>
       </c>
       <c r="R11" t="n">
-        <v>7041071</v>
+        <v>7041308</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,9 +1690,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,22 +1717,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120205221</v>
+        <v>120203571</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>89650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,39 +1745,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566496</v>
+        <v>566647</v>
       </c>
       <c r="R12" t="n">
-        <v>7041192</v>
+        <v>7041053</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1776,11 +1805,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120204056</v>
+        <v>120205199</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,34 +1847,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566678</v>
+        <v>566499</v>
       </c>
       <c r="R13" t="n">
-        <v>7041077</v>
+        <v>7041189</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1883,6 +1912,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,7 +1943,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120205084</v>
+        <v>120202553</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1944,7 +1978,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1953,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566515</v>
+        <v>566578</v>
       </c>
       <c r="R14" t="n">
-        <v>7041125</v>
+        <v>7040998</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120205064</v>
+        <v>120205138</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,25 +2061,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566502</v>
+        <v>566529</v>
       </c>
       <c r="R15" t="n">
-        <v>7041103</v>
+        <v>7041203</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120201490</v>
+        <v>120202768</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2167,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,13 +2191,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566563</v>
+        <v>566600</v>
       </c>
       <c r="R16" t="n">
-        <v>7040951</v>
+        <v>7041007</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2190,19 +2224,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,22 +2241,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120201451</v>
+        <v>120203004</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,21 +2269,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,13 +2293,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566541</v>
+        <v>566624</v>
       </c>
       <c r="R17" t="n">
-        <v>7040997</v>
+        <v>7041079</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2302,19 +2326,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,19 +2343,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120205460</v>
+        <v>120205221</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2386,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566500</v>
+        <v>566496</v>
       </c>
       <c r="R18" t="n">
-        <v>7041094</v>
+        <v>7041192</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2453,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120205179</v>
+        <v>120201231</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,25 +2479,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2493,13 +2507,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566503</v>
+        <v>566502</v>
       </c>
       <c r="R19" t="n">
-        <v>7041183</v>
+        <v>7041017</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,9 +2540,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,22 +2572,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120205511</v>
+        <v>120204939</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,31 +2596,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2600,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566509</v>
+        <v>566566</v>
       </c>
       <c r="R20" t="n">
-        <v>7041097</v>
+        <v>7041107</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2636,11 +2664,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2667,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120200809</v>
+        <v>120202571</v>
       </c>
       <c r="B21" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,31 +2702,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2712,13 +2734,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566509</v>
+        <v>566582</v>
       </c>
       <c r="R21" t="n">
-        <v>7041308</v>
+        <v>7041015</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2745,19 +2767,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,22 +2784,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120202392</v>
+        <v>120202867</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,42 +2808,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566555</v>
+        <v>566626</v>
       </c>
       <c r="R22" t="n">
-        <v>7041027</v>
+        <v>7041042</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2890,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120202867</v>
+        <v>120204503</v>
       </c>
       <c r="B23" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,25 +2910,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2930,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566626</v>
+        <v>566603</v>
       </c>
       <c r="R23" t="n">
-        <v>7041042</v>
+        <v>7041138</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2992,10 +3000,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120202853</v>
+        <v>120204116</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3004,25 +3012,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3032,10 +3040,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566624</v>
+        <v>566691</v>
       </c>
       <c r="R24" t="n">
-        <v>7041060</v>
+        <v>7041096</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3094,10 +3102,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120200832</v>
+        <v>120204013</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3110,42 +3118,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566507</v>
+        <v>566666</v>
       </c>
       <c r="R25" t="n">
-        <v>7041231</v>
+        <v>7041066</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3172,19 +3175,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3199,22 +3192,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120202553</v>
+        <v>120204807</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3223,42 +3216,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566578</v>
+        <v>566575</v>
       </c>
       <c r="R26" t="n">
-        <v>7040998</v>
+        <v>7041141</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3317,7 +3306,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120204212</v>
+        <v>120202392</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3352,7 +3341,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3361,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566711</v>
+        <v>566555</v>
       </c>
       <c r="R27" t="n">
-        <v>7041082</v>
+        <v>7041027</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3423,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120204958</v>
+        <v>120205278</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,38 +3424,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566564</v>
+        <v>566528</v>
       </c>
       <c r="R28" t="n">
-        <v>7041107</v>
+        <v>7041117</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3525,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120204567</v>
+        <v>120202733</v>
       </c>
       <c r="B29" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3537,25 +3530,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3565,10 +3558,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566612</v>
+        <v>566567</v>
       </c>
       <c r="R29" t="n">
-        <v>7041175</v>
+        <v>7041052</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3627,10 +3620,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120204013</v>
+        <v>120202492</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,38 +3632,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566666</v>
+        <v>566568</v>
       </c>
       <c r="R30" t="n">
-        <v>7041066</v>
+        <v>7041045</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3729,10 +3726,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120201231</v>
+        <v>120205084</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3741,41 +3738,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566502</v>
+        <v>566515</v>
       </c>
       <c r="R31" t="n">
-        <v>7041017</v>
+        <v>7041125</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3802,24 +3803,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3834,22 +3820,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202768</v>
+        <v>120202647</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,38 +3844,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566600</v>
+        <v>566587</v>
       </c>
       <c r="R32" t="n">
-        <v>7041007</v>
+        <v>7041021</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3948,10 +3938,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120203937</v>
+        <v>120203396</v>
       </c>
       <c r="B33" t="n">
-        <v>90864</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,25 +3950,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3988,10 +3978,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566660</v>
+        <v>566638</v>
       </c>
       <c r="R33" t="n">
-        <v>7041078</v>
+        <v>7041075</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4050,10 +4040,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120202289</v>
+        <v>120202853</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4066,21 +4056,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,10 +4080,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566546</v>
+        <v>566624</v>
       </c>
       <c r="R34" t="n">
-        <v>7041010</v>
+        <v>7041060</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4152,7 +4142,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120202622</v>
+        <v>120204862</v>
       </c>
       <c r="B35" t="n">
         <v>90545</v>
@@ -4192,10 +4182,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566590</v>
+        <v>566579</v>
       </c>
       <c r="R35" t="n">
-        <v>7041027</v>
+        <v>7041130</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4254,10 +4244,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120205323</v>
+        <v>120202289</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,21 +4260,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,10 +4284,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566528</v>
+        <v>566546</v>
       </c>
       <c r="R36" t="n">
-        <v>7041117</v>
+        <v>7041010</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4356,10 +4346,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120202824</v>
+        <v>120204945</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4372,21 +4362,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4396,10 +4386,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566616</v>
+        <v>566565</v>
       </c>
       <c r="R37" t="n">
-        <v>7041049</v>
+        <v>7041107</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4458,10 +4448,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120205148</v>
+        <v>120201350</v>
       </c>
       <c r="B38" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,25 +4460,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4498,13 +4488,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566529</v>
+        <v>566534</v>
       </c>
       <c r="R38" t="n">
-        <v>7041203</v>
+        <v>7040990</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4531,9 +4521,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4548,22 +4548,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120205138</v>
+        <v>120201767</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566529</v>
+        <v>566610</v>
       </c>
       <c r="R39" t="n">
-        <v>7041203</v>
+        <v>7040928</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4633,9 +4633,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4650,19 +4665,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120201767</v>
+        <v>120205511</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4696,19 +4711,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566610</v>
+        <v>566509</v>
       </c>
       <c r="R40" t="n">
-        <v>7040928</v>
+        <v>7041097</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4735,24 +4755,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4767,19 +4777,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120202647</v>
+        <v>120205312</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -4814,7 +4824,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4823,13 +4838,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566587</v>
+        <v>566618</v>
       </c>
       <c r="R41" t="n">
-        <v>7041021</v>
+        <v>7040939</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4856,9 +4871,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4873,22 +4898,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120202727</v>
+        <v>120204476</v>
       </c>
       <c r="B42" t="n">
-        <v>90864</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4901,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566577</v>
+        <v>566635</v>
       </c>
       <c r="R42" t="n">
-        <v>7041064</v>
+        <v>7041139</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4987,10 +5012,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120204901</v>
+        <v>120204104</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>78278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5003,21 +5028,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566567</v>
+        <v>566694</v>
       </c>
       <c r="R43" t="n">
-        <v>7041107</v>
+        <v>7041098</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5089,10 +5114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120204405</v>
+        <v>120202697</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>90594</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5101,25 +5126,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566637</v>
+        <v>566589</v>
       </c>
       <c r="R44" t="n">
-        <v>7041131</v>
+        <v>7041075</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5191,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120202733</v>
+        <v>120201620</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,25 +5228,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,13 +5256,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566567</v>
+        <v>566582</v>
       </c>
       <c r="R45" t="n">
-        <v>7041052</v>
+        <v>7040944</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5264,9 +5289,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5281,22 +5316,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120204835</v>
+        <v>120202674</v>
       </c>
       <c r="B46" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5340,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5368,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566561</v>
+        <v>566584</v>
       </c>
       <c r="R46" t="n">
-        <v>7041134</v>
+        <v>7041103</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5395,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120204116</v>
+        <v>120203123</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,38 +5442,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566691</v>
+        <v>566628</v>
       </c>
       <c r="R47" t="n">
-        <v>7041096</v>
+        <v>7041063</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5497,10 +5536,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120204492</v>
+        <v>120204212</v>
       </c>
       <c r="B48" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,38 +5548,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566608</v>
+        <v>566711</v>
       </c>
       <c r="R48" t="n">
-        <v>7041149</v>
+        <v>7041082</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5599,10 +5642,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120205199</v>
+        <v>120204205</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,39 +5658,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566499</v>
+        <v>566711</v>
       </c>
       <c r="R49" t="n">
-        <v>7041189</v>
+        <v>7041082</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5680,11 +5718,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5711,10 +5744,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120205312</v>
+        <v>120204567</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5723,50 +5756,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566618</v>
+        <v>566612</v>
       </c>
       <c r="R50" t="n">
-        <v>7040939</v>
+        <v>7041175</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5793,19 +5817,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5820,22 +5834,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120204939</v>
+        <v>120205024</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5844,42 +5858,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566566</v>
+        <v>566549</v>
       </c>
       <c r="R51" t="n">
-        <v>7041107</v>
+        <v>7041126</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5938,10 +5948,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120202571</v>
+        <v>120201490</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5950,45 +5960,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566582</v>
+        <v>566563</v>
       </c>
       <c r="R52" t="n">
-        <v>7041015</v>
+        <v>7040951</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6015,9 +6021,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6032,22 +6048,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120205154</v>
+        <v>120205420</v>
       </c>
       <c r="B53" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6056,30 +6072,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6088,13 +6109,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566510</v>
+        <v>566583</v>
       </c>
       <c r="R53" t="n">
-        <v>7041190</v>
+        <v>7040942</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6121,9 +6142,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6138,22 +6169,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120204104</v>
+        <v>120202786</v>
       </c>
       <c r="B54" t="n">
-        <v>78278</v>
+        <v>91023</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6162,25 +6193,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6190,10 +6221,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566694</v>
+        <v>566623</v>
       </c>
       <c r="R54" t="n">
-        <v>7041098</v>
+        <v>7041032</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6252,10 +6283,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120204205</v>
+        <v>120202297</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6268,21 +6299,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6292,10 +6323,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566711</v>
+        <v>566551</v>
       </c>
       <c r="R55" t="n">
-        <v>7041082</v>
+        <v>7040999</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6354,10 +6385,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120205024</v>
+        <v>120204797</v>
       </c>
       <c r="B56" t="n">
-        <v>90545</v>
+        <v>96885</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6370,21 +6401,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6394,10 +6425,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566549</v>
+        <v>566572</v>
       </c>
       <c r="R56" t="n">
-        <v>7041126</v>
+        <v>7041137</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6456,10 +6487,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120204797</v>
+        <v>120205460</v>
       </c>
       <c r="B57" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6468,38 +6499,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566572</v>
+        <v>566500</v>
       </c>
       <c r="R57" t="n">
-        <v>7041137</v>
+        <v>7041094</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6532,6 +6568,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6558,10 +6599,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120203123</v>
+        <v>120201661</v>
       </c>
       <c r="B58" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6570,45 +6611,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566628</v>
+        <v>566582</v>
       </c>
       <c r="R58" t="n">
-        <v>7041063</v>
+        <v>7040944</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6635,9 +6672,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6652,22 +6699,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120201620</v>
+        <v>120201451</v>
       </c>
       <c r="B59" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6676,25 +6723,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6704,10 +6751,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566582</v>
+        <v>566541</v>
       </c>
       <c r="R59" t="n">
-        <v>7040944</v>
+        <v>7040997</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6739,7 +6786,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6749,7 +6796,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6776,10 +6823,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120204358</v>
+        <v>120205398</v>
       </c>
       <c r="B60" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6792,21 +6839,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6816,13 +6863,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566663</v>
+        <v>566613</v>
       </c>
       <c r="R60" t="n">
-        <v>7041118</v>
+        <v>7040940</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6849,9 +6896,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6866,22 +6923,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120205368</v>
+        <v>120205468</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6894,39 +6951,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566521</v>
+        <v>566498</v>
       </c>
       <c r="R61" t="n">
-        <v>7041138</v>
+        <v>7041093</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6959,11 +7011,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6990,10 +7037,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120200849</v>
+        <v>120204835</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7002,25 +7049,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7030,13 +7077,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566521</v>
+        <v>566561</v>
       </c>
       <c r="R62" t="n">
-        <v>7041283</v>
+        <v>7041134</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7063,24 +7110,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7095,19 +7127,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120203396</v>
+        <v>120204267</v>
       </c>
       <c r="B63" t="n">
         <v>91858</v>
@@ -7147,10 +7179,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566638</v>
+        <v>566695</v>
       </c>
       <c r="R63" t="n">
-        <v>7041075</v>
+        <v>7041080</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7209,10 +7241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120204503</v>
+        <v>120205192</v>
       </c>
       <c r="B64" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7225,34 +7257,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566603</v>
+        <v>566499</v>
       </c>
       <c r="R64" t="n">
-        <v>7041138</v>
+        <v>7041186</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7285,6 +7322,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7311,10 +7353,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120205420</v>
+        <v>120200869</v>
       </c>
       <c r="B65" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7327,43 +7369,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566583</v>
+        <v>566512</v>
       </c>
       <c r="R65" t="n">
-        <v>7040942</v>
+        <v>7041220</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7395,7 +7428,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7405,7 +7438,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7432,10 +7465,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120202786</v>
+        <v>120204056</v>
       </c>
       <c r="B66" t="n">
-        <v>91023</v>
+        <v>92048</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7444,25 +7477,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7472,10 +7505,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566623</v>
+        <v>566678</v>
       </c>
       <c r="R66" t="n">
-        <v>7041032</v>
+        <v>7041077</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7534,10 +7567,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120203571</v>
+        <v>120204980</v>
       </c>
       <c r="B67" t="n">
-        <v>89650</v>
+        <v>90598</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7550,21 +7583,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7574,10 +7607,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566647</v>
+        <v>566561</v>
       </c>
       <c r="R67" t="n">
-        <v>7041053</v>
+        <v>7041107</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7636,10 +7669,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120205192</v>
+        <v>120204405</v>
       </c>
       <c r="B68" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7648,43 +7681,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566499</v>
+        <v>566637</v>
       </c>
       <c r="R68" t="n">
-        <v>7041186</v>
+        <v>7041131</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7717,11 +7745,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7748,10 +7771,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120202642</v>
+        <v>120203962</v>
       </c>
       <c r="B69" t="n">
-        <v>74654</v>
+        <v>79160</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7764,21 +7787,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7788,10 +7811,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566590</v>
+        <v>566665</v>
       </c>
       <c r="R69" t="n">
-        <v>7041023</v>
+        <v>7041086</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7850,10 +7873,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120204980</v>
+        <v>120202239</v>
       </c>
       <c r="B70" t="n">
-        <v>90598</v>
+        <v>90742</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7866,21 +7889,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7890,10 +7913,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566561</v>
+        <v>566526</v>
       </c>
       <c r="R70" t="n">
-        <v>7041107</v>
+        <v>7041005</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7952,10 +7975,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120202755</v>
+        <v>120202811</v>
       </c>
       <c r="B71" t="n">
-        <v>91023</v>
+        <v>90923</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7968,21 +7991,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>2062</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7992,10 +8015,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566572</v>
+        <v>566616</v>
       </c>
       <c r="R71" t="n">
-        <v>7041055</v>
+        <v>7041049</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8054,10 +8077,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120203962</v>
+        <v>120202622</v>
       </c>
       <c r="B72" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8066,25 +8089,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8094,10 +8117,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566665</v>
+        <v>566590</v>
       </c>
       <c r="R72" t="n">
-        <v>7041086</v>
+        <v>7041027</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8156,10 +8179,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120204945</v>
+        <v>120205064</v>
       </c>
       <c r="B73" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8168,25 +8191,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8196,10 +8219,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566565</v>
+        <v>566502</v>
       </c>
       <c r="R73" t="n">
-        <v>7041107</v>
+        <v>7041103</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,10 +8281,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120201350</v>
+        <v>120200832</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8274,34 +8297,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566534</v>
+        <v>566507</v>
       </c>
       <c r="R74" t="n">
-        <v>7040990</v>
+        <v>7041231</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8333,7 +8361,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8343,7 +8371,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8358,22 +8386,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120202811</v>
+        <v>120201983</v>
       </c>
       <c r="B75" t="n">
-        <v>90923</v>
+        <v>57473</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8382,41 +8410,46 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2062</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566616</v>
+        <v>566636</v>
       </c>
       <c r="R75" t="n">
-        <v>7041049</v>
+        <v>7040903</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8443,9 +8476,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8460,22 +8503,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120204267</v>
+        <v>120205323</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8484,25 +8527,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8512,10 +8555,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566695</v>
+        <v>566528</v>
       </c>
       <c r="R76" t="n">
-        <v>7041080</v>
+        <v>7041117</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8574,10 +8617,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120202492</v>
+        <v>120203937</v>
       </c>
       <c r="B77" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8586,42 +8629,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566568</v>
+        <v>566660</v>
       </c>
       <c r="R77" t="n">
-        <v>7041045</v>
+        <v>7041078</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8680,10 +8719,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120204507</v>
+        <v>120205179</v>
       </c>
       <c r="B78" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8692,25 +8731,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8720,10 +8759,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566602</v>
+        <v>566503</v>
       </c>
       <c r="R78" t="n">
-        <v>7041134</v>
+        <v>7041183</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8782,10 +8821,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120200869</v>
+        <v>120205368</v>
       </c>
       <c r="B79" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8798,37 +8837,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566512</v>
+        <v>566521</v>
       </c>
       <c r="R79" t="n">
-        <v>7041220</v>
+        <v>7041138</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8855,19 +8899,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8882,22 +8921,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120201661</v>
+        <v>120203078</v>
       </c>
       <c r="B80" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8910,21 +8949,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8934,13 +8973,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566582</v>
+        <v>566621</v>
       </c>
       <c r="R80" t="n">
-        <v>7040944</v>
+        <v>7041057</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8967,19 +9006,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8994,22 +9023,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120205398</v>
+        <v>120204958</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9022,21 +9051,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9046,13 +9075,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566613</v>
+        <v>566564</v>
       </c>
       <c r="R81" t="n">
-        <v>7040940</v>
+        <v>7041107</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9079,19 +9108,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9106,22 +9125,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120201983</v>
+        <v>120204492</v>
       </c>
       <c r="B82" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9134,42 +9153,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566636</v>
+        <v>566608</v>
       </c>
       <c r="R82" t="n">
-        <v>7040903</v>
+        <v>7041149</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9196,19 +9210,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9223,22 +9227,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120202697</v>
+        <v>120202642</v>
       </c>
       <c r="B83" t="n">
-        <v>90594</v>
+        <v>74654</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9251,21 +9255,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9275,10 +9279,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566589</v>
+        <v>566590</v>
       </c>
       <c r="R83" t="n">
-        <v>7041075</v>
+        <v>7041023</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9337,7 +9341,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120202297</v>
+        <v>120202824</v>
       </c>
       <c r="B84" t="n">
         <v>90580</v>
@@ -9377,10 +9381,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566551</v>
+        <v>566616</v>
       </c>
       <c r="R84" t="n">
-        <v>7040999</v>
+        <v>7041049</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9439,10 +9443,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120205278</v>
+        <v>120204153</v>
       </c>
       <c r="B85" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9451,42 +9455,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566528</v>
+        <v>566671</v>
       </c>
       <c r="R85" t="n">
-        <v>7041117</v>
+        <v>7041071</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202755</v>
+        <v>120205064</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566572</v>
+        <v>566502</v>
       </c>
       <c r="R2" t="n">
-        <v>7041055</v>
+        <v>7041103</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120204901</v>
+        <v>120202755</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566567</v>
+        <v>566572</v>
       </c>
       <c r="R3" t="n">
-        <v>7041107</v>
+        <v>7041055</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204816</v>
+        <v>120204358</v>
       </c>
       <c r="B4" t="n">
         <v>90580</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566572</v>
+        <v>566663</v>
       </c>
       <c r="R4" t="n">
-        <v>7041139</v>
+        <v>7041118</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204507</v>
+        <v>120205192</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566602</v>
+        <v>566499</v>
       </c>
       <c r="R5" t="n">
-        <v>7041134</v>
+        <v>7041186</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120202727</v>
+        <v>120205199</v>
       </c>
       <c r="B6" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566577</v>
+        <v>566499</v>
       </c>
       <c r="R6" t="n">
-        <v>7041064</v>
+        <v>7041189</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120200849</v>
+        <v>120204205</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566521</v>
+        <v>566711</v>
       </c>
       <c r="R7" t="n">
-        <v>7041283</v>
+        <v>7041082</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,24 +1278,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120205148</v>
+        <v>120204958</v>
       </c>
       <c r="B8" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566529</v>
+        <v>566564</v>
       </c>
       <c r="R8" t="n">
-        <v>7041203</v>
+        <v>7041107</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120205154</v>
+        <v>120202239</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>90742</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,42 +1421,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566510</v>
+        <v>566526</v>
       </c>
       <c r="R9" t="n">
-        <v>7041190</v>
+        <v>7041005</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1510,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120204358</v>
+        <v>120202733</v>
       </c>
       <c r="B10" t="n">
         <v>90580</v>
@@ -1550,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566663</v>
+        <v>566567</v>
       </c>
       <c r="R10" t="n">
-        <v>7041118</v>
+        <v>7041052</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1612,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120200809</v>
+        <v>120203937</v>
       </c>
       <c r="B11" t="n">
-        <v>56524</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,42 +1629,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566509</v>
+        <v>566660</v>
       </c>
       <c r="R11" t="n">
-        <v>7041308</v>
+        <v>7041078</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,19 +1686,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120203571</v>
+        <v>120205312</v>
       </c>
       <c r="B12" t="n">
-        <v>89650</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,41 +1727,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566647</v>
+        <v>566618</v>
       </c>
       <c r="R12" t="n">
-        <v>7041053</v>
+        <v>7040939</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,9 +1797,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,22 +1824,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120205199</v>
+        <v>120202647</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,31 +1848,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1876,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566499</v>
+        <v>566587</v>
       </c>
       <c r="R13" t="n">
-        <v>7041189</v>
+        <v>7041021</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,11 +1916,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120202553</v>
+        <v>120204507</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,42 +1954,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566578</v>
+        <v>566602</v>
       </c>
       <c r="R14" t="n">
-        <v>7040998</v>
+        <v>7041134</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2049,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120205138</v>
+        <v>120204104</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,21 +2060,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566529</v>
+        <v>566694</v>
       </c>
       <c r="R15" t="n">
-        <v>7041203</v>
+        <v>7041098</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2151,10 +2146,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120202768</v>
+        <v>120203962</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2167,21 +2162,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2191,10 +2186,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566600</v>
+        <v>566665</v>
       </c>
       <c r="R16" t="n">
-        <v>7041007</v>
+        <v>7041086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2253,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120203004</v>
+        <v>120205511</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2269,34 +2264,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566624</v>
+        <v>566509</v>
       </c>
       <c r="R17" t="n">
-        <v>7041079</v>
+        <v>7041097</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2329,6 +2329,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120205221</v>
+        <v>120204116</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2367,43 +2372,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566496</v>
+        <v>566691</v>
       </c>
       <c r="R18" t="n">
-        <v>7041192</v>
+        <v>7041096</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2436,11 +2436,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2467,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120201231</v>
+        <v>120205179</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,25 +2474,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2507,13 +2502,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566502</v>
+        <v>566503</v>
       </c>
       <c r="R19" t="n">
-        <v>7041017</v>
+        <v>7041183</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2540,24 +2535,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2572,22 +2552,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204939</v>
+        <v>120204492</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,42 +2576,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566566</v>
+        <v>566608</v>
       </c>
       <c r="R20" t="n">
-        <v>7041107</v>
+        <v>7041149</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2690,7 +2666,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120202571</v>
+        <v>120205278</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2725,7 +2701,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2734,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566582</v>
+        <v>566528</v>
       </c>
       <c r="R21" t="n">
-        <v>7041015</v>
+        <v>7041117</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2796,10 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120202867</v>
+        <v>120202553</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,38 +2784,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566626</v>
+        <v>566578</v>
       </c>
       <c r="R22" t="n">
-        <v>7041042</v>
+        <v>7040998</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2898,10 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120204503</v>
+        <v>120203004</v>
       </c>
       <c r="B23" t="n">
-        <v>78279</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2914,21 +2894,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2938,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566603</v>
+        <v>566624</v>
       </c>
       <c r="R23" t="n">
-        <v>7041138</v>
+        <v>7041079</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3000,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120204116</v>
+        <v>120204503</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,25 +2992,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3040,10 +3020,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566691</v>
+        <v>566603</v>
       </c>
       <c r="R24" t="n">
-        <v>7041096</v>
+        <v>7041138</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3102,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120204013</v>
+        <v>120200849</v>
       </c>
       <c r="B25" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3118,21 +3098,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3142,13 +3122,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566666</v>
+        <v>566521</v>
       </c>
       <c r="R25" t="n">
-        <v>7041066</v>
+        <v>7041283</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3175,9 +3155,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3192,22 +3187,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120204807</v>
+        <v>120202492</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3216,38 +3211,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566575</v>
+        <v>566568</v>
       </c>
       <c r="R26" t="n">
-        <v>7041141</v>
+        <v>7041045</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3306,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120202392</v>
+        <v>120202853</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3318,42 +3317,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566555</v>
+        <v>566624</v>
       </c>
       <c r="R27" t="n">
-        <v>7041027</v>
+        <v>7041060</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3412,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120205278</v>
+        <v>120205138</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,42 +3419,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566528</v>
+        <v>566529</v>
       </c>
       <c r="R28" t="n">
-        <v>7041117</v>
+        <v>7041203</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3518,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120202733</v>
+        <v>120203396</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,25 +3521,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3558,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566567</v>
+        <v>566638</v>
       </c>
       <c r="R29" t="n">
-        <v>7041052</v>
+        <v>7041075</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3620,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120202492</v>
+        <v>120204807</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3632,42 +3623,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566568</v>
+        <v>566575</v>
       </c>
       <c r="R30" t="n">
-        <v>7041045</v>
+        <v>7041141</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3726,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120205084</v>
+        <v>120200832</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3738,30 +3725,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3770,13 +3758,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566515</v>
+        <v>566507</v>
       </c>
       <c r="R31" t="n">
-        <v>7041125</v>
+        <v>7041231</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3803,9 +3791,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3820,19 +3818,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202647</v>
+        <v>120204212</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3867,7 +3865,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3876,10 +3874,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566587</v>
+        <v>566711</v>
       </c>
       <c r="R32" t="n">
-        <v>7041021</v>
+        <v>7041082</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3938,10 +3936,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120203396</v>
+        <v>120202786</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3950,25 +3948,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3978,10 +3976,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566638</v>
+        <v>566623</v>
       </c>
       <c r="R33" t="n">
-        <v>7041075</v>
+        <v>7041032</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4040,10 +4038,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120202853</v>
+        <v>120203571</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>89650</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4056,21 +4054,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4080,10 +4078,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566624</v>
+        <v>566647</v>
       </c>
       <c r="R34" t="n">
-        <v>7041060</v>
+        <v>7041053</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4142,10 +4140,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120204862</v>
+        <v>120202811</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>90923</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,25 +4152,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4182,10 +4180,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566579</v>
+        <v>566616</v>
       </c>
       <c r="R35" t="n">
-        <v>7041130</v>
+        <v>7041049</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4244,10 +4242,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120202289</v>
+        <v>120204797</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4256,25 +4254,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4284,10 +4282,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566546</v>
+        <v>566572</v>
       </c>
       <c r="R36" t="n">
-        <v>7041010</v>
+        <v>7041137</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4448,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120201350</v>
+        <v>120202727</v>
       </c>
       <c r="B38" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4464,21 +4462,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4488,13 +4486,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566534</v>
+        <v>566577</v>
       </c>
       <c r="R38" t="n">
-        <v>7040990</v>
+        <v>7041064</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4521,19 +4519,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4548,22 +4536,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120201767</v>
+        <v>120204980</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,21 +4564,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,13 +4588,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566610</v>
+        <v>566561</v>
       </c>
       <c r="R39" t="n">
-        <v>7040928</v>
+        <v>7041107</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4633,24 +4621,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4665,22 +4638,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120205511</v>
+        <v>120202867</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4689,43 +4662,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566509</v>
+        <v>566626</v>
       </c>
       <c r="R40" t="n">
-        <v>7041097</v>
+        <v>7041042</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4758,11 +4726,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4789,10 +4752,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120205312</v>
+        <v>120201231</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4801,47 +4764,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566618</v>
+        <v>566502</v>
       </c>
       <c r="R41" t="n">
-        <v>7040939</v>
+        <v>7041017</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4873,7 +4827,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4883,7 +4837,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4898,22 +4857,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120204476</v>
+        <v>120202768</v>
       </c>
       <c r="B42" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,21 +4885,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4950,10 +4909,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566635</v>
+        <v>566600</v>
       </c>
       <c r="R42" t="n">
-        <v>7041139</v>
+        <v>7041007</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5012,10 +4971,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120204104</v>
+        <v>120202297</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5028,21 +4987,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5052,10 +5011,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566694</v>
+        <v>566551</v>
       </c>
       <c r="R43" t="n">
-        <v>7041098</v>
+        <v>7040999</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5114,10 +5073,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120202697</v>
+        <v>120202622</v>
       </c>
       <c r="B44" t="n">
-        <v>90594</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5126,25 +5085,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5154,10 +5113,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566589</v>
+        <v>566590</v>
       </c>
       <c r="R44" t="n">
-        <v>7041075</v>
+        <v>7041027</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5216,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120201620</v>
+        <v>120205024</v>
       </c>
       <c r="B45" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5228,25 +5187,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5256,13 +5215,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566582</v>
+        <v>566549</v>
       </c>
       <c r="R45" t="n">
-        <v>7040944</v>
+        <v>7041126</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5289,19 +5248,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5316,19 +5265,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120202674</v>
+        <v>120202824</v>
       </c>
       <c r="B46" t="n">
         <v>90580</v>
@@ -5368,10 +5317,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566584</v>
+        <v>566616</v>
       </c>
       <c r="R46" t="n">
-        <v>7041103</v>
+        <v>7041049</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5430,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120203123</v>
+        <v>120205460</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,30 +5391,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5474,10 +5424,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566628</v>
+        <v>566500</v>
       </c>
       <c r="R47" t="n">
-        <v>7041063</v>
+        <v>7041094</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5510,6 +5460,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5536,10 +5491,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120204212</v>
+        <v>120204267</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5548,42 +5503,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566711</v>
+        <v>566695</v>
       </c>
       <c r="R48" t="n">
-        <v>7041082</v>
+        <v>7041080</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5642,10 +5593,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120204205</v>
+        <v>120204835</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5654,25 +5605,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5682,10 +5633,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566711</v>
+        <v>566561</v>
       </c>
       <c r="R49" t="n">
-        <v>7041082</v>
+        <v>7041134</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5744,10 +5695,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120204567</v>
+        <v>120205148</v>
       </c>
       <c r="B50" t="n">
-        <v>90545</v>
+        <v>79652</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5760,21 +5711,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5784,10 +5735,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566612</v>
+        <v>566529</v>
       </c>
       <c r="R50" t="n">
-        <v>7041175</v>
+        <v>7041203</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5846,10 +5797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120205024</v>
+        <v>120201451</v>
       </c>
       <c r="B51" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5858,25 +5809,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5886,13 +5837,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566549</v>
+        <v>566541</v>
       </c>
       <c r="R51" t="n">
-        <v>7041126</v>
+        <v>7040997</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5919,9 +5870,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5936,22 +5897,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120201490</v>
+        <v>120205368</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5964,37 +5925,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566563</v>
+        <v>566521</v>
       </c>
       <c r="R52" t="n">
-        <v>7040951</v>
+        <v>7041138</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6021,19 +5987,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6048,22 +6009,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120205420</v>
+        <v>120202674</v>
       </c>
       <c r="B53" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6076,46 +6037,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566583</v>
+        <v>566584</v>
       </c>
       <c r="R53" t="n">
-        <v>7040942</v>
+        <v>7041103</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6142,19 +6094,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6169,22 +6111,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120202786</v>
+        <v>120204567</v>
       </c>
       <c r="B54" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6193,25 +6135,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6221,10 +6163,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566623</v>
+        <v>566612</v>
       </c>
       <c r="R54" t="n">
-        <v>7041032</v>
+        <v>7041175</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6283,10 +6225,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120202297</v>
+        <v>120201490</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6299,21 +6241,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6323,13 +6265,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566551</v>
+        <v>566563</v>
       </c>
       <c r="R55" t="n">
-        <v>7040999</v>
+        <v>7040951</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6356,9 +6298,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6373,22 +6325,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120204797</v>
+        <v>120203078</v>
       </c>
       <c r="B56" t="n">
-        <v>96885</v>
+        <v>79623</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6397,25 +6349,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6425,10 +6377,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566572</v>
+        <v>566621</v>
       </c>
       <c r="R56" t="n">
-        <v>7041137</v>
+        <v>7041057</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6487,10 +6439,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120205460</v>
+        <v>120202571</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6499,31 +6451,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6532,10 +6483,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566500</v>
+        <v>566582</v>
       </c>
       <c r="R57" t="n">
-        <v>7041094</v>
+        <v>7041015</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6568,11 +6519,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6599,10 +6545,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120201661</v>
+        <v>120205154</v>
       </c>
       <c r="B58" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6611,41 +6557,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566582</v>
+        <v>566510</v>
       </c>
       <c r="R58" t="n">
-        <v>7040944</v>
+        <v>7041190</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6672,19 +6622,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6699,22 +6639,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120201451</v>
+        <v>120205398</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6727,21 +6667,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6751,10 +6691,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566541</v>
+        <v>566613</v>
       </c>
       <c r="R59" t="n">
-        <v>7040997</v>
+        <v>7040940</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6786,7 +6726,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6796,7 +6736,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6823,10 +6763,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120205398</v>
+        <v>120204405</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6835,25 +6775,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6863,13 +6803,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566613</v>
+        <v>566637</v>
       </c>
       <c r="R60" t="n">
-        <v>7040940</v>
+        <v>7041131</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6896,19 +6836,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6923,22 +6853,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120205468</v>
+        <v>120202392</v>
       </c>
       <c r="B61" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6947,38 +6877,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566498</v>
+        <v>566555</v>
       </c>
       <c r="R61" t="n">
-        <v>7041093</v>
+        <v>7041027</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7037,10 +6971,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120204835</v>
+        <v>120203123</v>
       </c>
       <c r="B62" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7049,38 +6983,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566561</v>
+        <v>566628</v>
       </c>
       <c r="R62" t="n">
-        <v>7041134</v>
+        <v>7041063</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7139,10 +7077,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120204267</v>
+        <v>120201350</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7151,25 +7089,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7179,13 +7117,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566695</v>
+        <v>566534</v>
       </c>
       <c r="R63" t="n">
-        <v>7041080</v>
+        <v>7040990</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7212,9 +7150,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7229,22 +7177,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120205192</v>
+        <v>120202642</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7257,39 +7205,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566499</v>
+        <v>566590</v>
       </c>
       <c r="R64" t="n">
-        <v>7041186</v>
+        <v>7041023</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7322,11 +7265,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7353,10 +7291,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120200869</v>
+        <v>120201983</v>
       </c>
       <c r="B65" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7369,34 +7307,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566512</v>
+        <v>566636</v>
       </c>
       <c r="R65" t="n">
-        <v>7041220</v>
+        <v>7040903</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7428,7 +7371,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7438,7 +7381,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7453,22 +7396,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120204056</v>
+        <v>120201620</v>
       </c>
       <c r="B66" t="n">
-        <v>92048</v>
+        <v>91023</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7477,25 +7420,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7505,13 +7448,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566678</v>
+        <v>566582</v>
       </c>
       <c r="R66" t="n">
-        <v>7041077</v>
+        <v>7040944</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7538,9 +7481,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,22 +7508,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120204980</v>
+        <v>120204013</v>
       </c>
       <c r="B67" t="n">
-        <v>90598</v>
+        <v>78278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7583,21 +7536,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7607,10 +7560,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566561</v>
+        <v>566666</v>
       </c>
       <c r="R67" t="n">
-        <v>7041107</v>
+        <v>7041066</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7669,10 +7622,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120204405</v>
+        <v>120204901</v>
       </c>
       <c r="B68" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7681,25 +7634,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7709,10 +7662,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566637</v>
+        <v>566567</v>
       </c>
       <c r="R68" t="n">
-        <v>7041131</v>
+        <v>7041107</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7771,10 +7724,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120203962</v>
+        <v>120200869</v>
       </c>
       <c r="B69" t="n">
-        <v>79160</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7787,21 +7740,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7811,13 +7764,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566665</v>
+        <v>566512</v>
       </c>
       <c r="R69" t="n">
-        <v>7041086</v>
+        <v>7041220</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7844,9 +7797,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7861,22 +7824,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120202239</v>
+        <v>120201661</v>
       </c>
       <c r="B70" t="n">
-        <v>90742</v>
+        <v>90864</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7889,21 +7852,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7913,13 +7876,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566526</v>
+        <v>566582</v>
       </c>
       <c r="R70" t="n">
-        <v>7041005</v>
+        <v>7040944</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7946,9 +7909,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7963,22 +7936,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120202811</v>
+        <v>120204056</v>
       </c>
       <c r="B71" t="n">
-        <v>90923</v>
+        <v>92048</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7987,25 +7960,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2062</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8015,10 +7988,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566616</v>
+        <v>566678</v>
       </c>
       <c r="R71" t="n">
-        <v>7041049</v>
+        <v>7041077</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8077,10 +8050,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120202622</v>
+        <v>120204939</v>
       </c>
       <c r="B72" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8089,38 +8062,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566590</v>
+        <v>566566</v>
       </c>
       <c r="R72" t="n">
-        <v>7041027</v>
+        <v>7041107</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8179,10 +8156,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120205064</v>
+        <v>120202697</v>
       </c>
       <c r="B73" t="n">
-        <v>90545</v>
+        <v>90594</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8191,25 +8168,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8219,10 +8196,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566502</v>
+        <v>566589</v>
       </c>
       <c r="R73" t="n">
-        <v>7041103</v>
+        <v>7041075</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8281,10 +8258,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120200832</v>
+        <v>120204862</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8293,46 +8270,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566507</v>
+        <v>566579</v>
       </c>
       <c r="R74" t="n">
-        <v>7041231</v>
+        <v>7041130</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8359,19 +8331,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8386,22 +8348,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120201983</v>
+        <v>120205468</v>
       </c>
       <c r="B75" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8414,42 +8376,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566636</v>
+        <v>566498</v>
       </c>
       <c r="R75" t="n">
-        <v>7040903</v>
+        <v>7041093</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8476,19 +8433,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8503,22 +8450,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120205323</v>
+        <v>120204476</v>
       </c>
       <c r="B76" t="n">
-        <v>90580</v>
+        <v>78278</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8531,21 +8478,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8555,10 +8502,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566528</v>
+        <v>566635</v>
       </c>
       <c r="R76" t="n">
-        <v>7041117</v>
+        <v>7041139</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8617,10 +8564,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120203937</v>
+        <v>120200809</v>
       </c>
       <c r="B77" t="n">
-        <v>90864</v>
+        <v>56524</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8633,37 +8580,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566660</v>
+        <v>566509</v>
       </c>
       <c r="R77" t="n">
-        <v>7041078</v>
+        <v>7041308</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8690,9 +8642,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8707,22 +8669,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120205179</v>
+        <v>120205420</v>
       </c>
       <c r="B78" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8731,41 +8693,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566503</v>
+        <v>566583</v>
       </c>
       <c r="R78" t="n">
-        <v>7041183</v>
+        <v>7040942</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8792,9 +8763,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8809,22 +8790,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120205368</v>
+        <v>120204816</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8837,39 +8818,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566521</v>
+        <v>566572</v>
       </c>
       <c r="R79" t="n">
-        <v>7041138</v>
+        <v>7041139</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8902,11 +8878,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8933,10 +8904,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120203078</v>
+        <v>120205323</v>
       </c>
       <c r="B80" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8949,21 +8920,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8973,10 +8944,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566621</v>
+        <v>566528</v>
       </c>
       <c r="R80" t="n">
-        <v>7041057</v>
+        <v>7041117</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9035,10 +9006,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120204958</v>
+        <v>120204153</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9047,25 +9018,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9075,10 +9046,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566564</v>
+        <v>566671</v>
       </c>
       <c r="R81" t="n">
-        <v>7041107</v>
+        <v>7041071</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9137,10 +9108,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120204492</v>
+        <v>120202289</v>
       </c>
       <c r="B82" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9153,21 +9124,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9177,10 +9148,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566608</v>
+        <v>566546</v>
       </c>
       <c r="R82" t="n">
-        <v>7041149</v>
+        <v>7041010</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9239,10 +9210,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120202642</v>
+        <v>120201767</v>
       </c>
       <c r="B83" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9255,21 +9226,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9279,13 +9250,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566590</v>
+        <v>566610</v>
       </c>
       <c r="R83" t="n">
-        <v>7041023</v>
+        <v>7040928</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9312,9 +9283,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9329,22 +9315,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120202824</v>
+        <v>120205084</v>
       </c>
       <c r="B84" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9353,38 +9339,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566616</v>
+        <v>566515</v>
       </c>
       <c r="R84" t="n">
-        <v>7041049</v>
+        <v>7041125</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9443,10 +9433,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120204153</v>
+        <v>120205221</v>
       </c>
       <c r="B85" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9455,38 +9445,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566671</v>
+        <v>566496</v>
       </c>
       <c r="R85" t="n">
-        <v>7041071</v>
+        <v>7041192</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9519,6 +9514,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120205064</v>
+        <v>120205192</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566502</v>
+        <v>566499</v>
       </c>
       <c r="R2" t="n">
-        <v>7041103</v>
+        <v>7041186</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120202755</v>
+        <v>120205199</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566572</v>
+        <v>566499</v>
       </c>
       <c r="R3" t="n">
-        <v>7041055</v>
+        <v>7041189</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120204358</v>
+        <v>120202755</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566663</v>
+        <v>566572</v>
       </c>
       <c r="R4" t="n">
-        <v>7041118</v>
+        <v>7041055</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120205192</v>
+        <v>120204358</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566499</v>
+        <v>566663</v>
       </c>
       <c r="R5" t="n">
-        <v>7041186</v>
+        <v>7041118</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120205199</v>
+        <v>120205064</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,43 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566499</v>
+        <v>566502</v>
       </c>
       <c r="R6" t="n">
-        <v>7041189</v>
+        <v>7041103</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1942,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204507</v>
+        <v>120204116</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,25 +1954,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566602</v>
+        <v>566691</v>
       </c>
       <c r="R14" t="n">
-        <v>7041134</v>
+        <v>7041096</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204104</v>
+        <v>120204507</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566694</v>
+        <v>566602</v>
       </c>
       <c r="R15" t="n">
-        <v>7041098</v>
+        <v>7041134</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120203962</v>
+        <v>120204104</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,21 +2162,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566665</v>
+        <v>566694</v>
       </c>
       <c r="R16" t="n">
-        <v>7041086</v>
+        <v>7041098</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120205511</v>
+        <v>120203962</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2264,39 +2264,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566509</v>
+        <v>566665</v>
       </c>
       <c r="R17" t="n">
-        <v>7041097</v>
+        <v>7041086</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2329,11 +2324,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120204116</v>
+        <v>120205511</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2372,38 +2362,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566691</v>
+        <v>566509</v>
       </c>
       <c r="R18" t="n">
-        <v>7041096</v>
+        <v>7041097</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2436,6 +2431,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3611,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120204807</v>
+        <v>120202786</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3623,25 +3623,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566575</v>
+        <v>566623</v>
       </c>
       <c r="R30" t="n">
-        <v>7041141</v>
+        <v>7041032</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120200832</v>
+        <v>120203571</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>89650</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,42 +3729,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566507</v>
+        <v>566647</v>
       </c>
       <c r="R31" t="n">
-        <v>7041231</v>
+        <v>7041053</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3791,19 +3786,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3818,22 +3803,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120204212</v>
+        <v>120202811</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3846,38 +3831,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566711</v>
+        <v>566616</v>
       </c>
       <c r="R32" t="n">
-        <v>7041082</v>
+        <v>7041049</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3936,10 +3917,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120202786</v>
+        <v>120204807</v>
       </c>
       <c r="B33" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3948,25 +3929,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3976,10 +3957,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566623</v>
+        <v>566575</v>
       </c>
       <c r="R33" t="n">
-        <v>7041032</v>
+        <v>7041141</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4038,10 +4019,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120203571</v>
+        <v>120200832</v>
       </c>
       <c r="B34" t="n">
-        <v>89650</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4054,37 +4035,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566647</v>
+        <v>566507</v>
       </c>
       <c r="R34" t="n">
-        <v>7041053</v>
+        <v>7041231</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4111,9 +4097,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4128,22 +4124,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120202811</v>
+        <v>120204212</v>
       </c>
       <c r="B35" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4156,34 +4152,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566616</v>
+        <v>566711</v>
       </c>
       <c r="R35" t="n">
-        <v>7041049</v>
+        <v>7041082</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4548,10 +4548,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120204980</v>
+        <v>120201231</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4564,21 +4564,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4588,13 +4588,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566561</v>
+        <v>566502</v>
       </c>
       <c r="R39" t="n">
-        <v>7041107</v>
+        <v>7041017</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4621,9 +4621,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4638,22 +4653,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120202867</v>
+        <v>120204980</v>
       </c>
       <c r="B40" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4662,25 +4677,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4690,10 +4705,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566626</v>
+        <v>566561</v>
       </c>
       <c r="R40" t="n">
-        <v>7041042</v>
+        <v>7041107</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4752,10 +4767,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120201231</v>
+        <v>120202867</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4764,25 +4779,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4792,13 +4807,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566502</v>
+        <v>566626</v>
       </c>
       <c r="R41" t="n">
-        <v>7041017</v>
+        <v>7041042</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4825,24 +4840,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120205460</v>
+        <v>120204267</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5391,43 +5391,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566500</v>
+        <v>566695</v>
       </c>
       <c r="R47" t="n">
-        <v>7041094</v>
+        <v>7041080</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5460,11 +5455,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5491,10 +5481,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120204267</v>
+        <v>120204835</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5507,21 +5497,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5531,10 +5521,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566695</v>
+        <v>566561</v>
       </c>
       <c r="R48" t="n">
-        <v>7041080</v>
+        <v>7041134</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5593,10 +5583,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120204835</v>
+        <v>120205460</v>
       </c>
       <c r="B49" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5605,38 +5595,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566561</v>
+        <v>566500</v>
       </c>
       <c r="R49" t="n">
-        <v>7041134</v>
+        <v>7041094</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5669,6 +5664,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6651,10 +6651,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120205398</v>
+        <v>120204405</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6663,25 +6663,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6691,13 +6691,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566613</v>
+        <v>566637</v>
       </c>
       <c r="R59" t="n">
-        <v>7040940</v>
+        <v>7041131</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6724,19 +6724,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6751,22 +6741,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120204405</v>
+        <v>120205398</v>
       </c>
       <c r="B60" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6775,25 +6765,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6803,13 +6793,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566637</v>
+        <v>566613</v>
       </c>
       <c r="R60" t="n">
-        <v>7041131</v>
+        <v>7040940</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6836,9 +6826,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6853,12 +6853,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120201350</v>
+        <v>120201983</v>
       </c>
       <c r="B63" t="n">
-        <v>79624</v>
+        <v>57473</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7093,34 +7093,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566534</v>
+        <v>566636</v>
       </c>
       <c r="R63" t="n">
-        <v>7040990</v>
+        <v>7040903</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7152,7 +7157,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7162,7 +7167,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7189,10 +7194,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120202642</v>
+        <v>120201350</v>
       </c>
       <c r="B64" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7205,21 +7210,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7229,13 +7234,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566590</v>
+        <v>566534</v>
       </c>
       <c r="R64" t="n">
-        <v>7041023</v>
+        <v>7040990</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7262,9 +7267,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7279,22 +7294,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120201983</v>
+        <v>120202642</v>
       </c>
       <c r="B65" t="n">
-        <v>57473</v>
+        <v>74654</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7307,42 +7322,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566636</v>
+        <v>566590</v>
       </c>
       <c r="R65" t="n">
-        <v>7040903</v>
+        <v>7041023</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7369,19 +7379,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7396,12 +7396,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120202697</v>
+        <v>120205468</v>
       </c>
       <c r="B73" t="n">
-        <v>90594</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8172,21 +8172,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566589</v>
+        <v>566498</v>
       </c>
       <c r="R73" t="n">
-        <v>7041075</v>
+        <v>7041093</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120204862</v>
+        <v>120204476</v>
       </c>
       <c r="B74" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8270,25 +8270,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566579</v>
+        <v>566635</v>
       </c>
       <c r="R74" t="n">
-        <v>7041130</v>
+        <v>7041139</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120205468</v>
+        <v>120202697</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>90594</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566498</v>
+        <v>566589</v>
       </c>
       <c r="R75" t="n">
-        <v>7041093</v>
+        <v>7041075</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120204476</v>
+        <v>120204862</v>
       </c>
       <c r="B76" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8474,25 +8474,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566635</v>
+        <v>566579</v>
       </c>
       <c r="R76" t="n">
-        <v>7041139</v>
+        <v>7041130</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8681,10 +8681,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120205420</v>
+        <v>120204153</v>
       </c>
       <c r="B78" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8693,50 +8693,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566583</v>
+        <v>566671</v>
       </c>
       <c r="R78" t="n">
-        <v>7040942</v>
+        <v>7041071</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8763,19 +8754,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8790,22 +8771,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120204816</v>
+        <v>120202289</v>
       </c>
       <c r="B79" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8818,21 +8799,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8842,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566572</v>
+        <v>566546</v>
       </c>
       <c r="R79" t="n">
-        <v>7041139</v>
+        <v>7041010</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8904,10 +8885,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120205323</v>
+        <v>120201767</v>
       </c>
       <c r="B80" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8920,21 +8901,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8944,13 +8925,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566528</v>
+        <v>566610</v>
       </c>
       <c r="R80" t="n">
-        <v>7041117</v>
+        <v>7040928</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8977,9 +8958,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8994,22 +8990,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120204153</v>
+        <v>120205084</v>
       </c>
       <c r="B81" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9018,38 +9014,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566671</v>
+        <v>566515</v>
       </c>
       <c r="R81" t="n">
-        <v>7041071</v>
+        <v>7041125</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120202289</v>
+        <v>120205420</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9124,37 +9124,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566546</v>
+        <v>566583</v>
       </c>
       <c r="R82" t="n">
-        <v>7041010</v>
+        <v>7040942</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9181,9 +9190,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9198,22 +9217,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120201767</v>
+        <v>120204816</v>
       </c>
       <c r="B83" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9226,21 +9245,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9250,13 +9269,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566610</v>
+        <v>566572</v>
       </c>
       <c r="R83" t="n">
-        <v>7040928</v>
+        <v>7041139</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9283,24 +9302,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9315,22 +9319,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120205084</v>
+        <v>120205323</v>
       </c>
       <c r="B84" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9339,42 +9343,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566515</v>
+        <v>566528</v>
       </c>
       <c r="R84" t="n">
-        <v>7041125</v>
+        <v>7041117</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120205192</v>
+        <v>120202492</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566499</v>
+        <v>566568</v>
       </c>
       <c r="R2" t="n">
-        <v>7041186</v>
+        <v>7041045</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120205199</v>
+        <v>120205420</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566499</v>
+        <v>566583</v>
       </c>
       <c r="R3" t="n">
-        <v>7041189</v>
+        <v>7040942</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,14 +863,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +890,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120202755</v>
+        <v>120203004</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +914,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566572</v>
+        <v>566624</v>
       </c>
       <c r="R4" t="n">
-        <v>7041055</v>
+        <v>7041079</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1001,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120204358</v>
+        <v>120202642</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566663</v>
+        <v>566590</v>
       </c>
       <c r="R5" t="n">
-        <v>7041118</v>
+        <v>7041023</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120205064</v>
+        <v>120201451</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566502</v>
+        <v>566541</v>
       </c>
       <c r="R6" t="n">
-        <v>7041103</v>
+        <v>7040997</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,9 +1179,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1206,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120204205</v>
+        <v>120202727</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566711</v>
+        <v>566577</v>
       </c>
       <c r="R7" t="n">
-        <v>7041082</v>
+        <v>7041064</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120204958</v>
+        <v>120203937</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566564</v>
+        <v>566660</v>
       </c>
       <c r="R8" t="n">
-        <v>7041107</v>
+        <v>7041078</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1511,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120202733</v>
+        <v>120201490</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,13 +1564,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566567</v>
+        <v>566563</v>
       </c>
       <c r="R10" t="n">
-        <v>7041052</v>
+        <v>7040951</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,9 +1597,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,22 +1624,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120203937</v>
+        <v>120205192</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,34 +1652,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566660</v>
+        <v>566499</v>
       </c>
       <c r="R11" t="n">
-        <v>7041078</v>
+        <v>7041186</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1689,6 +1717,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120205312</v>
+        <v>120204492</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,50 +1760,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566618</v>
+        <v>566608</v>
       </c>
       <c r="R12" t="n">
-        <v>7040939</v>
+        <v>7041149</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,19 +1821,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,22 +1838,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120202647</v>
+        <v>120205511</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,30 +1862,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1880,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566587</v>
+        <v>566509</v>
       </c>
       <c r="R13" t="n">
-        <v>7041021</v>
+        <v>7041097</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,6 +1931,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204116</v>
+        <v>120204212</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,38 +1974,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566691</v>
+        <v>566711</v>
       </c>
       <c r="R14" t="n">
-        <v>7041096</v>
+        <v>7041082</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2044,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120204507</v>
+        <v>120202647</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,38 +2080,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566602</v>
+        <v>566587</v>
       </c>
       <c r="R15" t="n">
-        <v>7041134</v>
+        <v>7041021</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2146,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120204104</v>
+        <v>120205154</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,38 +2186,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566694</v>
+        <v>566510</v>
       </c>
       <c r="R16" t="n">
-        <v>7041098</v>
+        <v>7041190</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2248,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120203962</v>
+        <v>120204056</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>92048</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2264,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2288,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566665</v>
+        <v>566678</v>
       </c>
       <c r="R17" t="n">
-        <v>7041086</v>
+        <v>7041077</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2350,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120205511</v>
+        <v>120202755</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2362,43 +2394,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566509</v>
+        <v>566572</v>
       </c>
       <c r="R18" t="n">
-        <v>7041097</v>
+        <v>7041055</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2431,11 +2458,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120205179</v>
+        <v>120204358</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,25 +2496,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566503</v>
+        <v>566663</v>
       </c>
       <c r="R19" t="n">
-        <v>7041183</v>
+        <v>7041118</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2564,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120204492</v>
+        <v>120205221</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,34 +2602,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566608</v>
+        <v>566496</v>
       </c>
       <c r="R20" t="n">
-        <v>7041149</v>
+        <v>7041192</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2640,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2666,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120205278</v>
+        <v>120203396</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2678,42 +2710,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566528</v>
+        <v>566638</v>
       </c>
       <c r="R21" t="n">
-        <v>7041117</v>
+        <v>7041075</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2772,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120202553</v>
+        <v>120204405</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2784,42 +2812,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566578</v>
+        <v>566637</v>
       </c>
       <c r="R22" t="n">
-        <v>7040998</v>
+        <v>7041131</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2878,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120203004</v>
+        <v>120205278</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,38 +2914,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566624</v>
+        <v>566528</v>
       </c>
       <c r="R23" t="n">
-        <v>7041079</v>
+        <v>7041117</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2980,10 +3008,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120204503</v>
+        <v>120205460</v>
       </c>
       <c r="B24" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,34 +3024,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566603</v>
+        <v>566500</v>
       </c>
       <c r="R24" t="n">
-        <v>7041138</v>
+        <v>7041094</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3056,6 +3089,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3082,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120200849</v>
+        <v>120205148</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3094,25 +3132,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3122,13 +3160,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566521</v>
+        <v>566529</v>
       </c>
       <c r="R25" t="n">
-        <v>7041283</v>
+        <v>7041203</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3155,24 +3193,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3187,22 +3210,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120202492</v>
+        <v>120204807</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,42 +3234,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566568</v>
+        <v>566575</v>
       </c>
       <c r="R26" t="n">
-        <v>7041045</v>
+        <v>7041141</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3305,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120202853</v>
+        <v>120204267</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3317,25 +3336,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3345,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566624</v>
+        <v>566695</v>
       </c>
       <c r="R27" t="n">
-        <v>7041060</v>
+        <v>7041080</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3407,10 +3426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120205138</v>
+        <v>120202811</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>90923</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3419,25 +3438,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566529</v>
+        <v>566616</v>
       </c>
       <c r="R28" t="n">
-        <v>7041203</v>
+        <v>7041049</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3509,10 +3528,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120203396</v>
+        <v>120200869</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3521,25 +3540,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,13 +3568,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566638</v>
+        <v>566512</v>
       </c>
       <c r="R29" t="n">
-        <v>7041075</v>
+        <v>7041220</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3582,9 +3601,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3599,22 +3628,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120202786</v>
+        <v>120202289</v>
       </c>
       <c r="B30" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3623,25 +3652,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3651,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566623</v>
+        <v>566546</v>
       </c>
       <c r="R30" t="n">
-        <v>7041032</v>
+        <v>7041010</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3713,10 +3742,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120203571</v>
+        <v>120204153</v>
       </c>
       <c r="B31" t="n">
-        <v>89650</v>
+        <v>90545</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3725,25 +3754,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3753,10 +3782,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566647</v>
+        <v>566671</v>
       </c>
       <c r="R31" t="n">
-        <v>7041053</v>
+        <v>7041071</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3815,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120202811</v>
+        <v>120205398</v>
       </c>
       <c r="B32" t="n">
-        <v>90923</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3827,25 +3856,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3855,13 +3884,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566616</v>
+        <v>566613</v>
       </c>
       <c r="R32" t="n">
-        <v>7041049</v>
+        <v>7040940</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3888,9 +3917,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3905,22 +3944,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120204807</v>
+        <v>120205468</v>
       </c>
       <c r="B33" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3929,25 +3968,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3957,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566575</v>
+        <v>566498</v>
       </c>
       <c r="R33" t="n">
-        <v>7041141</v>
+        <v>7041093</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4019,10 +4058,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120200832</v>
+        <v>120203078</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4035,42 +4074,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566507</v>
+        <v>566621</v>
       </c>
       <c r="R34" t="n">
-        <v>7041231</v>
+        <v>7041057</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4097,19 +4131,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4124,22 +4148,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120204212</v>
+        <v>120205138</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4148,42 +4172,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566711</v>
+        <v>566529</v>
       </c>
       <c r="R35" t="n">
-        <v>7041082</v>
+        <v>7041203</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4242,10 +4262,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120204797</v>
+        <v>120202733</v>
       </c>
       <c r="B36" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,25 +4274,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4282,10 +4302,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566572</v>
+        <v>566567</v>
       </c>
       <c r="R36" t="n">
-        <v>7041137</v>
+        <v>7041052</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4344,10 +4364,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120204945</v>
+        <v>120205323</v>
       </c>
       <c r="B37" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4360,21 +4380,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4384,10 +4404,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566565</v>
+        <v>566528</v>
       </c>
       <c r="R37" t="n">
-        <v>7041107</v>
+        <v>7041117</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4446,10 +4466,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120202727</v>
+        <v>120201231</v>
       </c>
       <c r="B38" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4462,21 +4482,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4486,13 +4506,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566577</v>
+        <v>566502</v>
       </c>
       <c r="R38" t="n">
-        <v>7041064</v>
+        <v>7041017</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4519,9 +4539,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4536,22 +4571,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120201231</v>
+        <v>120204939</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,41 +4595,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566502</v>
+        <v>566566</v>
       </c>
       <c r="R39" t="n">
-        <v>7041017</v>
+        <v>7041107</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4621,24 +4660,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4653,22 +4677,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120204980</v>
+        <v>120204567</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,25 +4701,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4705,10 +4729,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566561</v>
+        <v>566612</v>
       </c>
       <c r="R40" t="n">
-        <v>7041107</v>
+        <v>7041175</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4767,10 +4791,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120202867</v>
+        <v>120204503</v>
       </c>
       <c r="B41" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4779,25 +4803,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4807,10 +4831,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566626</v>
+        <v>566603</v>
       </c>
       <c r="R41" t="n">
-        <v>7041042</v>
+        <v>7041138</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4869,10 +4893,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120202768</v>
+        <v>120201620</v>
       </c>
       <c r="B42" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4881,25 +4905,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4909,13 +4933,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566600</v>
+        <v>566582</v>
       </c>
       <c r="R42" t="n">
-        <v>7041007</v>
+        <v>7040944</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4942,9 +4966,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4959,22 +4993,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120202297</v>
+        <v>120205368</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4987,34 +5021,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566551</v>
+        <v>566521</v>
       </c>
       <c r="R43" t="n">
-        <v>7040999</v>
+        <v>7041138</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5047,6 +5086,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5073,10 +5117,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120202622</v>
+        <v>120201350</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>79624</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5085,25 +5129,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5113,13 +5157,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566590</v>
+        <v>566534</v>
       </c>
       <c r="R44" t="n">
-        <v>7041027</v>
+        <v>7040990</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5146,9 +5190,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5163,22 +5217,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120205024</v>
+        <v>120204116</v>
       </c>
       <c r="B45" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,21 +5245,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5215,10 +5269,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566549</v>
+        <v>566691</v>
       </c>
       <c r="R45" t="n">
-        <v>7041126</v>
+        <v>7041096</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5277,10 +5331,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120202824</v>
+        <v>120205179</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5289,25 +5343,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5317,10 +5371,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566616</v>
+        <v>566503</v>
       </c>
       <c r="R46" t="n">
-        <v>7041049</v>
+        <v>7041183</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5379,10 +5433,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120204267</v>
+        <v>120202297</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5391,25 +5445,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5419,10 +5473,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566695</v>
+        <v>566551</v>
       </c>
       <c r="R47" t="n">
-        <v>7041080</v>
+        <v>7040999</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5481,10 +5535,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120204835</v>
+        <v>120204013</v>
       </c>
       <c r="B48" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,25 +5547,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5521,10 +5575,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566561</v>
+        <v>566666</v>
       </c>
       <c r="R48" t="n">
-        <v>7041134</v>
+        <v>7041066</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5583,10 +5637,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120205460</v>
+        <v>120204104</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5599,39 +5653,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566500</v>
+        <v>566694</v>
       </c>
       <c r="R49" t="n">
-        <v>7041094</v>
+        <v>7041098</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5664,11 +5713,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5695,10 +5739,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120205148</v>
+        <v>120203962</v>
       </c>
       <c r="B50" t="n">
-        <v>79652</v>
+        <v>79160</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5707,25 +5751,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5735,10 +5779,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566529</v>
+        <v>566665</v>
       </c>
       <c r="R50" t="n">
-        <v>7041203</v>
+        <v>7041086</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5797,10 +5841,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120201451</v>
+        <v>120204476</v>
       </c>
       <c r="B51" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5813,21 +5857,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5837,13 +5881,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566541</v>
+        <v>566635</v>
       </c>
       <c r="R51" t="n">
-        <v>7040997</v>
+        <v>7041139</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5870,19 +5914,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5897,22 +5931,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120205368</v>
+        <v>120200809</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5925,16 +5959,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5945,7 +5979,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5954,13 +5988,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566521</v>
+        <v>566509</v>
       </c>
       <c r="R52" t="n">
-        <v>7041138</v>
+        <v>7041308</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5987,14 +6021,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6009,22 +6048,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120202674</v>
+        <v>120201983</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6037,37 +6076,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566584</v>
+        <v>566636</v>
       </c>
       <c r="R53" t="n">
-        <v>7041103</v>
+        <v>7040903</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6094,9 +6138,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6111,22 +6165,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120204567</v>
+        <v>120205084</v>
       </c>
       <c r="B54" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6135,38 +6189,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566612</v>
+        <v>566515</v>
       </c>
       <c r="R54" t="n">
-        <v>7041175</v>
+        <v>7041125</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6225,10 +6283,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120201490</v>
+        <v>120204901</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6241,21 +6299,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6265,13 +6323,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566563</v>
+        <v>566567</v>
       </c>
       <c r="R55" t="n">
-        <v>7040951</v>
+        <v>7041107</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6298,19 +6356,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6325,22 +6373,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120203078</v>
+        <v>120203571</v>
       </c>
       <c r="B56" t="n">
-        <v>79623</v>
+        <v>89650</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6353,21 +6401,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6377,10 +6425,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566621</v>
+        <v>566647</v>
       </c>
       <c r="R56" t="n">
-        <v>7041057</v>
+        <v>7041053</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6439,10 +6487,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120202571</v>
+        <v>120202674</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6451,42 +6499,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566582</v>
+        <v>566584</v>
       </c>
       <c r="R57" t="n">
-        <v>7041015</v>
+        <v>7041103</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6545,10 +6589,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120205154</v>
+        <v>120202867</v>
       </c>
       <c r="B58" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6557,42 +6601,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566510</v>
+        <v>566626</v>
       </c>
       <c r="R58" t="n">
-        <v>7041190</v>
+        <v>7041042</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6651,10 +6691,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120204405</v>
+        <v>120204797</v>
       </c>
       <c r="B59" t="n">
-        <v>90545</v>
+        <v>96885</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6667,21 +6707,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6691,10 +6731,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566637</v>
+        <v>566572</v>
       </c>
       <c r="R59" t="n">
-        <v>7041131</v>
+        <v>7041137</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6753,10 +6793,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120205398</v>
+        <v>120203123</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6765,41 +6805,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566613</v>
+        <v>566628</v>
       </c>
       <c r="R60" t="n">
-        <v>7040940</v>
+        <v>7041063</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6826,19 +6870,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6853,22 +6887,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120202392</v>
+        <v>120204862</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6877,42 +6911,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566555</v>
+        <v>566579</v>
       </c>
       <c r="R61" t="n">
-        <v>7041027</v>
+        <v>7041130</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6971,10 +7001,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120203123</v>
+        <v>120202622</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6983,42 +7013,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566628</v>
+        <v>566590</v>
       </c>
       <c r="R62" t="n">
-        <v>7041063</v>
+        <v>7041027</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7077,10 +7103,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120201983</v>
+        <v>120204980</v>
       </c>
       <c r="B63" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7093,42 +7119,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566636</v>
+        <v>566561</v>
       </c>
       <c r="R63" t="n">
-        <v>7040903</v>
+        <v>7041107</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7155,19 +7176,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7182,22 +7193,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120201350</v>
+        <v>120204816</v>
       </c>
       <c r="B64" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7210,21 +7221,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7234,13 +7245,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566534</v>
+        <v>566572</v>
       </c>
       <c r="R64" t="n">
-        <v>7040990</v>
+        <v>7041139</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7267,19 +7278,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7294,22 +7295,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120202642</v>
+        <v>120202786</v>
       </c>
       <c r="B65" t="n">
-        <v>74654</v>
+        <v>91023</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7318,25 +7319,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7346,10 +7347,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566590</v>
+        <v>566623</v>
       </c>
       <c r="R65" t="n">
-        <v>7041023</v>
+        <v>7041032</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7408,10 +7409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120201620</v>
+        <v>120202824</v>
       </c>
       <c r="B66" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7420,25 +7421,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7448,13 +7449,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566582</v>
+        <v>566616</v>
       </c>
       <c r="R66" t="n">
-        <v>7040944</v>
+        <v>7041049</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7481,19 +7482,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7508,22 +7499,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120204013</v>
+        <v>120205199</v>
       </c>
       <c r="B67" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7536,34 +7527,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566666</v>
+        <v>566499</v>
       </c>
       <c r="R67" t="n">
-        <v>7041066</v>
+        <v>7041189</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7596,6 +7592,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7622,10 +7623,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120204901</v>
+        <v>120201767</v>
       </c>
       <c r="B68" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7638,21 +7639,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7662,13 +7663,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566567</v>
+        <v>566610</v>
       </c>
       <c r="R68" t="n">
-        <v>7041107</v>
+        <v>7040928</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7695,9 +7696,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7712,22 +7728,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120200869</v>
+        <v>120202392</v>
       </c>
       <c r="B69" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7736,41 +7752,45 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>566512</v>
+        <v>566555</v>
       </c>
       <c r="R69" t="n">
-        <v>7041220</v>
+        <v>7041027</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7797,19 +7817,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7824,19 +7834,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120201661</v>
+        <v>120202768</v>
       </c>
       <c r="B70" t="n">
         <v>90864</v>
@@ -7876,13 +7886,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566582</v>
+        <v>566600</v>
       </c>
       <c r="R70" t="n">
-        <v>7040944</v>
+        <v>7041007</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7909,19 +7919,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7936,22 +7936,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120204056</v>
+        <v>120202697</v>
       </c>
       <c r="B71" t="n">
-        <v>92048</v>
+        <v>90594</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7964,21 +7964,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>1204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566678</v>
+        <v>566589</v>
       </c>
       <c r="R71" t="n">
-        <v>7041077</v>
+        <v>7041075</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8050,10 +8050,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120204939</v>
+        <v>120204958</v>
       </c>
       <c r="B72" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8062,39 +8062,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566566</v>
+        <v>566564</v>
       </c>
       <c r="R72" t="n">
         <v>7041107</v>
@@ -8156,10 +8152,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120205468</v>
+        <v>120204507</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>79160</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8172,21 +8168,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8196,10 +8192,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>566498</v>
+        <v>566602</v>
       </c>
       <c r="R73" t="n">
-        <v>7041093</v>
+        <v>7041134</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8258,10 +8254,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120204476</v>
+        <v>120202853</v>
       </c>
       <c r="B74" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8274,21 +8270,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8298,10 +8294,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566635</v>
+        <v>566624</v>
       </c>
       <c r="R74" t="n">
-        <v>7041139</v>
+        <v>7041060</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8360,10 +8356,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120202697</v>
+        <v>120204835</v>
       </c>
       <c r="B75" t="n">
-        <v>90594</v>
+        <v>90545</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8372,25 +8368,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8400,10 +8396,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566589</v>
+        <v>566561</v>
       </c>
       <c r="R75" t="n">
-        <v>7041075</v>
+        <v>7041134</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8462,10 +8458,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120204862</v>
+        <v>120202571</v>
       </c>
       <c r="B76" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8474,38 +8470,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566579</v>
+        <v>566582</v>
       </c>
       <c r="R76" t="n">
-        <v>7041130</v>
+        <v>7041015</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120200809</v>
+        <v>120205312</v>
       </c>
       <c r="B77" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8576,31 +8576,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8609,10 +8613,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566509</v>
+        <v>566618</v>
       </c>
       <c r="R77" t="n">
-        <v>7041308</v>
+        <v>7040939</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8644,7 +8648,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8654,7 +8658,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8669,22 +8673,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120204153</v>
+        <v>120204945</v>
       </c>
       <c r="B78" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8693,25 +8697,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8721,10 +8725,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566671</v>
+        <v>566565</v>
       </c>
       <c r="R78" t="n">
-        <v>7041071</v>
+        <v>7041107</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8783,7 +8787,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120202289</v>
+        <v>120204205</v>
       </c>
       <c r="B79" t="n">
         <v>78542</v>
@@ -8823,10 +8827,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566546</v>
+        <v>566711</v>
       </c>
       <c r="R79" t="n">
-        <v>7041010</v>
+        <v>7041082</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8885,7 +8889,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120201767</v>
+        <v>120200849</v>
       </c>
       <c r="B80" t="n">
         <v>57320</v>
@@ -8925,10 +8929,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566610</v>
+        <v>566521</v>
       </c>
       <c r="R80" t="n">
-        <v>7040928</v>
+        <v>7041283</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8960,7 +8964,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8970,12 +8974,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9002,10 +9006,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120205084</v>
+        <v>120200832</v>
       </c>
       <c r="B81" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9014,30 +9018,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9046,13 +9051,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566515</v>
+        <v>566507</v>
       </c>
       <c r="R81" t="n">
-        <v>7041125</v>
+        <v>7041231</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9079,9 +9084,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9096,19 +9111,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120205420</v>
+        <v>120201661</v>
       </c>
       <c r="B82" t="n">
         <v>90864</v>
@@ -9141,26 +9156,17 @@
           <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566583</v>
+        <v>566582</v>
       </c>
       <c r="R82" t="n">
-        <v>7040942</v>
+        <v>7040944</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9192,7 +9198,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9202,7 +9208,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9217,22 +9223,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120204816</v>
+        <v>120205064</v>
       </c>
       <c r="B83" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9241,25 +9247,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9269,10 +9275,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566572</v>
+        <v>566502</v>
       </c>
       <c r="R83" t="n">
-        <v>7041139</v>
+        <v>7041103</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9331,10 +9337,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120205323</v>
+        <v>120205024</v>
       </c>
       <c r="B84" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9343,25 +9349,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9371,10 +9377,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566528</v>
+        <v>566549</v>
       </c>
       <c r="R84" t="n">
-        <v>7041117</v>
+        <v>7041126</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9433,10 +9439,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120205221</v>
+        <v>120202553</v>
       </c>
       <c r="B85" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9445,31 +9451,30 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9478,10 +9483,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566496</v>
+        <v>566578</v>
       </c>
       <c r="R85" t="n">
-        <v>7041192</v>
+        <v>7040998</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9514,11 +9519,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120202492</v>
+        <v>120203571</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>89650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566568</v>
+        <v>566647</v>
       </c>
       <c r="R2" t="n">
-        <v>7041045</v>
+        <v>7041053</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120205420</v>
+        <v>120205192</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566583</v>
+        <v>566499</v>
       </c>
       <c r="R3" t="n">
-        <v>7040942</v>
+        <v>7041186</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,19 +855,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:07</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120203004</v>
+        <v>120204267</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566624</v>
+        <v>566695</v>
       </c>
       <c r="R4" t="n">
-        <v>7041079</v>
+        <v>7041080</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1004,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120202642</v>
+        <v>120204797</v>
       </c>
       <c r="B5" t="n">
-        <v>74654</v>
+        <v>96885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566590</v>
+        <v>566572</v>
       </c>
       <c r="R5" t="n">
-        <v>7041023</v>
+        <v>7041137</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120201451</v>
+        <v>120204212</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,41 +1105,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566541</v>
+        <v>566711</v>
       </c>
       <c r="R6" t="n">
-        <v>7040997</v>
+        <v>7041082</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,19 +1170,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120202727</v>
+        <v>120205221</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,34 +1215,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566577</v>
+        <v>566496</v>
       </c>
       <c r="R7" t="n">
-        <v>7041064</v>
+        <v>7041192</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1294,6 +1280,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120203937</v>
+        <v>120201983</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,37 +1327,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566660</v>
+        <v>566636</v>
       </c>
       <c r="R8" t="n">
-        <v>7041078</v>
+        <v>7040903</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,9 +1389,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,22 +1416,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120202239</v>
+        <v>120204980</v>
       </c>
       <c r="B9" t="n">
-        <v>90742</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566526</v>
+        <v>566561</v>
       </c>
       <c r="R9" t="n">
-        <v>7041005</v>
+        <v>7041107</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1524,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120201490</v>
+        <v>120205084</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,41 +1542,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566563</v>
+        <v>566515</v>
       </c>
       <c r="R10" t="n">
-        <v>7040951</v>
+        <v>7041125</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,19 +1607,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,22 +1624,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120205192</v>
+        <v>120205179</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,43 +1648,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566499</v>
+        <v>566503</v>
       </c>
       <c r="R11" t="n">
-        <v>7041186</v>
+        <v>7041183</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1717,11 +1712,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204492</v>
+        <v>120204901</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,21 +1754,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566608</v>
+        <v>566567</v>
       </c>
       <c r="R12" t="n">
-        <v>7041149</v>
+        <v>7041107</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1850,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120205511</v>
+        <v>120203078</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,39 +1856,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566509</v>
+        <v>566621</v>
       </c>
       <c r="R13" t="n">
-        <v>7041097</v>
+        <v>7041057</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1931,11 +1916,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204212</v>
+        <v>120204476</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,42 +1954,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566711</v>
+        <v>566635</v>
       </c>
       <c r="R14" t="n">
-        <v>7041082</v>
+        <v>7041139</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2068,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120202647</v>
+        <v>120204056</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>92048</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,42 +2056,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566587</v>
+        <v>566678</v>
       </c>
       <c r="R15" t="n">
-        <v>7041021</v>
+        <v>7041077</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2174,10 +2146,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120205154</v>
+        <v>120201350</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,45 +2158,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566510</v>
+        <v>566534</v>
       </c>
       <c r="R16" t="n">
-        <v>7041190</v>
+        <v>7040990</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,9 +2219,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,22 +2246,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120204056</v>
+        <v>120202697</v>
       </c>
       <c r="B17" t="n">
-        <v>92048</v>
+        <v>90594</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2274,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566678</v>
+        <v>566589</v>
       </c>
       <c r="R17" t="n">
-        <v>7041077</v>
+        <v>7041075</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2382,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120202755</v>
+        <v>120202289</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,25 +2372,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566572</v>
+        <v>566546</v>
       </c>
       <c r="R18" t="n">
-        <v>7041055</v>
+        <v>7041010</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2484,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120204358</v>
+        <v>120200869</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,13 +2502,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566663</v>
+        <v>566512</v>
       </c>
       <c r="R19" t="n">
-        <v>7041118</v>
+        <v>7041220</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,9 +2535,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,22 +2562,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120205221</v>
+        <v>120201451</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,42 +2590,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566496</v>
+        <v>566541</v>
       </c>
       <c r="R20" t="n">
-        <v>7041192</v>
+        <v>7040997</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2664,14 +2647,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,22 +2674,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120203396</v>
+        <v>120204153</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2702,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566638</v>
+        <v>566671</v>
       </c>
       <c r="R21" t="n">
-        <v>7041075</v>
+        <v>7041071</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2800,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120204405</v>
+        <v>120204945</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2800,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2828,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566637</v>
+        <v>566565</v>
       </c>
       <c r="R22" t="n">
-        <v>7041131</v>
+        <v>7041107</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2902,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120205278</v>
+        <v>120205368</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2914,30 +2902,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2946,10 +2935,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566528</v>
+        <v>566521</v>
       </c>
       <c r="R23" t="n">
-        <v>7041117</v>
+        <v>7041138</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2982,6 +2971,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3008,7 +3002,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120205460</v>
+        <v>120200832</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3053,13 +3047,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566500</v>
+        <v>566507</v>
       </c>
       <c r="R24" t="n">
-        <v>7041094</v>
+        <v>7041231</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3086,14 +3080,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3108,22 +3107,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120205148</v>
+        <v>120202786</v>
       </c>
       <c r="B25" t="n">
-        <v>79652</v>
+        <v>91023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,25 +3131,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3160,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566529</v>
+        <v>566623</v>
       </c>
       <c r="R25" t="n">
-        <v>7041203</v>
+        <v>7041032</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3222,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120204807</v>
+        <v>120202674</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,25 +3233,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3262,10 +3261,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566575</v>
+        <v>566584</v>
       </c>
       <c r="R26" t="n">
-        <v>7041141</v>
+        <v>7041103</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3324,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120204267</v>
+        <v>120202867</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3340,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3364,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566695</v>
+        <v>566626</v>
       </c>
       <c r="R27" t="n">
-        <v>7041080</v>
+        <v>7041042</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3426,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120202811</v>
+        <v>120205148</v>
       </c>
       <c r="B28" t="n">
-        <v>90923</v>
+        <v>79652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,25 +3437,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566616</v>
+        <v>566529</v>
       </c>
       <c r="R28" t="n">
-        <v>7041049</v>
+        <v>7041203</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3528,10 +3527,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120200869</v>
+        <v>120204567</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,25 +3539,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3568,13 +3567,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566512</v>
+        <v>566612</v>
       </c>
       <c r="R29" t="n">
-        <v>7041220</v>
+        <v>7041175</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3601,19 +3600,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3628,22 +3617,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120202289</v>
+        <v>120202492</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3652,38 +3641,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566546</v>
+        <v>566568</v>
       </c>
       <c r="R30" t="n">
-        <v>7041010</v>
+        <v>7041045</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3742,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120204153</v>
+        <v>120204939</v>
       </c>
       <c r="B31" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,38 +3747,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566671</v>
+        <v>566566</v>
       </c>
       <c r="R31" t="n">
-        <v>7041071</v>
+        <v>7041107</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3844,10 +3841,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120205398</v>
+        <v>120204116</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,25 +3853,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3884,13 +3881,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566613</v>
+        <v>566691</v>
       </c>
       <c r="R32" t="n">
-        <v>7040940</v>
+        <v>7041096</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3917,19 +3914,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3944,19 +3931,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120205468</v>
+        <v>120205138</v>
       </c>
       <c r="B33" t="n">
         <v>79623</v>
@@ -3996,10 +3983,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566498</v>
+        <v>566529</v>
       </c>
       <c r="R33" t="n">
-        <v>7041093</v>
+        <v>7041203</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4058,10 +4045,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120203078</v>
+        <v>120205064</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,25 +4057,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4098,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566621</v>
+        <v>566502</v>
       </c>
       <c r="R34" t="n">
-        <v>7041057</v>
+        <v>7041103</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4160,10 +4147,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120205138</v>
+        <v>120202733</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4176,21 +4163,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4187,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566529</v>
+        <v>566567</v>
       </c>
       <c r="R35" t="n">
-        <v>7041203</v>
+        <v>7041052</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4262,7 +4249,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120202733</v>
+        <v>120202297</v>
       </c>
       <c r="B36" t="n">
         <v>90580</v>
@@ -4302,10 +4289,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566567</v>
+        <v>566551</v>
       </c>
       <c r="R36" t="n">
-        <v>7041052</v>
+        <v>7040999</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4364,10 +4351,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120205323</v>
+        <v>120205024</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4376,25 +4363,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4404,10 +4391,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566528</v>
+        <v>566549</v>
       </c>
       <c r="R37" t="n">
-        <v>7041117</v>
+        <v>7041126</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4466,10 +4453,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120201231</v>
+        <v>120202642</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4482,21 +4469,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4506,13 +4493,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566502</v>
+        <v>566590</v>
       </c>
       <c r="R38" t="n">
-        <v>7041017</v>
+        <v>7041023</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4539,24 +4526,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4571,22 +4543,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120204939</v>
+        <v>120203962</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4595,42 +4567,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566566</v>
+        <v>566665</v>
       </c>
       <c r="R39" t="n">
-        <v>7041107</v>
+        <v>7041086</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4689,10 +4657,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120204567</v>
+        <v>120201767</v>
       </c>
       <c r="B40" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4701,25 +4669,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4729,13 +4697,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566612</v>
+        <v>566610</v>
       </c>
       <c r="R40" t="n">
-        <v>7041175</v>
+        <v>7040928</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4762,9 +4730,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,22 +4762,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120204503</v>
+        <v>120202571</v>
       </c>
       <c r="B41" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4803,38 +4786,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566603</v>
+        <v>566582</v>
       </c>
       <c r="R41" t="n">
-        <v>7041138</v>
+        <v>7041015</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4893,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120201620</v>
+        <v>120204358</v>
       </c>
       <c r="B42" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4905,25 +4892,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4933,13 +4920,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566582</v>
+        <v>566663</v>
       </c>
       <c r="R42" t="n">
-        <v>7040944</v>
+        <v>7041118</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4966,19 +4953,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4993,22 +4970,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120205368</v>
+        <v>120205323</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,39 +4998,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566521</v>
+        <v>566528</v>
       </c>
       <c r="R43" t="n">
-        <v>7041138</v>
+        <v>7041117</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5086,11 +5058,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5117,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120201350</v>
+        <v>120202853</v>
       </c>
       <c r="B44" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5133,21 +5100,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5157,13 +5124,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566534</v>
+        <v>566624</v>
       </c>
       <c r="R44" t="n">
-        <v>7040990</v>
+        <v>7041060</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5190,19 +5157,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,22 +5174,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120204116</v>
+        <v>120204958</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5241,25 +5198,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5269,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566691</v>
+        <v>566564</v>
       </c>
       <c r="R45" t="n">
-        <v>7041096</v>
+        <v>7041107</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5331,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120205179</v>
+        <v>120201620</v>
       </c>
       <c r="B46" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5343,25 +5300,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5371,13 +5328,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566503</v>
+        <v>566582</v>
       </c>
       <c r="R46" t="n">
-        <v>7041183</v>
+        <v>7040944</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5404,9 +5361,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5421,22 +5388,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120202297</v>
+        <v>120203396</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5445,25 +5412,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5473,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566551</v>
+        <v>566638</v>
       </c>
       <c r="R47" t="n">
-        <v>7040999</v>
+        <v>7041075</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5535,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120204013</v>
+        <v>120205312</v>
       </c>
       <c r="B48" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5547,41 +5514,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566666</v>
+        <v>566618</v>
       </c>
       <c r="R48" t="n">
-        <v>7041066</v>
+        <v>7040939</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5608,9 +5584,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5625,22 +5611,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120204104</v>
+        <v>120204862</v>
       </c>
       <c r="B49" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5649,25 +5635,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5677,10 +5663,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566694</v>
+        <v>566579</v>
       </c>
       <c r="R49" t="n">
-        <v>7041098</v>
+        <v>7041130</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5739,10 +5725,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120203962</v>
+        <v>120204835</v>
       </c>
       <c r="B50" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5751,25 +5737,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5779,10 +5765,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566665</v>
+        <v>566561</v>
       </c>
       <c r="R50" t="n">
-        <v>7041086</v>
+        <v>7041134</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5841,10 +5827,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120204476</v>
+        <v>120202622</v>
       </c>
       <c r="B51" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5853,25 +5839,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5881,10 +5867,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566635</v>
+        <v>566590</v>
       </c>
       <c r="R51" t="n">
-        <v>7041139</v>
+        <v>7041027</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5943,10 +5929,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120200809</v>
+        <v>120205199</v>
       </c>
       <c r="B52" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5959,16 +5945,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5979,7 +5965,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5988,13 +5974,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566509</v>
+        <v>566499</v>
       </c>
       <c r="R52" t="n">
-        <v>7041308</v>
+        <v>7041189</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6021,19 +6007,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:50</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6048,22 +6029,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120201983</v>
+        <v>120204205</v>
       </c>
       <c r="B53" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6076,42 +6057,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566636</v>
+        <v>566711</v>
       </c>
       <c r="R53" t="n">
-        <v>7040903</v>
+        <v>7041082</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6138,19 +6114,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6165,22 +6131,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120205084</v>
+        <v>120205398</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6189,45 +6155,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>566515</v>
+        <v>566613</v>
       </c>
       <c r="R54" t="n">
-        <v>7041125</v>
+        <v>7040940</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6254,9 +6216,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6271,22 +6243,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120204901</v>
+        <v>120202647</v>
       </c>
       <c r="B55" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6295,38 +6267,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>566567</v>
+        <v>566587</v>
       </c>
       <c r="R55" t="n">
-        <v>7041107</v>
+        <v>7041021</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6385,10 +6361,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120203571</v>
+        <v>120204807</v>
       </c>
       <c r="B56" t="n">
-        <v>89650</v>
+        <v>90545</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6397,25 +6373,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6425,10 +6401,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566647</v>
+        <v>566575</v>
       </c>
       <c r="R56" t="n">
-        <v>7041053</v>
+        <v>7041141</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6487,10 +6463,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120202674</v>
+        <v>120203937</v>
       </c>
       <c r="B57" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6503,21 +6479,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6527,10 +6503,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566584</v>
+        <v>566660</v>
       </c>
       <c r="R57" t="n">
-        <v>7041103</v>
+        <v>7041078</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6589,10 +6565,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120202867</v>
+        <v>120202727</v>
       </c>
       <c r="B58" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6601,25 +6577,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6629,10 +6605,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>566626</v>
+        <v>566577</v>
       </c>
       <c r="R58" t="n">
-        <v>7041042</v>
+        <v>7041064</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6691,10 +6667,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120204797</v>
+        <v>120202824</v>
       </c>
       <c r="B59" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6703,25 +6679,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6731,10 +6707,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>566572</v>
+        <v>566616</v>
       </c>
       <c r="R59" t="n">
-        <v>7041137</v>
+        <v>7041049</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6793,10 +6769,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120203123</v>
+        <v>120204405</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6805,42 +6781,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>566628</v>
+        <v>566637</v>
       </c>
       <c r="R60" t="n">
-        <v>7041063</v>
+        <v>7041131</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6899,10 +6871,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120204862</v>
+        <v>120204013</v>
       </c>
       <c r="B61" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6911,25 +6883,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6939,10 +6911,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>566579</v>
+        <v>566666</v>
       </c>
       <c r="R61" t="n">
-        <v>7041130</v>
+        <v>7041066</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7001,10 +6973,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120202622</v>
+        <v>120205511</v>
       </c>
       <c r="B62" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7013,38 +6985,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>566590</v>
+        <v>566509</v>
       </c>
       <c r="R62" t="n">
-        <v>7041027</v>
+        <v>7041097</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7077,6 +7054,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7103,10 +7085,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120204980</v>
+        <v>120200849</v>
       </c>
       <c r="B63" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7119,21 +7101,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7143,13 +7125,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>566561</v>
+        <v>566521</v>
       </c>
       <c r="R63" t="n">
-        <v>7041107</v>
+        <v>7041283</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7176,9 +7158,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7193,22 +7190,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120204816</v>
+        <v>120204503</v>
       </c>
       <c r="B64" t="n">
-        <v>90580</v>
+        <v>78279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7221,21 +7218,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7245,10 +7242,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>566572</v>
+        <v>566603</v>
       </c>
       <c r="R64" t="n">
-        <v>7041139</v>
+        <v>7041138</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7307,10 +7304,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120202786</v>
+        <v>120204816</v>
       </c>
       <c r="B65" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7319,25 +7316,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7347,10 +7344,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>566623</v>
+        <v>566572</v>
       </c>
       <c r="R65" t="n">
-        <v>7041032</v>
+        <v>7041139</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7409,7 +7406,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120202824</v>
+        <v>120203004</v>
       </c>
       <c r="B66" t="n">
         <v>90580</v>
@@ -7449,10 +7446,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>566616</v>
+        <v>566624</v>
       </c>
       <c r="R66" t="n">
-        <v>7041049</v>
+        <v>7041079</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7511,10 +7508,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120205199</v>
+        <v>120201490</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7527,42 +7524,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>566499</v>
+        <v>566563</v>
       </c>
       <c r="R67" t="n">
-        <v>7041189</v>
+        <v>7040951</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7589,14 +7581,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7611,22 +7608,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120201767</v>
+        <v>120204492</v>
       </c>
       <c r="B68" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7639,21 +7636,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7663,13 +7660,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>566610</v>
+        <v>566608</v>
       </c>
       <c r="R68" t="n">
-        <v>7040928</v>
+        <v>7041149</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7696,24 +7693,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7728,12 +7710,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7846,10 +7828,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120202768</v>
+        <v>120203123</v>
       </c>
       <c r="B70" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7858,38 +7840,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>566600</v>
+        <v>566628</v>
       </c>
       <c r="R70" t="n">
-        <v>7041007</v>
+        <v>7041063</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7948,10 +7934,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120202697</v>
+        <v>120202239</v>
       </c>
       <c r="B71" t="n">
-        <v>90594</v>
+        <v>90742</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7964,21 +7950,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>1588</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7988,10 +7974,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>566589</v>
+        <v>566526</v>
       </c>
       <c r="R71" t="n">
-        <v>7041075</v>
+        <v>7041005</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8050,10 +8036,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120204958</v>
+        <v>120202811</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8062,25 +8048,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8090,10 +8076,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>566564</v>
+        <v>566616</v>
       </c>
       <c r="R72" t="n">
-        <v>7041107</v>
+        <v>7041049</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8254,10 +8240,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120202853</v>
+        <v>120201231</v>
       </c>
       <c r="B74" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8270,21 +8256,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8294,13 +8280,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>566624</v>
+        <v>566502</v>
       </c>
       <c r="R74" t="n">
-        <v>7041060</v>
+        <v>7041017</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8327,9 +8313,24 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8344,22 +8345,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120204835</v>
+        <v>120205460</v>
       </c>
       <c r="B75" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8368,38 +8369,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>566561</v>
+        <v>566500</v>
       </c>
       <c r="R75" t="n">
-        <v>7041134</v>
+        <v>7041094</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8432,6 +8438,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8458,7 +8469,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120202571</v>
+        <v>120202553</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -8493,7 +8504,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8502,10 +8513,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>566582</v>
+        <v>566578</v>
       </c>
       <c r="R76" t="n">
-        <v>7041015</v>
+        <v>7040998</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8564,7 +8575,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120205312</v>
+        <v>120205154</v>
       </c>
       <c r="B77" t="n">
         <v>97930</v>
@@ -8599,12 +8610,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8613,13 +8619,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>566618</v>
+        <v>566510</v>
       </c>
       <c r="R77" t="n">
-        <v>7040939</v>
+        <v>7041190</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8646,19 +8652,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8673,19 +8669,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120204945</v>
+        <v>120201661</v>
       </c>
       <c r="B78" t="n">
         <v>90864</v>
@@ -8725,13 +8721,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>566565</v>
+        <v>566582</v>
       </c>
       <c r="R78" t="n">
-        <v>7041107</v>
+        <v>7040944</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8758,9 +8754,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8775,22 +8781,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120204205</v>
+        <v>120205420</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8803,37 +8809,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>566711</v>
+        <v>566583</v>
       </c>
       <c r="R79" t="n">
-        <v>7041082</v>
+        <v>7040942</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8860,9 +8875,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8877,22 +8902,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120200849</v>
+        <v>120205468</v>
       </c>
       <c r="B80" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8905,21 +8930,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8929,13 +8954,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>566521</v>
+        <v>566498</v>
       </c>
       <c r="R80" t="n">
-        <v>7041283</v>
+        <v>7041093</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8962,24 +8987,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8994,22 +9004,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120200832</v>
+        <v>120205278</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9018,31 +9028,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9051,13 +9060,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>566507</v>
+        <v>566528</v>
       </c>
       <c r="R81" t="n">
-        <v>7041231</v>
+        <v>7041117</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9084,19 +9093,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:42</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9111,22 +9110,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120201661</v>
+        <v>120200809</v>
       </c>
       <c r="B82" t="n">
-        <v>90864</v>
+        <v>56524</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9139,34 +9138,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>566582</v>
+        <v>566509</v>
       </c>
       <c r="R82" t="n">
-        <v>7040944</v>
+        <v>7041308</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9198,7 +9202,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9208,7 +9212,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9235,10 +9239,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120205064</v>
+        <v>120202755</v>
       </c>
       <c r="B83" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9247,25 +9251,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9275,10 +9279,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>566502</v>
+        <v>566572</v>
       </c>
       <c r="R83" t="n">
-        <v>7041103</v>
+        <v>7041055</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9337,10 +9341,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120205024</v>
+        <v>120204104</v>
       </c>
       <c r="B84" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9349,25 +9353,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9377,10 +9381,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>566549</v>
+        <v>566694</v>
       </c>
       <c r="R84" t="n">
-        <v>7041126</v>
+        <v>7041098</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9439,10 +9443,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120202553</v>
+        <v>120202768</v>
       </c>
       <c r="B85" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9451,42 +9455,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>566578</v>
+        <v>566600</v>
       </c>
       <c r="R85" t="n">
-        <v>7040998</v>
+        <v>7041007</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>

--- a/artfynd/A 40504-2024 artfynd.xlsx
+++ b/artfynd/A 40504-2024 artfynd.xlsx
@@ -1530,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120205084</v>
+        <v>120205179</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,42 +1542,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566515</v>
+        <v>566503</v>
       </c>
       <c r="R10" t="n">
-        <v>7041125</v>
+        <v>7041183</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1636,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120205179</v>
+        <v>120204901</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1644,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566503</v>
+        <v>566567</v>
       </c>
       <c r="R11" t="n">
-        <v>7041183</v>
+        <v>7041107</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1738,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120204901</v>
+        <v>120203078</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,21 +1750,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566567</v>
+        <v>566621</v>
       </c>
       <c r="R12" t="n">
-        <v>7041107</v>
+        <v>7041057</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1840,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120203078</v>
+        <v>120204476</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566621</v>
+        <v>566635</v>
       </c>
       <c r="R13" t="n">
-        <v>7041057</v>
+        <v>7041139</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1942,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120204476</v>
+        <v>120205084</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,38 +1950,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566635</v>
+        <v>566515</v>
       </c>
       <c r="R14" t="n">
-        <v>7041139</v>
+        <v>7041125</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120200869</v>
+        <v>120204153</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,25 +2474,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566512</v>
+        <v>566671</v>
       </c>
       <c r="R19" t="n">
-        <v>7041220</v>
+        <v>7041071</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2535,19 +2535,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2562,19 +2552,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120201451</v>
+        <v>120200869</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -2614,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566541</v>
+        <v>566512</v>
       </c>
       <c r="R20" t="n">
-        <v>7040997</v>
+        <v>7041220</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2649,7 +2639,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2659,7 +2649,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,22 +2664,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120204153</v>
+        <v>120201451</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2698,25 +2688,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2726,13 +2716,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566671</v>
+        <v>566541</v>
       </c>
       <c r="R21" t="n">
-        <v>7041071</v>
+        <v>7040997</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2759,9 +2749,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,12 +2776,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120204958</v>
+        <v>120205312</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,41 +5198,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566564</v>
+        <v>566618</v>
       </c>
       <c r="R45" t="n">
-        <v>7041107</v>
+        <v>7040939</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5259,9 +5268,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,22 +5295,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120201620</v>
+        <v>120204958</v>
       </c>
       <c r="B46" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5300,25 +5319,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5328,13 +5347,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566582</v>
+        <v>566564</v>
       </c>
       <c r="R46" t="n">
-        <v>7040944</v>
+        <v>7041107</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5361,19 +5380,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5388,22 +5397,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120203396</v>
+        <v>120201620</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5412,25 +5421,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,13 +5449,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>566638</v>
+        <v>566582</v>
       </c>
       <c r="R47" t="n">
-        <v>7041075</v>
+        <v>7040944</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5473,9 +5482,19 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,22 +5509,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120205312</v>
+        <v>120203396</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5514,50 +5533,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566618</v>
+        <v>566638</v>
       </c>
       <c r="R48" t="n">
-        <v>7040939</v>
+        <v>7041075</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5584,19 +5594,9 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5611,22 +5611,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120204862</v>
+        <v>120205199</v>
       </c>
       <c r="B49" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5635,38 +5635,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566579</v>
+        <v>566499</v>
       </c>
       <c r="R49" t="n">
-        <v>7041130</v>
+        <v>7041189</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5699,6 +5704,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5725,7 +5735,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120204835</v>
+        <v>120204862</v>
       </c>
       <c r="B50" t="n">
         <v>90545</v>
@@ -5765,10 +5775,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>566561</v>
+        <v>566579</v>
       </c>
       <c r="R50" t="n">
-        <v>7041134</v>
+        <v>7041130</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5827,7 +5837,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120202622</v>
+        <v>120204835</v>
       </c>
       <c r="B51" t="n">
         <v>90545</v>
@@ -5867,10 +5877,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>566590</v>
+        <v>566561</v>
       </c>
       <c r="R51" t="n">
-        <v>7041027</v>
+        <v>7041134</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5929,10 +5939,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120205199</v>
+        <v>120204205</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5945,39 +5955,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>566499</v>
+        <v>566711</v>
       </c>
       <c r="R52" t="n">
-        <v>7041189</v>
+        <v>7041082</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6010,11 +6015,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6041,10 +6041,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120204205</v>
+        <v>120202622</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6053,25 +6053,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>566711</v>
+        <v>566590</v>
       </c>
       <c r="R53" t="n">
-        <v>7041082</v>
+        <v>7041027</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120204807</v>
+        <v>120203937</v>
       </c>
       <c r="B56" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6373,25 +6373,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>566575</v>
+        <v>566660</v>
       </c>
       <c r="R56" t="n">
-        <v>7041141</v>
+        <v>7041078</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120203937</v>
+        <v>120204807</v>
       </c>
       <c r="B57" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6475,25 +6475,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>566660</v>
+        <v>566575</v>
       </c>
       <c r="R57" t="n">
-        <v>7041078</v>
+        <v>7041141</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
